--- a/output/2024-05-22.xlsx
+++ b/output/2024-05-22.xlsx
@@ -625,13 +625,13 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.14</v>
+        <v>2.84</v>
       </c>
       <c r="F14" t="n">
-        <v>9.83</v>
+        <v>10.24</v>
       </c>
       <c r="G14" t="n">
-        <v>46.3</v>
+        <v>44</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -640,19 +640,19 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-72.25</v>
+        <v>-26.22</v>
       </c>
       <c r="K14" t="n">
-        <v>45.6</v>
+        <v>96.06</v>
       </c>
       <c r="L14" t="n">
-        <v>85.44</v>
+        <v>99.58</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:49:59</t>
+          <t>04:51:24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.97</v>
+        <v>3.12</v>
       </c>
       <c r="F15" t="n">
-        <v>9.029999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="G15" t="n">
-        <v>62.2</v>
+        <v>60.5</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>64.5</v>
+        <v>-26.09</v>
       </c>
       <c r="K15" t="n">
-        <v>-96.64</v>
+        <v>200.78</v>
       </c>
       <c r="L15" t="n">
-        <v>116.18</v>
+        <v>202.47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:52:27</t>
+          <t>04:52:44</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.39</v>
+        <v>2.83</v>
       </c>
       <c r="F16" t="n">
-        <v>9.57</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>34.9</v>
+        <v>50.2</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>159.32</v>
+        <v>-52.74</v>
       </c>
       <c r="K16" t="n">
-        <v>-197.28</v>
+        <v>-160.02</v>
       </c>
       <c r="L16" t="n">
-        <v>253.58</v>
+        <v>168.49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:56:31</t>
+          <t>04:55:37</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="F17" t="n">
-        <v>9.06</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>62.7</v>
+        <v>34.3</v>
       </c>
       <c r="H17" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>-222.01</v>
+        <v>72.73</v>
       </c>
       <c r="K17" t="n">
-        <v>104.04</v>
+        <v>2.18</v>
       </c>
       <c r="L17" t="n">
-        <v>245.18</v>
+        <v>72.76000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:57:49</t>
+          <t>04:58:16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="F18" t="n">
-        <v>9.57</v>
+        <v>9.59</v>
       </c>
       <c r="G18" t="n">
-        <v>58</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>-24.28</v>
+        <v>144.18</v>
       </c>
       <c r="K18" t="n">
-        <v>-24.76</v>
+        <v>101.04</v>
       </c>
       <c r="L18" t="n">
-        <v>34.68</v>
+        <v>176.06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:59:19</t>
+          <t>04:59:22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.11</v>
+        <v>2.45</v>
       </c>
       <c r="F19" t="n">
         <v>9.130000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>54.5</v>
+        <v>47.3</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>28.16</v>
+        <v>-108.26</v>
       </c>
       <c r="K19" t="n">
-        <v>-193.28</v>
+        <v>135.09</v>
       </c>
       <c r="L19" t="n">
-        <v>195.32</v>
+        <v>173.12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:04:37</t>
+          <t>05:05:13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="F20" t="n">
-        <v>9.68</v>
+        <v>9.59</v>
       </c>
       <c r="G20" t="n">
-        <v>37.9</v>
+        <v>44.7</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>-353.88</v>
+        <v>-68.05</v>
       </c>
       <c r="K20" t="n">
-        <v>-167</v>
+        <v>194.38</v>
       </c>
       <c r="L20" t="n">
-        <v>391.31</v>
+        <v>205.94</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:06:11</t>
+          <t>05:06:52</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="F21" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="G21" t="n">
-        <v>66.5</v>
+        <v>50.8</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>211.28</v>
+        <v>-228.71</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5</v>
+        <v>391.89</v>
       </c>
       <c r="L21" t="n">
-        <v>211.31</v>
+        <v>453.75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:07:46</t>
+          <t>05:09:13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="F22" t="n">
-        <v>10.07</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>45.9</v>
+        <v>64.5</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-432.97</v>
+        <v>-121.8</v>
       </c>
       <c r="K22" t="n">
-        <v>-295.98</v>
+        <v>270.62</v>
       </c>
       <c r="L22" t="n">
-        <v>524.47</v>
+        <v>296.76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:12:18</t>
+          <t>05:12:32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.51</v>
+        <v>3.29</v>
       </c>
       <c r="F23" t="n">
-        <v>9.52</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="H23" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-160.07</v>
+        <v>-224.35</v>
       </c>
       <c r="K23" t="n">
-        <v>107.87</v>
+        <v>23.69</v>
       </c>
       <c r="L23" t="n">
-        <v>193.02</v>
+        <v>225.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:14:24</t>
+          <t>05:14:05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="F24" t="n">
-        <v>9.17</v>
+        <v>10.01</v>
       </c>
       <c r="G24" t="n">
-        <v>64.3</v>
+        <v>52.7</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>185.83</v>
+        <v>-97.54000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>20.15</v>
+        <v>-138.75</v>
       </c>
       <c r="L24" t="n">
-        <v>186.92</v>
+        <v>169.61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:15:39</t>
+          <t>05:14:52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.79</v>
+        <v>3.34</v>
       </c>
       <c r="F25" t="n">
-        <v>9.029999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>69.2</v>
+        <v>51.8</v>
       </c>
       <c r="H25" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>144.8</v>
+        <v>272.93</v>
       </c>
       <c r="K25" t="n">
-        <v>338.81</v>
+        <v>-358.44</v>
       </c>
       <c r="L25" t="n">
-        <v>368.46</v>
+        <v>450.52</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:20:20</t>
+          <t>05:21:10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.71</v>
+        <v>2.81</v>
       </c>
       <c r="F26" t="n">
-        <v>9.94</v>
+        <v>10.15</v>
       </c>
       <c r="G26" t="n">
-        <v>53.6</v>
+        <v>37.5</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4</v>
+        <v>4.9</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-400.94</v>
+        <v>-557.74</v>
       </c>
       <c r="K26" t="n">
-        <v>-113.4</v>
+        <v>-896.27</v>
       </c>
       <c r="L26" t="n">
-        <v>416.67</v>
+        <v>1055.64</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:22:02</t>
+          <t>05:23:18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="F27" t="n">
-        <v>9.31</v>
+        <v>9.16</v>
       </c>
       <c r="G27" t="n">
-        <v>71</v>
+        <v>50.7</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>395.11</v>
+        <v>62.57</v>
       </c>
       <c r="K27" t="n">
-        <v>142.73</v>
+        <v>147.09</v>
       </c>
       <c r="L27" t="n">
-        <v>420.1</v>
+        <v>159.85</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:23:30</t>
+          <t>05:24:42</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.39</v>
+        <v>2.83</v>
       </c>
       <c r="F28" t="n">
-        <v>10.21</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>62.3</v>
+        <v>48.1</v>
       </c>
       <c r="H28" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-898.4</v>
+        <v>-12.61</v>
       </c>
       <c r="K28" t="n">
-        <v>178.49</v>
+        <v>-260.6</v>
       </c>
       <c r="L28" t="n">
-        <v>915.96</v>
+        <v>260.91</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:30:20</t>
+          <t>05:34:26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.42</v>
+        <v>3.39</v>
       </c>
       <c r="F29" t="n">
-        <v>9.4</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>50.9</v>
+        <v>63.4</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-21.87</v>
+        <v>-149.04</v>
       </c>
       <c r="K29" t="n">
-        <v>128.21</v>
+        <v>-22.91</v>
       </c>
       <c r="L29" t="n">
-        <v>130.06</v>
+        <v>150.79</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:33:02</t>
+          <t>05:36:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="F30" t="n">
-        <v>8.92</v>
+        <v>9.81</v>
       </c>
       <c r="G30" t="n">
-        <v>50.4</v>
+        <v>52.8</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>78.39</v>
+        <v>-182.66</v>
       </c>
       <c r="K30" t="n">
-        <v>-136.81</v>
+        <v>-72.48999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>157.68</v>
+        <v>196.52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:34:49</t>
+          <t>05:38:12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.94</v>
+        <v>2.65</v>
       </c>
       <c r="F31" t="n">
-        <v>9.58</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>51.5</v>
+        <v>48.8</v>
       </c>
       <c r="H31" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>11.44</v>
+        <v>-119.65</v>
       </c>
       <c r="K31" t="n">
-        <v>-53.67</v>
+        <v>80.38</v>
       </c>
       <c r="L31" t="n">
-        <v>54.88</v>
+        <v>144.14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:40:02</t>
+          <t>05:43:34</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="F32" t="n">
-        <v>9.550000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="G32" t="n">
-        <v>56.5</v>
+        <v>64.5</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-25.95</v>
+        <v>-75.15000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>96.12</v>
+        <v>-32.71</v>
       </c>
       <c r="L32" t="n">
-        <v>99.56</v>
+        <v>81.95999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:41:49</t>
+          <t>05:44:57</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.86</v>
+        <v>2.39</v>
       </c>
       <c r="F33" t="n">
-        <v>9.27</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>54.5</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>40.96</v>
+        <v>-92.72</v>
       </c>
       <c r="K33" t="n">
-        <v>-116.21</v>
+        <v>-58.47</v>
       </c>
       <c r="L33" t="n">
-        <v>123.21</v>
+        <v>109.61</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:43:14</t>
+          <t>05:46:32</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.26</v>
+        <v>3.46</v>
       </c>
       <c r="F34" t="n">
-        <v>9.98</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>59.9</v>
+        <v>49.3</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>60.21</v>
+        <v>174.47</v>
       </c>
       <c r="K34" t="n">
-        <v>-104.78</v>
+        <v>-11.83</v>
       </c>
       <c r="L34" t="n">
-        <v>120.85</v>
+        <v>174.87</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:46:51</t>
+          <t>05:51:59</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.09</v>
+        <v>2.73</v>
       </c>
       <c r="F35" t="n">
-        <v>9.81</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>40.3</v>
+        <v>38.6</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="I35" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>175.1</v>
+        <v>-32.69</v>
       </c>
       <c r="K35" t="n">
-        <v>108.5</v>
+        <v>287.09</v>
       </c>
       <c r="L35" t="n">
-        <v>205.99</v>
+        <v>288.94</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:47:36</t>
+          <t>05:54:04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.02</v>
+        <v>3.36</v>
       </c>
       <c r="F36" t="n">
-        <v>9.640000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>57.1</v>
+        <v>54.1</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>69.62</v>
+        <v>343.61</v>
       </c>
       <c r="K36" t="n">
-        <v>37.14</v>
+        <v>-202.8</v>
       </c>
       <c r="L36" t="n">
-        <v>78.91</v>
+        <v>399</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:49:12</t>
+          <t>05:56:14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="F37" t="n">
-        <v>10.04</v>
+        <v>9.83</v>
       </c>
       <c r="G37" t="n">
-        <v>49.2</v>
+        <v>50.3</v>
       </c>
       <c r="H37" t="n">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="I37" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>88.22</v>
+        <v>108.35</v>
       </c>
       <c r="K37" t="n">
-        <v>-152.94</v>
+        <v>-516.8</v>
       </c>
       <c r="L37" t="n">
-        <v>176.56</v>
+        <v>528.04</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:55:16</t>
+          <t>06:01:12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="F38" t="n">
-        <v>9.539999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>46.6</v>
+        <v>44.7</v>
       </c>
       <c r="H38" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="I38" t="n">
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>53.01</v>
+        <v>71.28</v>
       </c>
       <c r="K38" t="n">
-        <v>14.72</v>
+        <v>-520.71</v>
       </c>
       <c r="L38" t="n">
-        <v>55.01</v>
+        <v>525.5700000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:57:49</t>
+          <t>06:03:53</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.54</v>
+        <v>3.19</v>
       </c>
       <c r="F39" t="n">
-        <v>10.02</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>51.5</v>
+        <v>56.9</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>158.59</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>-198.49</v>
+        <v>-264.08</v>
       </c>
       <c r="L39" t="n">
-        <v>254.07</v>
+        <v>272.94</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:59:54</t>
+          <t>06:05:22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="F40" t="n">
-        <v>9.08</v>
+        <v>9.82</v>
       </c>
       <c r="G40" t="n">
-        <v>39.4</v>
+        <v>54.8</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-412.36</v>
+        <v>116.11</v>
       </c>
       <c r="K40" t="n">
-        <v>452.54</v>
+        <v>1.51</v>
       </c>
       <c r="L40" t="n">
-        <v>612.24</v>
+        <v>116.12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:03:30</t>
+          <t>06:11:46</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.86</v>
+        <v>3.59</v>
       </c>
       <c r="F41" t="n">
-        <v>9.220000000000001</v>
+        <v>9.16</v>
       </c>
       <c r="G41" t="n">
-        <v>57.2</v>
+        <v>54.4</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-70.02</v>
+        <v>-383.06</v>
       </c>
       <c r="K41" t="n">
-        <v>-350.84</v>
+        <v>15.65</v>
       </c>
       <c r="L41" t="n">
-        <v>357.76</v>
+        <v>383.38</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:05:34</t>
+          <t>06:12:29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.55</v>
+        <v>3.32</v>
       </c>
       <c r="F42" t="n">
-        <v>9.34</v>
+        <v>9.51</v>
       </c>
       <c r="G42" t="n">
-        <v>54.7</v>
+        <v>53.6</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>714.84</v>
+        <v>853.6900000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>-494.24</v>
+        <v>-46.02</v>
       </c>
       <c r="L42" t="n">
-        <v>869.0599999999999</v>
+        <v>854.9299999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:07:36</t>
+          <t>06:15:02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.6</v>
+        <v>3.41</v>
       </c>
       <c r="F43" t="n">
-        <v>9.68</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>54.8</v>
+        <v>42.7</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-451.69</v>
+        <v>500.68</v>
       </c>
       <c r="K43" t="n">
-        <v>-315.12</v>
+        <v>-418.09</v>
       </c>
       <c r="L43" t="n">
-        <v>550.75</v>
+        <v>652.29</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:18:00</t>
+          <t>06:25:32</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="F44" t="n">
-        <v>10.39</v>
+        <v>10.18</v>
       </c>
       <c r="G44" t="n">
-        <v>56.1</v>
+        <v>47.9</v>
       </c>
       <c r="H44" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="I44" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>64.04000000000001</v>
+        <v>59.51</v>
       </c>
       <c r="K44" t="n">
-        <v>54.68</v>
+        <v>101.25</v>
       </c>
       <c r="L44" t="n">
-        <v>84.20999999999999</v>
+        <v>117.45</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:19:23</t>
+          <t>06:27:39</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="F45" t="n">
-        <v>9.91</v>
+        <v>9.76</v>
       </c>
       <c r="G45" t="n">
-        <v>40.1</v>
+        <v>45</v>
       </c>
       <c r="H45" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-14.13</v>
+        <v>53.17</v>
       </c>
       <c r="K45" t="n">
-        <v>99.97</v>
+        <v>65.92</v>
       </c>
       <c r="L45" t="n">
-        <v>100.96</v>
+        <v>84.69</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:21:27</t>
+          <t>06:29:51</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.24</v>
+        <v>2.98</v>
       </c>
       <c r="F46" t="n">
-        <v>9.869999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="G46" t="n">
-        <v>60.1</v>
+        <v>50.1</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="I46" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>80.08</v>
+        <v>-115.92</v>
       </c>
       <c r="K46" t="n">
-        <v>-173.06</v>
+        <v>54.73</v>
       </c>
       <c r="L46" t="n">
-        <v>190.69</v>
+        <v>128.19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:26:27</t>
+          <t>06:34:44</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.04</v>
+        <v>4.21</v>
       </c>
       <c r="F47" t="n">
-        <v>10.54</v>
+        <v>9.6</v>
       </c>
       <c r="G47" t="n">
-        <v>43.8</v>
+        <v>46.6</v>
       </c>
       <c r="H47" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="I47" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-112.43</v>
+        <v>-25.92</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.58</v>
+        <v>201.56</v>
       </c>
       <c r="L47" t="n">
-        <v>112.49</v>
+        <v>203.22</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:27:52</t>
+          <t>06:35:26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="F48" t="n">
-        <v>9.470000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="G48" t="n">
-        <v>58.6</v>
+        <v>57.4</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="I48" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-170.41</v>
+        <v>-137.01</v>
       </c>
       <c r="K48" t="n">
-        <v>-22</v>
+        <v>-153.21</v>
       </c>
       <c r="L48" t="n">
-        <v>171.82</v>
+        <v>205.54</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:29:58</t>
+          <t>06:36:56</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.88</v>
+        <v>3.67</v>
       </c>
       <c r="F49" t="n">
-        <v>9.66</v>
+        <v>9.52</v>
       </c>
       <c r="G49" t="n">
-        <v>66.40000000000001</v>
+        <v>36</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.8</v>
+        <v>131.18</v>
       </c>
       <c r="K49" t="n">
-        <v>-59.92</v>
+        <v>143.26</v>
       </c>
       <c r="L49" t="n">
-        <v>60.11</v>
+        <v>194.25</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:35:12</t>
+          <t>06:43:09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,13 +2137,13 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="F50" t="n">
-        <v>9.74</v>
+        <v>9.85</v>
       </c>
       <c r="G50" t="n">
-        <v>46.1</v>
+        <v>59.8</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2152,19 +2152,19 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>102.78</v>
+        <v>435.32</v>
       </c>
       <c r="K50" t="n">
-        <v>-25.61</v>
+        <v>-327.54</v>
       </c>
       <c r="L50" t="n">
-        <v>105.92</v>
+        <v>544.78</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:37:02</t>
+          <t>06:45:36</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="F51" t="n">
-        <v>9.550000000000001</v>
+        <v>10.01</v>
       </c>
       <c r="G51" t="n">
-        <v>55.4</v>
+        <v>53.2</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I51" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J51" t="n">
-        <v>8.68</v>
+        <v>-174.32</v>
       </c>
       <c r="K51" t="n">
-        <v>-130.86</v>
+        <v>-174.13</v>
       </c>
       <c r="L51" t="n">
-        <v>131.15</v>
+        <v>246.4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:38:09</t>
+          <t>06:47:48</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.98</v>
+        <v>3.21</v>
       </c>
       <c r="F52" t="n">
-        <v>9.390000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>56.6</v>
+        <v>53.8</v>
       </c>
       <c r="H52" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>160.31</v>
+        <v>0.87</v>
       </c>
       <c r="K52" t="n">
-        <v>-383.98</v>
+        <v>226.66</v>
       </c>
       <c r="L52" t="n">
-        <v>416.1</v>
+        <v>226.66</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:43:35</t>
+          <t>06:51:23</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.87</v>
+        <v>3.27</v>
       </c>
       <c r="F53" t="n">
-        <v>9.74</v>
+        <v>9.44</v>
       </c>
       <c r="G53" t="n">
         <v>60.8</v>
       </c>
       <c r="H53" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-222.25</v>
+        <v>-186.59</v>
       </c>
       <c r="K53" t="n">
-        <v>35.53</v>
+        <v>215.77</v>
       </c>
       <c r="L53" t="n">
-        <v>225.07</v>
+        <v>285.26</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:44:54</t>
+          <t>06:53:31</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="F54" t="n">
-        <v>9.25</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>55.7</v>
+        <v>67.3</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I54" t="n">
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>45.39</v>
+        <v>-129.26</v>
       </c>
       <c r="K54" t="n">
-        <v>-66.12</v>
+        <v>-340.29</v>
       </c>
       <c r="L54" t="n">
-        <v>80.2</v>
+        <v>364.01</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:47:22</t>
+          <t>06:55:01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.11</v>
+        <v>2.91</v>
       </c>
       <c r="F55" t="n">
-        <v>9.49</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>55.2</v>
+        <v>52</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-86.56999999999999</v>
+        <v>-144.16</v>
       </c>
       <c r="K55" t="n">
-        <v>48.52</v>
+        <v>-278.2</v>
       </c>
       <c r="L55" t="n">
-        <v>99.23999999999999</v>
+        <v>313.33</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:50:40</t>
+          <t>06:59:42</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.01</v>
+        <v>3.59</v>
       </c>
       <c r="F56" t="n">
-        <v>9.75</v>
+        <v>9.94</v>
       </c>
       <c r="G56" t="n">
-        <v>45.1</v>
+        <v>50.9</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>1069</v>
+        <v>-169.51</v>
       </c>
       <c r="K56" t="n">
-        <v>-250.11</v>
+        <v>-278.61</v>
       </c>
       <c r="L56" t="n">
-        <v>1097.86</v>
+        <v>326.13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:51:51</t>
+          <t>07:01:54</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.69</v>
+        <v>3.58</v>
       </c>
       <c r="F57" t="n">
-        <v>10.11</v>
+        <v>9.84</v>
       </c>
       <c r="G57" t="n">
-        <v>49.6</v>
+        <v>34.8</v>
       </c>
       <c r="H57" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>51.75</v>
+        <v>-21.55</v>
       </c>
       <c r="K57" t="n">
-        <v>257.55</v>
+        <v>-541.3</v>
       </c>
       <c r="L57" t="n">
-        <v>262.7</v>
+        <v>541.72</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:53:40</t>
+          <t>07:02:50</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.45</v>
+        <v>3.02</v>
       </c>
       <c r="F58" t="n">
-        <v>9.699999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="G58" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>51.84</v>
+        <v>37.22</v>
       </c>
       <c r="K58" t="n">
-        <v>339.73</v>
+        <v>432.04</v>
       </c>
       <c r="L58" t="n">
-        <v>343.66</v>
+        <v>433.64</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:02:44</t>
+          <t>07:13:56</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.58</v>
+        <v>3.13</v>
       </c>
       <c r="F59" t="n">
-        <v>9.48</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>54.6</v>
+        <v>55.2</v>
       </c>
       <c r="H59" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-75.79000000000001</v>
+        <v>203.81</v>
       </c>
       <c r="K59" t="n">
-        <v>14.61</v>
+        <v>-60.9</v>
       </c>
       <c r="L59" t="n">
-        <v>77.19</v>
+        <v>212.71</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:03:46</t>
+          <t>07:14:59</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.15</v>
+        <v>2.89</v>
       </c>
       <c r="F60" t="n">
-        <v>9.26</v>
+        <v>9.31</v>
       </c>
       <c r="G60" t="n">
-        <v>55</v>
+        <v>63.8</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-145.51</v>
+        <v>43.55</v>
       </c>
       <c r="K60" t="n">
-        <v>-190.52</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>239.73</v>
+        <v>84.23</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:05:59</t>
+          <t>07:15:44</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.3</v>
+        <v>3.63</v>
       </c>
       <c r="F61" t="n">
-        <v>9.77</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>46.8</v>
+        <v>56.7</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-78.03</v>
+        <v>98.25</v>
       </c>
       <c r="K61" t="n">
-        <v>-6.7</v>
+        <v>8.99</v>
       </c>
       <c r="L61" t="n">
-        <v>78.31999999999999</v>
+        <v>98.66</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:11:48</t>
+          <t>07:21:42</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="F62" t="n">
-        <v>9.779999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="G62" t="n">
-        <v>60.8</v>
+        <v>68.3</v>
       </c>
       <c r="H62" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>92.09999999999999</v>
+        <v>-48.73</v>
       </c>
       <c r="K62" t="n">
-        <v>-147.67</v>
+        <v>-225.19</v>
       </c>
       <c r="L62" t="n">
-        <v>174.04</v>
+        <v>230.4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:13:44</t>
+          <t>07:22:40</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.01</v>
+        <v>3.37</v>
       </c>
       <c r="F63" t="n">
-        <v>9.25</v>
+        <v>8.98</v>
       </c>
       <c r="G63" t="n">
-        <v>44.7</v>
+        <v>37.6</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>102.84</v>
+        <v>-140.88</v>
       </c>
       <c r="K63" t="n">
-        <v>-126.15</v>
+        <v>192.72</v>
       </c>
       <c r="L63" t="n">
-        <v>162.76</v>
+        <v>238.72</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:14:32</t>
+          <t>07:24:25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="F64" t="n">
-        <v>9.56</v>
+        <v>10.24</v>
       </c>
       <c r="G64" t="n">
-        <v>56.8</v>
+        <v>48.5</v>
       </c>
       <c r="H64" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>137.22</v>
+        <v>72.98</v>
       </c>
       <c r="K64" t="n">
-        <v>51.31</v>
+        <v>-36.08</v>
       </c>
       <c r="L64" t="n">
-        <v>146.5</v>
+        <v>81.41</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:20:27</t>
+          <t>07:29:47</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.14</v>
+        <v>3.63</v>
       </c>
       <c r="F65" t="n">
-        <v>9.48</v>
+        <v>9.91</v>
       </c>
       <c r="G65" t="n">
-        <v>58.8</v>
+        <v>50.2</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="I65" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>144.58</v>
+        <v>-236.03</v>
       </c>
       <c r="K65" t="n">
-        <v>-69.78</v>
+        <v>63.97</v>
       </c>
       <c r="L65" t="n">
-        <v>160.54</v>
+        <v>244.54</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:22:28</t>
+          <t>07:31:41</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.71</v>
+        <v>3.44</v>
       </c>
       <c r="F66" t="n">
-        <v>9.65</v>
+        <v>9.57</v>
       </c>
       <c r="G66" t="n">
-        <v>57.2</v>
+        <v>56.3</v>
       </c>
       <c r="H66" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="I66" t="n">
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-47.92</v>
+        <v>-5.71</v>
       </c>
       <c r="K66" t="n">
-        <v>-247.76</v>
+        <v>-93.69</v>
       </c>
       <c r="L66" t="n">
-        <v>252.35</v>
+        <v>93.86</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:24:23</t>
+          <t>07:33:04</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.18</v>
+        <v>3.48</v>
       </c>
       <c r="F67" t="n">
-        <v>10.05</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="G67" t="n">
-        <v>56.4</v>
+        <v>43.8</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-70.44</v>
+        <v>388.5</v>
       </c>
       <c r="K67" t="n">
-        <v>443.54</v>
+        <v>-232.81</v>
       </c>
       <c r="L67" t="n">
-        <v>449.1</v>
+        <v>452.91</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:29:33</t>
+          <t>07:38:30</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.67</v>
+        <v>3.58</v>
       </c>
       <c r="F68" t="n">
-        <v>9.65</v>
+        <v>10.09</v>
       </c>
       <c r="G68" t="n">
-        <v>54.8</v>
+        <v>65</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="I68" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-289.74</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>101.22</v>
+        <v>-510.32</v>
       </c>
       <c r="L68" t="n">
-        <v>306.91</v>
+        <v>517.95</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:30:44</t>
+          <t>07:41:01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.07</v>
+        <v>3.49</v>
       </c>
       <c r="F69" t="n">
-        <v>8.93</v>
+        <v>8.92</v>
       </c>
       <c r="G69" t="n">
-        <v>56</v>
+        <v>58.3</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>281.75</v>
+        <v>-286.1</v>
       </c>
       <c r="K69" t="n">
-        <v>-256.39</v>
+        <v>-200.3</v>
       </c>
       <c r="L69" t="n">
-        <v>380.94</v>
+        <v>349.25</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:32:51</t>
+          <t>07:42:41</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.81</v>
+        <v>3.81</v>
       </c>
       <c r="F70" t="n">
-        <v>9.6</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G70" t="n">
-        <v>69.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="I70" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-12.45</v>
+        <v>-402.65</v>
       </c>
       <c r="K70" t="n">
-        <v>310.18</v>
+        <v>241.12</v>
       </c>
       <c r="L70" t="n">
-        <v>310.43</v>
+        <v>469.33</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:37:15</t>
+          <t>07:48:05</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.54</v>
+        <v>3.32</v>
       </c>
       <c r="F71" t="n">
-        <v>8.470000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="G71" t="n">
-        <v>51.5</v>
+        <v>62.4</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>-141.73</v>
+        <v>247.62</v>
       </c>
       <c r="K71" t="n">
-        <v>-203.88</v>
+        <v>139.89</v>
       </c>
       <c r="L71" t="n">
-        <v>248.31</v>
+        <v>284.4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:38:50</t>
+          <t>07:50:35</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.34</v>
+        <v>3.65</v>
       </c>
       <c r="F72" t="n">
-        <v>9.98</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>53.3</v>
+        <v>42.1</v>
       </c>
       <c r="H72" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="I72" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>-488.03</v>
+        <v>142.4</v>
       </c>
       <c r="K72" t="n">
-        <v>86.51000000000001</v>
+        <v>636.48</v>
       </c>
       <c r="L72" t="n">
-        <v>495.64</v>
+        <v>652.21</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:40:27</t>
+          <t>07:52:15</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.98</v>
+        <v>3.34</v>
       </c>
       <c r="F73" t="n">
-        <v>10.24</v>
+        <v>9.75</v>
       </c>
       <c r="G73" t="n">
-        <v>53.7</v>
+        <v>50.9</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>139.99</v>
+        <v>-302.91</v>
       </c>
       <c r="K73" t="n">
-        <v>-205.69</v>
+        <v>429.66</v>
       </c>
       <c r="L73" t="n">
-        <v>248.81</v>
+        <v>525.7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:48:12</t>
+          <t>08:03:48</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.28</v>
+        <v>3.82</v>
       </c>
       <c r="F74" t="n">
-        <v>9.99</v>
+        <v>9.82</v>
       </c>
       <c r="G74" t="n">
-        <v>50.6</v>
+        <v>56.8</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I74" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>-40</v>
+        <v>20.4</v>
       </c>
       <c r="K74" t="n">
-        <v>41.14</v>
+        <v>-90.27</v>
       </c>
       <c r="L74" t="n">
-        <v>57.38</v>
+        <v>92.54000000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:49:18</t>
+          <t>08:05:42</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.83</v>
+        <v>3.9</v>
       </c>
       <c r="F75" t="n">
-        <v>9.33</v>
+        <v>10.11</v>
       </c>
       <c r="G75" t="n">
-        <v>59.8</v>
+        <v>47.5</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>10.28</v>
+        <v>49.62</v>
       </c>
       <c r="K75" t="n">
-        <v>-30.7</v>
+        <v>-87.12</v>
       </c>
       <c r="L75" t="n">
-        <v>32.38</v>
+        <v>100.26</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:51:38</t>
+          <t>08:06:58</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.87</v>
+        <v>3.65</v>
       </c>
       <c r="F76" t="n">
-        <v>8.76</v>
+        <v>10.25</v>
       </c>
       <c r="G76" t="n">
-        <v>53</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>82.52</v>
+        <v>-182.23</v>
       </c>
       <c r="K76" t="n">
-        <v>-170.63</v>
+        <v>27.96</v>
       </c>
       <c r="L76" t="n">
-        <v>189.54</v>
+        <v>184.36</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:56:30</t>
+          <t>08:11:26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.42</v>
+        <v>4.19</v>
       </c>
       <c r="F77" t="n">
-        <v>10.22</v>
+        <v>10.59</v>
       </c>
       <c r="G77" t="n">
-        <v>60.2</v>
+        <v>60</v>
       </c>
       <c r="H77" t="n">
-        <v>2.7</v>
+        <v>5.7</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-99.06</v>
+        <v>-144.22</v>
       </c>
       <c r="K77" t="n">
-        <v>68.8</v>
+        <v>190.73</v>
       </c>
       <c r="L77" t="n">
-        <v>120.6</v>
+        <v>239.11</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:57:24</t>
+          <t>08:12:51</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.03</v>
+        <v>3.16</v>
       </c>
       <c r="F78" t="n">
-        <v>9.58</v>
+        <v>9.85</v>
       </c>
       <c r="G78" t="n">
-        <v>63.7</v>
+        <v>63.4</v>
       </c>
       <c r="H78" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-79.98</v>
+        <v>-50.37</v>
       </c>
       <c r="K78" t="n">
-        <v>52.16</v>
+        <v>168.86</v>
       </c>
       <c r="L78" t="n">
-        <v>95.48</v>
+        <v>176.22</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:58:47</t>
+          <t>08:14:20</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.49</v>
+        <v>4.77</v>
       </c>
       <c r="F79" t="n">
-        <v>9.41</v>
+        <v>9.51</v>
       </c>
       <c r="G79" t="n">
-        <v>51.6</v>
+        <v>50</v>
       </c>
       <c r="H79" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>109.72</v>
+        <v>5.06</v>
       </c>
       <c r="K79" t="n">
-        <v>18.73</v>
+        <v>317.77</v>
       </c>
       <c r="L79" t="n">
-        <v>111.3</v>
+        <v>317.81</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:03:09</t>
+          <t>08:18:11</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.8</v>
+        <v>3.93</v>
       </c>
       <c r="F80" t="n">
-        <v>10.23</v>
+        <v>9.58</v>
       </c>
       <c r="G80" t="n">
-        <v>63</v>
+        <v>65.8</v>
       </c>
       <c r="H80" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>155.38</v>
+        <v>194.15</v>
       </c>
       <c r="K80" t="n">
-        <v>347.6</v>
+        <v>258.34</v>
       </c>
       <c r="L80" t="n">
-        <v>380.75</v>
+        <v>323.16</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:05:29</t>
+          <t>08:20:05</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.91</v>
+        <v>2.8</v>
       </c>
       <c r="F81" t="n">
-        <v>9.720000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="G81" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="H81" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="I81" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>82.5</v>
+        <v>-76.66</v>
       </c>
       <c r="K81" t="n">
-        <v>-15.51</v>
+        <v>108.2</v>
       </c>
       <c r="L81" t="n">
-        <v>83.94</v>
+        <v>132.6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:07:16</t>
+          <t>08:21:56</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.81</v>
+        <v>3.21</v>
       </c>
       <c r="F82" t="n">
-        <v>10.35</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>64.7</v>
+        <v>57.1</v>
       </c>
       <c r="H82" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="I82" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>18.62</v>
+        <v>-129.74</v>
       </c>
       <c r="K82" t="n">
-        <v>111.04</v>
+        <v>249.89</v>
       </c>
       <c r="L82" t="n">
-        <v>112.59</v>
+        <v>281.56</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:12:52</t>
+          <t>08:25:59</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.53</v>
+        <v>3.09</v>
       </c>
       <c r="F83" t="n">
-        <v>9.6</v>
+        <v>9.27</v>
       </c>
       <c r="G83" t="n">
-        <v>59.3</v>
+        <v>49.6</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>219.19</v>
+        <v>-318.61</v>
       </c>
       <c r="K83" t="n">
-        <v>-320.23</v>
+        <v>-234.11</v>
       </c>
       <c r="L83" t="n">
-        <v>388.07</v>
+        <v>395.37</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:13:54</t>
+          <t>08:27:33</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.14</v>
+        <v>3.76</v>
       </c>
       <c r="F84" t="n">
-        <v>10.25</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G84" t="n">
-        <v>59.5</v>
+        <v>60.5</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>558.7</v>
+        <v>200.25</v>
       </c>
       <c r="K84" t="n">
-        <v>-559.88</v>
+        <v>327.07</v>
       </c>
       <c r="L84" t="n">
-        <v>790.96</v>
+        <v>383.51</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:16:03</t>
+          <t>08:29:10</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.47</v>
+        <v>3.71</v>
       </c>
       <c r="F85" t="n">
-        <v>9.49</v>
+        <v>9.5</v>
       </c>
       <c r="G85" t="n">
-        <v>56.2</v>
+        <v>54.8</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-251.33</v>
+        <v>226.43</v>
       </c>
       <c r="K85" t="n">
-        <v>305.09</v>
+        <v>142.97</v>
       </c>
       <c r="L85" t="n">
-        <v>395.28</v>
+        <v>267.79</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:21:19</t>
+          <t>08:32:55</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.75</v>
+        <v>3.52</v>
       </c>
       <c r="F86" t="n">
-        <v>9.6</v>
+        <v>9.19</v>
       </c>
       <c r="G86" t="n">
-        <v>41.5</v>
+        <v>57.9</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="I86" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>176.4</v>
+        <v>-555.9299999999999</v>
       </c>
       <c r="K86" t="n">
-        <v>252.78</v>
+        <v>44.38</v>
       </c>
       <c r="L86" t="n">
-        <v>308.25</v>
+        <v>557.7</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:22:54</t>
+          <t>08:33:58</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.13</v>
+        <v>3.52</v>
       </c>
       <c r="F87" t="n">
-        <v>10.06</v>
+        <v>10.47</v>
       </c>
       <c r="G87" t="n">
-        <v>55.3</v>
+        <v>60.8</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>-720.01</v>
+        <v>46.13</v>
       </c>
       <c r="K87" t="n">
-        <v>-95.79000000000001</v>
+        <v>-404.38</v>
       </c>
       <c r="L87" t="n">
-        <v>726.35</v>
+        <v>407.01</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:25:01</t>
+          <t>08:36:18</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.92</v>
+        <v>3.16</v>
       </c>
       <c r="F88" t="n">
-        <v>10.56</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>60.1</v>
+        <v>49.3</v>
       </c>
       <c r="H88" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>356.84</v>
+        <v>212.71</v>
       </c>
       <c r="K88" t="n">
-        <v>-29.6</v>
+        <v>-400.74</v>
       </c>
       <c r="L88" t="n">
-        <v>358.06</v>
+        <v>453.69</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-22.xlsx
+++ b/output/2024-05-22.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-26.22</v>
+        <v>-27.78</v>
       </c>
       <c r="K14" t="n">
-        <v>96.06</v>
+        <v>101.79</v>
       </c>
       <c r="L14" t="n">
-        <v>99.58</v>
+        <v>105.51</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-26.09</v>
+        <v>-24.65</v>
       </c>
       <c r="K15" t="n">
-        <v>200.78</v>
+        <v>189.73</v>
       </c>
       <c r="L15" t="n">
-        <v>202.47</v>
+        <v>191.32</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-52.74</v>
+        <v>-44.07</v>
       </c>
       <c r="K16" t="n">
-        <v>-160.02</v>
+        <v>-133.73</v>
       </c>
       <c r="L16" t="n">
-        <v>168.49</v>
+        <v>140.81</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>72.73</v>
+        <v>93.11</v>
       </c>
       <c r="K17" t="n">
-        <v>2.18</v>
+        <v>2.79</v>
       </c>
       <c r="L17" t="n">
-        <v>72.76000000000001</v>
+        <v>93.15000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>144.18</v>
+        <v>148.8</v>
       </c>
       <c r="K18" t="n">
-        <v>101.04</v>
+        <v>104.28</v>
       </c>
       <c r="L18" t="n">
-        <v>176.06</v>
+        <v>181.7</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-108.26</v>
+        <v>-86.83</v>
       </c>
       <c r="K19" t="n">
-        <v>135.09</v>
+        <v>108.35</v>
       </c>
       <c r="L19" t="n">
-        <v>173.12</v>
+        <v>138.85</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>-68.05</v>
+        <v>-69.01000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>194.38</v>
+        <v>197.11</v>
       </c>
       <c r="L20" t="n">
-        <v>205.94</v>
+        <v>208.85</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-228.71</v>
+        <v>-212.52</v>
       </c>
       <c r="K21" t="n">
-        <v>391.89</v>
+        <v>364.15</v>
       </c>
       <c r="L21" t="n">
-        <v>453.75</v>
+        <v>421.62</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-121.8</v>
+        <v>-117.1</v>
       </c>
       <c r="K22" t="n">
-        <v>270.62</v>
+        <v>260.16</v>
       </c>
       <c r="L22" t="n">
-        <v>296.76</v>
+        <v>285.3</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-224.35</v>
+        <v>-302.32</v>
       </c>
       <c r="K23" t="n">
-        <v>23.69</v>
+        <v>31.93</v>
       </c>
       <c r="L23" t="n">
-        <v>225.6</v>
+        <v>304.01</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-97.54000000000001</v>
+        <v>-158.15</v>
       </c>
       <c r="K24" t="n">
-        <v>-138.75</v>
+        <v>-224.96</v>
       </c>
       <c r="L24" t="n">
-        <v>169.61</v>
+        <v>274.99</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>272.93</v>
+        <v>296.51</v>
       </c>
       <c r="K25" t="n">
-        <v>-358.44</v>
+        <v>-389.41</v>
       </c>
       <c r="L25" t="n">
-        <v>450.52</v>
+        <v>489.45</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-557.74</v>
+        <v>-462.63</v>
       </c>
       <c r="K26" t="n">
-        <v>-896.27</v>
+        <v>-743.4299999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>1055.64</v>
+        <v>875.62</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>62.57</v>
+        <v>117.84</v>
       </c>
       <c r="K27" t="n">
-        <v>147.09</v>
+        <v>277.01</v>
       </c>
       <c r="L27" t="n">
-        <v>159.85</v>
+        <v>301.03</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-12.61</v>
+        <v>-19.88</v>
       </c>
       <c r="K28" t="n">
-        <v>-260.6</v>
+        <v>-410.9</v>
       </c>
       <c r="L28" t="n">
-        <v>260.91</v>
+        <v>411.38</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-149.04</v>
+        <v>-138.14</v>
       </c>
       <c r="K29" t="n">
-        <v>-22.91</v>
+        <v>-21.24</v>
       </c>
       <c r="L29" t="n">
-        <v>150.79</v>
+        <v>139.76</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-182.66</v>
+        <v>-138.49</v>
       </c>
       <c r="K30" t="n">
-        <v>-72.48999999999999</v>
+        <v>-54.96</v>
       </c>
       <c r="L30" t="n">
-        <v>196.52</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-119.65</v>
+        <v>-107.89</v>
       </c>
       <c r="K31" t="n">
-        <v>80.38</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>144.14</v>
+        <v>129.98</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-75.15000000000001</v>
+        <v>-99.31</v>
       </c>
       <c r="K32" t="n">
-        <v>-32.71</v>
+        <v>-43.23</v>
       </c>
       <c r="L32" t="n">
-        <v>81.95999999999999</v>
+        <v>108.31</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>-92.72</v>
+        <v>-78.17</v>
       </c>
       <c r="K33" t="n">
-        <v>-58.47</v>
+        <v>-49.29</v>
       </c>
       <c r="L33" t="n">
-        <v>109.61</v>
+        <v>92.42</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>174.47</v>
+        <v>188.92</v>
       </c>
       <c r="K34" t="n">
-        <v>-11.83</v>
+        <v>-12.81</v>
       </c>
       <c r="L34" t="n">
-        <v>174.87</v>
+        <v>189.35</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-32.69</v>
+        <v>-32.45</v>
       </c>
       <c r="K35" t="n">
-        <v>287.09</v>
+        <v>285.01</v>
       </c>
       <c r="L35" t="n">
-        <v>288.94</v>
+        <v>286.85</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>343.61</v>
+        <v>365.51</v>
       </c>
       <c r="K36" t="n">
-        <v>-202.8</v>
+        <v>-215.73</v>
       </c>
       <c r="L36" t="n">
-        <v>399</v>
+        <v>424.43</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>108.35</v>
+        <v>106.57</v>
       </c>
       <c r="K37" t="n">
-        <v>-516.8</v>
+        <v>-508.3</v>
       </c>
       <c r="L37" t="n">
-        <v>528.04</v>
+        <v>519.35</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>71.28</v>
+        <v>77.39</v>
       </c>
       <c r="K38" t="n">
-        <v>-520.71</v>
+        <v>-565.3099999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>525.5700000000001</v>
+        <v>570.59</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>68.95999999999999</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>-264.08</v>
+        <v>-363.83</v>
       </c>
       <c r="L39" t="n">
-        <v>272.94</v>
+        <v>376.03</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>116.11</v>
+        <v>220.48</v>
       </c>
       <c r="K40" t="n">
-        <v>1.51</v>
+        <v>2.86</v>
       </c>
       <c r="L40" t="n">
-        <v>116.12</v>
+        <v>220.5</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-383.06</v>
+        <v>-530</v>
       </c>
       <c r="K41" t="n">
-        <v>15.65</v>
+        <v>21.65</v>
       </c>
       <c r="L41" t="n">
-        <v>383.38</v>
+        <v>530.4400000000001</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>853.6900000000001</v>
+        <v>941.1900000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>-46.02</v>
+        <v>-50.73</v>
       </c>
       <c r="L42" t="n">
-        <v>854.9299999999999</v>
+        <v>942.5599999999999</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>500.68</v>
+        <v>600.05</v>
       </c>
       <c r="K43" t="n">
-        <v>-418.09</v>
+        <v>-501.06</v>
       </c>
       <c r="L43" t="n">
-        <v>652.29</v>
+        <v>781.74</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>59.51</v>
+        <v>53.06</v>
       </c>
       <c r="K44" t="n">
-        <v>101.25</v>
+        <v>90.27</v>
       </c>
       <c r="L44" t="n">
-        <v>117.45</v>
+        <v>104.71</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>53.17</v>
+        <v>69.34</v>
       </c>
       <c r="K45" t="n">
-        <v>65.92</v>
+        <v>85.97</v>
       </c>
       <c r="L45" t="n">
-        <v>84.69</v>
+        <v>110.45</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-115.92</v>
+        <v>-117.43</v>
       </c>
       <c r="K46" t="n">
-        <v>54.73</v>
+        <v>55.44</v>
       </c>
       <c r="L46" t="n">
-        <v>128.19</v>
+        <v>129.86</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-25.92</v>
+        <v>-29.57</v>
       </c>
       <c r="K47" t="n">
-        <v>201.56</v>
+        <v>229.96</v>
       </c>
       <c r="L47" t="n">
-        <v>203.22</v>
+        <v>231.85</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-137.01</v>
+        <v>-116.92</v>
       </c>
       <c r="K48" t="n">
-        <v>-153.21</v>
+        <v>-130.75</v>
       </c>
       <c r="L48" t="n">
-        <v>205.54</v>
+        <v>175.4</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>131.18</v>
+        <v>127.43</v>
       </c>
       <c r="K49" t="n">
-        <v>143.26</v>
+        <v>139.16</v>
       </c>
       <c r="L49" t="n">
-        <v>194.25</v>
+        <v>188.69</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>435.32</v>
+        <v>411.41</v>
       </c>
       <c r="K50" t="n">
-        <v>-327.54</v>
+        <v>-309.55</v>
       </c>
       <c r="L50" t="n">
-        <v>544.78</v>
+        <v>514.86</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>28</v>
       </c>
       <c r="J51" t="n">
-        <v>-174.32</v>
+        <v>-167.97</v>
       </c>
       <c r="K51" t="n">
-        <v>-174.13</v>
+        <v>-167.78</v>
       </c>
       <c r="L51" t="n">
-        <v>246.4</v>
+        <v>237.41</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>0.87</v>
+        <v>1.01</v>
       </c>
       <c r="K52" t="n">
-        <v>226.66</v>
+        <v>263.84</v>
       </c>
       <c r="L52" t="n">
-        <v>226.66</v>
+        <v>263.84</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-186.59</v>
+        <v>-230.23</v>
       </c>
       <c r="K53" t="n">
-        <v>215.77</v>
+        <v>266.23</v>
       </c>
       <c r="L53" t="n">
-        <v>285.26</v>
+        <v>351.97</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-129.26</v>
+        <v>-147.77</v>
       </c>
       <c r="K54" t="n">
-        <v>-340.29</v>
+        <v>-389.01</v>
       </c>
       <c r="L54" t="n">
-        <v>364.01</v>
+        <v>416.14</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-144.16</v>
+        <v>-147.11</v>
       </c>
       <c r="K55" t="n">
-        <v>-278.2</v>
+        <v>-283.9</v>
       </c>
       <c r="L55" t="n">
-        <v>313.33</v>
+        <v>319.75</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-169.51</v>
+        <v>-276.8</v>
       </c>
       <c r="K56" t="n">
-        <v>-278.61</v>
+        <v>-454.96</v>
       </c>
       <c r="L56" t="n">
-        <v>326.13</v>
+        <v>532.54</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-21.55</v>
+        <v>-24.17</v>
       </c>
       <c r="K57" t="n">
-        <v>-541.3</v>
+        <v>-607.13</v>
       </c>
       <c r="L57" t="n">
-        <v>541.72</v>
+        <v>607.61</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>37.22</v>
+        <v>47.78</v>
       </c>
       <c r="K58" t="n">
-        <v>432.04</v>
+        <v>554.65</v>
       </c>
       <c r="L58" t="n">
-        <v>433.64</v>
+        <v>556.7</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>203.81</v>
+        <v>183.29</v>
       </c>
       <c r="K59" t="n">
-        <v>-60.9</v>
+        <v>-54.77</v>
       </c>
       <c r="L59" t="n">
-        <v>212.71</v>
+        <v>191.3</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>43.55</v>
+        <v>49.67</v>
       </c>
       <c r="K60" t="n">
-        <v>72.09999999999999</v>
+        <v>82.23</v>
       </c>
       <c r="L60" t="n">
-        <v>84.23</v>
+        <v>96.06999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>98.25</v>
+        <v>137.84</v>
       </c>
       <c r="K61" t="n">
-        <v>8.99</v>
+        <v>12.62</v>
       </c>
       <c r="L61" t="n">
-        <v>98.66</v>
+        <v>138.42</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-48.73</v>
+        <v>-46.08</v>
       </c>
       <c r="K62" t="n">
-        <v>-225.19</v>
+        <v>-212.94</v>
       </c>
       <c r="L62" t="n">
-        <v>230.4</v>
+        <v>217.86</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>-140.88</v>
+        <v>-125.68</v>
       </c>
       <c r="K63" t="n">
-        <v>192.72</v>
+        <v>171.92</v>
       </c>
       <c r="L63" t="n">
-        <v>238.72</v>
+        <v>212.96</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>72.98</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>-36.08</v>
+        <v>-46.54</v>
       </c>
       <c r="L64" t="n">
-        <v>81.41</v>
+        <v>105.03</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-236.03</v>
+        <v>-298.97</v>
       </c>
       <c r="K65" t="n">
-        <v>63.97</v>
+        <v>81.03</v>
       </c>
       <c r="L65" t="n">
-        <v>244.54</v>
+        <v>309.76</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.71</v>
+        <v>-10.88</v>
       </c>
       <c r="K66" t="n">
-        <v>-93.69</v>
+        <v>-178.33</v>
       </c>
       <c r="L66" t="n">
-        <v>93.86</v>
+        <v>178.66</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>388.5</v>
+        <v>332.26</v>
       </c>
       <c r="K67" t="n">
-        <v>-232.81</v>
+        <v>-199.11</v>
       </c>
       <c r="L67" t="n">
-        <v>452.91</v>
+        <v>387.35</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>88.56999999999999</v>
+        <v>98.83</v>
       </c>
       <c r="K68" t="n">
-        <v>-510.32</v>
+        <v>-569.47</v>
       </c>
       <c r="L68" t="n">
-        <v>517.95</v>
+        <v>577.98</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-286.1</v>
+        <v>-305.25</v>
       </c>
       <c r="K69" t="n">
-        <v>-200.3</v>
+        <v>-213.7</v>
       </c>
       <c r="L69" t="n">
-        <v>349.25</v>
+        <v>372.62</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-402.65</v>
+        <v>-479.96</v>
       </c>
       <c r="K70" t="n">
-        <v>241.12</v>
+        <v>287.41</v>
       </c>
       <c r="L70" t="n">
-        <v>469.33</v>
+        <v>559.4299999999999</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>247.62</v>
+        <v>328.93</v>
       </c>
       <c r="K71" t="n">
-        <v>139.89</v>
+        <v>185.83</v>
       </c>
       <c r="L71" t="n">
-        <v>284.4</v>
+        <v>377.8</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>142.4</v>
+        <v>152.88</v>
       </c>
       <c r="K72" t="n">
-        <v>636.48</v>
+        <v>683.35</v>
       </c>
       <c r="L72" t="n">
-        <v>652.21</v>
+        <v>700.25</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-302.91</v>
+        <v>-346.79</v>
       </c>
       <c r="K73" t="n">
-        <v>429.66</v>
+        <v>491.91</v>
       </c>
       <c r="L73" t="n">
-        <v>525.7</v>
+        <v>601.87</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>20.4</v>
+        <v>26.39</v>
       </c>
       <c r="K74" t="n">
-        <v>-90.27</v>
+        <v>-116.77</v>
       </c>
       <c r="L74" t="n">
-        <v>92.54000000000001</v>
+        <v>119.71</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>49.62</v>
+        <v>60.16</v>
       </c>
       <c r="K75" t="n">
-        <v>-87.12</v>
+        <v>-105.62</v>
       </c>
       <c r="L75" t="n">
-        <v>100.26</v>
+        <v>121.55</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>-182.23</v>
+        <v>-191.32</v>
       </c>
       <c r="K76" t="n">
-        <v>27.96</v>
+        <v>29.35</v>
       </c>
       <c r="L76" t="n">
-        <v>184.36</v>
+        <v>193.56</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-144.22</v>
+        <v>-138.1</v>
       </c>
       <c r="K77" t="n">
-        <v>190.73</v>
+        <v>182.64</v>
       </c>
       <c r="L77" t="n">
-        <v>239.11</v>
+        <v>228.97</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-50.37</v>
+        <v>-52.15</v>
       </c>
       <c r="K78" t="n">
-        <v>168.86</v>
+        <v>174.8</v>
       </c>
       <c r="L78" t="n">
-        <v>176.22</v>
+        <v>182.41</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>5.06</v>
+        <v>4.97</v>
       </c>
       <c r="K79" t="n">
-        <v>317.77</v>
+        <v>312.56</v>
       </c>
       <c r="L79" t="n">
-        <v>317.81</v>
+        <v>312.6</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>194.15</v>
+        <v>239.06</v>
       </c>
       <c r="K80" t="n">
-        <v>258.34</v>
+        <v>318.09</v>
       </c>
       <c r="L80" t="n">
-        <v>323.16</v>
+        <v>397.91</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-76.66</v>
+        <v>-89.81</v>
       </c>
       <c r="K81" t="n">
-        <v>108.2</v>
+        <v>126.77</v>
       </c>
       <c r="L81" t="n">
-        <v>132.6</v>
+        <v>155.35</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-129.74</v>
+        <v>-120.41</v>
       </c>
       <c r="K82" t="n">
-        <v>249.89</v>
+        <v>231.91</v>
       </c>
       <c r="L82" t="n">
-        <v>281.56</v>
+        <v>261.3</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-318.61</v>
+        <v>-373.12</v>
       </c>
       <c r="K83" t="n">
-        <v>-234.11</v>
+        <v>-274.17</v>
       </c>
       <c r="L83" t="n">
-        <v>395.37</v>
+        <v>463.02</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>200.25</v>
+        <v>243.75</v>
       </c>
       <c r="K84" t="n">
-        <v>327.07</v>
+        <v>398.12</v>
       </c>
       <c r="L84" t="n">
-        <v>383.51</v>
+        <v>466.81</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>226.43</v>
+        <v>313.36</v>
       </c>
       <c r="K85" t="n">
-        <v>142.97</v>
+        <v>197.86</v>
       </c>
       <c r="L85" t="n">
-        <v>267.79</v>
+        <v>370.6</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-555.9299999999999</v>
+        <v>-613.9299999999999</v>
       </c>
       <c r="K86" t="n">
-        <v>44.38</v>
+        <v>49.01</v>
       </c>
       <c r="L86" t="n">
-        <v>557.7</v>
+        <v>615.88</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>46.13</v>
+        <v>61.32</v>
       </c>
       <c r="K87" t="n">
-        <v>-404.38</v>
+        <v>-537.49</v>
       </c>
       <c r="L87" t="n">
-        <v>407.01</v>
+        <v>540.97</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>212.71</v>
+        <v>257.6</v>
       </c>
       <c r="K88" t="n">
-        <v>-400.74</v>
+        <v>-485.33</v>
       </c>
       <c r="L88" t="n">
-        <v>453.69</v>
+        <v>549.46</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-22.xlsx
+++ b/output/2024-05-22.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-27.78</v>
+        <v>-23.18</v>
       </c>
       <c r="K14" t="n">
-        <v>101.79</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>105.51</v>
+        <v>88.03</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-24.65</v>
+        <v>-18.69</v>
       </c>
       <c r="K15" t="n">
-        <v>189.73</v>
+        <v>143.8</v>
       </c>
       <c r="L15" t="n">
-        <v>191.32</v>
+        <v>145.01</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-44.07</v>
+        <v>-38.18</v>
       </c>
       <c r="K16" t="n">
-        <v>-133.73</v>
+        <v>-115.83</v>
       </c>
       <c r="L16" t="n">
-        <v>140.81</v>
+        <v>121.96</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>93.11</v>
+        <v>79.45</v>
       </c>
       <c r="K17" t="n">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="L17" t="n">
-        <v>93.15000000000001</v>
+        <v>79.48</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>148.8</v>
+        <v>108.9</v>
       </c>
       <c r="K18" t="n">
-        <v>104.28</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>181.7</v>
+        <v>132.98</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-86.83</v>
+        <v>-76.63</v>
       </c>
       <c r="K19" t="n">
-        <v>108.35</v>
+        <v>95.63</v>
       </c>
       <c r="L19" t="n">
-        <v>138.85</v>
+        <v>122.55</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>-69.01000000000001</v>
+        <v>-54.32</v>
       </c>
       <c r="K20" t="n">
-        <v>197.11</v>
+        <v>155.14</v>
       </c>
       <c r="L20" t="n">
-        <v>208.85</v>
+        <v>164.37</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-212.52</v>
+        <v>-141.79</v>
       </c>
       <c r="K21" t="n">
-        <v>364.15</v>
+        <v>242.97</v>
       </c>
       <c r="L21" t="n">
-        <v>421.62</v>
+        <v>281.31</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-117.1</v>
+        <v>-84.73999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>260.16</v>
+        <v>188.28</v>
       </c>
       <c r="L22" t="n">
-        <v>285.3</v>
+        <v>206.47</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-302.32</v>
+        <v>-190.02</v>
       </c>
       <c r="K23" t="n">
-        <v>31.93</v>
+        <v>20.07</v>
       </c>
       <c r="L23" t="n">
-        <v>304.01</v>
+        <v>191.08</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-158.15</v>
+        <v>-93.16</v>
       </c>
       <c r="K24" t="n">
-        <v>-224.96</v>
+        <v>-132.52</v>
       </c>
       <c r="L24" t="n">
-        <v>274.99</v>
+        <v>161.99</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>296.51</v>
+        <v>178.73</v>
       </c>
       <c r="K25" t="n">
-        <v>-389.41</v>
+        <v>-234.72</v>
       </c>
       <c r="L25" t="n">
-        <v>489.45</v>
+        <v>295.02</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-462.63</v>
+        <v>-297.42</v>
       </c>
       <c r="K26" t="n">
-        <v>-743.4299999999999</v>
+        <v>-477.93</v>
       </c>
       <c r="L26" t="n">
-        <v>875.62</v>
+        <v>562.92</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>117.84</v>
+        <v>65.42</v>
       </c>
       <c r="K27" t="n">
-        <v>277.01</v>
+        <v>153.77</v>
       </c>
       <c r="L27" t="n">
-        <v>301.03</v>
+        <v>167.11</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-19.88</v>
+        <v>-10.5</v>
       </c>
       <c r="K28" t="n">
-        <v>-410.9</v>
+        <v>-217.04</v>
       </c>
       <c r="L28" t="n">
-        <v>411.38</v>
+        <v>217.29</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-138.14</v>
+        <v>-122.85</v>
       </c>
       <c r="K29" t="n">
-        <v>-21.24</v>
+        <v>-18.89</v>
       </c>
       <c r="L29" t="n">
-        <v>139.76</v>
+        <v>124.29</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-138.49</v>
+        <v>-128.6</v>
       </c>
       <c r="K30" t="n">
-        <v>-54.96</v>
+        <v>-51.04</v>
       </c>
       <c r="L30" t="n">
-        <v>149</v>
+        <v>138.36</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-107.89</v>
+        <v>-86.48</v>
       </c>
       <c r="K31" t="n">
-        <v>72.48999999999999</v>
+        <v>58.1</v>
       </c>
       <c r="L31" t="n">
-        <v>129.98</v>
+        <v>104.19</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-99.31</v>
+        <v>-84.29000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-43.23</v>
+        <v>-36.69</v>
       </c>
       <c r="L32" t="n">
-        <v>108.31</v>
+        <v>91.93000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>-78.17</v>
+        <v>-75.76000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>-49.29</v>
+        <v>-47.77</v>
       </c>
       <c r="L33" t="n">
-        <v>92.42</v>
+        <v>89.56</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>188.92</v>
+        <v>141.86</v>
       </c>
       <c r="K34" t="n">
-        <v>-12.81</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>189.35</v>
+        <v>142.18</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-32.45</v>
+        <v>-21.62</v>
       </c>
       <c r="K35" t="n">
-        <v>285.01</v>
+        <v>189.92</v>
       </c>
       <c r="L35" t="n">
-        <v>286.85</v>
+        <v>191.15</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>365.51</v>
+        <v>224.42</v>
       </c>
       <c r="K36" t="n">
-        <v>-215.73</v>
+        <v>-132.46</v>
       </c>
       <c r="L36" t="n">
-        <v>424.43</v>
+        <v>260.6</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>106.57</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>-508.3</v>
+        <v>-319.75</v>
       </c>
       <c r="L37" t="n">
-        <v>519.35</v>
+        <v>326.7</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>77.39</v>
+        <v>42.78</v>
       </c>
       <c r="K38" t="n">
-        <v>-565.3099999999999</v>
+        <v>-312.49</v>
       </c>
       <c r="L38" t="n">
-        <v>570.59</v>
+        <v>315.41</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>95.01000000000001</v>
+        <v>52.23</v>
       </c>
       <c r="K39" t="n">
-        <v>-363.83</v>
+        <v>-200</v>
       </c>
       <c r="L39" t="n">
-        <v>376.03</v>
+        <v>206.7</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>220.48</v>
+        <v>131.03</v>
       </c>
       <c r="K40" t="n">
-        <v>2.86</v>
+        <v>1.7</v>
       </c>
       <c r="L40" t="n">
-        <v>220.5</v>
+        <v>131.04</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-530</v>
+        <v>-288.91</v>
       </c>
       <c r="K41" t="n">
-        <v>21.65</v>
+        <v>11.8</v>
       </c>
       <c r="L41" t="n">
-        <v>530.4400000000001</v>
+        <v>289.15</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>941.1900000000001</v>
+        <v>483.73</v>
       </c>
       <c r="K42" t="n">
-        <v>-50.73</v>
+        <v>-26.08</v>
       </c>
       <c r="L42" t="n">
-        <v>942.5599999999999</v>
+        <v>484.43</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>600.05</v>
+        <v>307.21</v>
       </c>
       <c r="K43" t="n">
-        <v>-501.06</v>
+        <v>-256.53</v>
       </c>
       <c r="L43" t="n">
-        <v>781.74</v>
+        <v>400.23</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>53.06</v>
+        <v>50.66</v>
       </c>
       <c r="K44" t="n">
-        <v>90.27</v>
+        <v>86.19</v>
       </c>
       <c r="L44" t="n">
-        <v>104.71</v>
+        <v>99.98</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>69.34</v>
+        <v>53.76</v>
       </c>
       <c r="K45" t="n">
-        <v>85.97</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>110.45</v>
+        <v>85.63</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-117.43</v>
+        <v>-93.2</v>
       </c>
       <c r="K46" t="n">
-        <v>55.44</v>
+        <v>44</v>
       </c>
       <c r="L46" t="n">
-        <v>129.86</v>
+        <v>103.07</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-29.57</v>
+        <v>-22.06</v>
       </c>
       <c r="K47" t="n">
-        <v>229.96</v>
+        <v>171.5</v>
       </c>
       <c r="L47" t="n">
-        <v>231.85</v>
+        <v>172.91</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-116.92</v>
+        <v>-100.98</v>
       </c>
       <c r="K48" t="n">
-        <v>-130.75</v>
+        <v>-112.93</v>
       </c>
       <c r="L48" t="n">
-        <v>175.4</v>
+        <v>151.49</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>127.43</v>
+        <v>105.99</v>
       </c>
       <c r="K49" t="n">
-        <v>139.16</v>
+        <v>115.74</v>
       </c>
       <c r="L49" t="n">
-        <v>188.69</v>
+        <v>156.94</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>411.41</v>
+        <v>268.01</v>
       </c>
       <c r="K50" t="n">
-        <v>-309.55</v>
+        <v>-201.65</v>
       </c>
       <c r="L50" t="n">
-        <v>514.86</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>28</v>
       </c>
       <c r="J51" t="n">
-        <v>-167.97</v>
+        <v>-130.8</v>
       </c>
       <c r="K51" t="n">
-        <v>-167.78</v>
+        <v>-130.66</v>
       </c>
       <c r="L51" t="n">
-        <v>237.41</v>
+        <v>184.88</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>1.01</v>
+        <v>0.67</v>
       </c>
       <c r="K52" t="n">
-        <v>263.84</v>
+        <v>174.61</v>
       </c>
       <c r="L52" t="n">
-        <v>263.84</v>
+        <v>174.61</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-230.23</v>
+        <v>-139.39</v>
       </c>
       <c r="K53" t="n">
-        <v>266.23</v>
+        <v>161.19</v>
       </c>
       <c r="L53" t="n">
-        <v>351.97</v>
+        <v>213.1</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-147.77</v>
+        <v>-86.98999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>-389.01</v>
+        <v>-229</v>
       </c>
       <c r="L54" t="n">
-        <v>416.14</v>
+        <v>244.97</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-147.11</v>
+        <v>-99.08</v>
       </c>
       <c r="K55" t="n">
-        <v>-283.9</v>
+        <v>-191.2</v>
       </c>
       <c r="L55" t="n">
-        <v>319.75</v>
+        <v>215.35</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-276.8</v>
+        <v>-136.27</v>
       </c>
       <c r="K56" t="n">
-        <v>-454.96</v>
+        <v>-223.97</v>
       </c>
       <c r="L56" t="n">
-        <v>532.54</v>
+        <v>262.17</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-24.17</v>
+        <v>-14.28</v>
       </c>
       <c r="K57" t="n">
-        <v>-607.13</v>
+        <v>-358.77</v>
       </c>
       <c r="L57" t="n">
-        <v>607.61</v>
+        <v>359.05</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>47.78</v>
+        <v>24.94</v>
       </c>
       <c r="K58" t="n">
-        <v>554.65</v>
+        <v>289.59</v>
       </c>
       <c r="L58" t="n">
-        <v>556.7</v>
+        <v>290.66</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>183.29</v>
+        <v>143.29</v>
       </c>
       <c r="K59" t="n">
-        <v>-54.77</v>
+        <v>-42.81</v>
       </c>
       <c r="L59" t="n">
-        <v>191.3</v>
+        <v>149.54</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>49.67</v>
+        <v>41.19</v>
       </c>
       <c r="K60" t="n">
-        <v>82.23</v>
+        <v>68.2</v>
       </c>
       <c r="L60" t="n">
-        <v>96.06999999999999</v>
+        <v>79.67</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>137.84</v>
+        <v>100.55</v>
       </c>
       <c r="K61" t="n">
-        <v>12.62</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>138.42</v>
+        <v>100.97</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-46.08</v>
+        <v>-35.09</v>
       </c>
       <c r="K62" t="n">
-        <v>-212.94</v>
+        <v>-162.17</v>
       </c>
       <c r="L62" t="n">
-        <v>217.86</v>
+        <v>165.92</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>-125.68</v>
+        <v>-102.41</v>
       </c>
       <c r="K63" t="n">
-        <v>171.92</v>
+        <v>140.09</v>
       </c>
       <c r="L63" t="n">
-        <v>212.96</v>
+        <v>173.53</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>94.15000000000001</v>
+        <v>78.12</v>
       </c>
       <c r="K64" t="n">
-        <v>-46.54</v>
+        <v>-38.62</v>
       </c>
       <c r="L64" t="n">
-        <v>105.03</v>
+        <v>87.15000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-298.97</v>
+        <v>-186.84</v>
       </c>
       <c r="K65" t="n">
-        <v>81.03</v>
+        <v>50.64</v>
       </c>
       <c r="L65" t="n">
-        <v>309.76</v>
+        <v>193.58</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.88</v>
+        <v>-7.1</v>
       </c>
       <c r="K66" t="n">
-        <v>-178.33</v>
+        <v>-116.42</v>
       </c>
       <c r="L66" t="n">
-        <v>178.66</v>
+        <v>116.64</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>332.26</v>
+        <v>254.32</v>
       </c>
       <c r="K67" t="n">
-        <v>-199.11</v>
+        <v>-152.41</v>
       </c>
       <c r="L67" t="n">
-        <v>387.35</v>
+        <v>296.49</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>98.83</v>
+        <v>56.66</v>
       </c>
       <c r="K68" t="n">
-        <v>-569.47</v>
+        <v>-326.46</v>
       </c>
       <c r="L68" t="n">
-        <v>577.98</v>
+        <v>331.34</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-305.25</v>
+        <v>-206.65</v>
       </c>
       <c r="K69" t="n">
-        <v>-213.7</v>
+        <v>-144.68</v>
       </c>
       <c r="L69" t="n">
-        <v>372.62</v>
+        <v>252.26</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-479.96</v>
+        <v>-271.94</v>
       </c>
       <c r="K70" t="n">
-        <v>287.41</v>
+        <v>162.85</v>
       </c>
       <c r="L70" t="n">
-        <v>559.4299999999999</v>
+        <v>316.97</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>328.93</v>
+        <v>205.49</v>
       </c>
       <c r="K71" t="n">
-        <v>185.83</v>
+        <v>116.09</v>
       </c>
       <c r="L71" t="n">
-        <v>377.8</v>
+        <v>236.02</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>152.88</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>683.35</v>
+        <v>402.72</v>
       </c>
       <c r="L72" t="n">
-        <v>700.25</v>
+        <v>412.67</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-346.79</v>
+        <v>-198.55</v>
       </c>
       <c r="K73" t="n">
-        <v>491.91</v>
+        <v>281.64</v>
       </c>
       <c r="L73" t="n">
-        <v>601.87</v>
+        <v>344.59</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>26.39</v>
+        <v>21.91</v>
       </c>
       <c r="K74" t="n">
-        <v>-116.77</v>
+        <v>-96.95999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>119.71</v>
+        <v>99.41</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>60.16</v>
+        <v>51.86</v>
       </c>
       <c r="K75" t="n">
-        <v>-105.62</v>
+        <v>-91.04000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>121.55</v>
+        <v>104.78</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>-191.32</v>
+        <v>-143.89</v>
       </c>
       <c r="K76" t="n">
-        <v>29.35</v>
+        <v>22.08</v>
       </c>
       <c r="L76" t="n">
-        <v>193.56</v>
+        <v>145.57</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-138.1</v>
+        <v>-116.82</v>
       </c>
       <c r="K77" t="n">
-        <v>182.64</v>
+        <v>154.5</v>
       </c>
       <c r="L77" t="n">
-        <v>228.97</v>
+        <v>193.69</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-52.15</v>
+        <v>-38.72</v>
       </c>
       <c r="K78" t="n">
-        <v>174.8</v>
+        <v>129.8</v>
       </c>
       <c r="L78" t="n">
-        <v>182.41</v>
+        <v>135.46</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>4.97</v>
+        <v>3.97</v>
       </c>
       <c r="K79" t="n">
-        <v>312.56</v>
+        <v>249.76</v>
       </c>
       <c r="L79" t="n">
-        <v>312.6</v>
+        <v>249.8</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>239.06</v>
+        <v>142.75</v>
       </c>
       <c r="K80" t="n">
-        <v>318.09</v>
+        <v>189.94</v>
       </c>
       <c r="L80" t="n">
-        <v>397.91</v>
+        <v>237.6</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-89.81</v>
+        <v>-69.08</v>
       </c>
       <c r="K81" t="n">
-        <v>126.77</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>155.35</v>
+        <v>119.5</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-120.41</v>
+        <v>-93.63</v>
       </c>
       <c r="K82" t="n">
-        <v>231.91</v>
+        <v>180.34</v>
       </c>
       <c r="L82" t="n">
-        <v>261.3</v>
+        <v>203.19</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-373.12</v>
+        <v>-206.55</v>
       </c>
       <c r="K83" t="n">
-        <v>-274.17</v>
+        <v>-151.77</v>
       </c>
       <c r="L83" t="n">
-        <v>463.02</v>
+        <v>256.32</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>243.75</v>
+        <v>143.54</v>
       </c>
       <c r="K84" t="n">
-        <v>398.12</v>
+        <v>234.45</v>
       </c>
       <c r="L84" t="n">
-        <v>466.81</v>
+        <v>274.9</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>313.36</v>
+        <v>185</v>
       </c>
       <c r="K85" t="n">
-        <v>197.86</v>
+        <v>116.81</v>
       </c>
       <c r="L85" t="n">
-        <v>370.6</v>
+        <v>218.79</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-613.9299999999999</v>
+        <v>-363.66</v>
       </c>
       <c r="K86" t="n">
-        <v>49.01</v>
+        <v>29.03</v>
       </c>
       <c r="L86" t="n">
-        <v>615.88</v>
+        <v>364.82</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>61.32</v>
+        <v>33.52</v>
       </c>
       <c r="K87" t="n">
-        <v>-537.49</v>
+        <v>-293.81</v>
       </c>
       <c r="L87" t="n">
-        <v>540.97</v>
+        <v>295.72</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>257.6</v>
+        <v>143.13</v>
       </c>
       <c r="K88" t="n">
-        <v>-485.33</v>
+        <v>-269.66</v>
       </c>
       <c r="L88" t="n">
-        <v>549.46</v>
+        <v>305.29</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-22.xlsx
+++ b/output/2024-05-22.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-23.18</v>
+        <v>-21.25</v>
       </c>
       <c r="K14" t="n">
-        <v>84.93000000000001</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>88.03</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-18.69</v>
+        <v>-17.31</v>
       </c>
       <c r="K15" t="n">
-        <v>143.8</v>
+        <v>133.2</v>
       </c>
       <c r="L15" t="n">
-        <v>145.01</v>
+        <v>134.32</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-38.18</v>
+        <v>-34.91</v>
       </c>
       <c r="K16" t="n">
-        <v>-115.83</v>
+        <v>-105.91</v>
       </c>
       <c r="L16" t="n">
-        <v>121.96</v>
+        <v>111.51</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>79.45</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="L17" t="n">
-        <v>79.48</v>
+        <v>75.20999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>108.9</v>
+        <v>105.01</v>
       </c>
       <c r="K18" t="n">
-        <v>76.31999999999999</v>
+        <v>73.59</v>
       </c>
       <c r="L18" t="n">
-        <v>132.98</v>
+        <v>128.23</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-76.63</v>
+        <v>-72.2</v>
       </c>
       <c r="K19" t="n">
-        <v>95.63</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>122.55</v>
+        <v>115.46</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>-54.32</v>
+        <v>-52.45</v>
       </c>
       <c r="K20" t="n">
-        <v>155.14</v>
+        <v>149.83</v>
       </c>
       <c r="L20" t="n">
-        <v>164.37</v>
+        <v>158.74</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-141.79</v>
+        <v>-139.91</v>
       </c>
       <c r="K21" t="n">
-        <v>242.97</v>
+        <v>239.74</v>
       </c>
       <c r="L21" t="n">
-        <v>281.31</v>
+        <v>277.58</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-84.73999999999999</v>
+        <v>-82.76000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>188.28</v>
+        <v>183.86</v>
       </c>
       <c r="L22" t="n">
-        <v>206.47</v>
+        <v>201.63</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-190.02</v>
+        <v>-190.07</v>
       </c>
       <c r="K23" t="n">
         <v>20.07</v>
       </c>
       <c r="L23" t="n">
-        <v>191.08</v>
+        <v>191.13</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-93.16</v>
+        <v>-93.78</v>
       </c>
       <c r="K24" t="n">
-        <v>-132.52</v>
+        <v>-133.4</v>
       </c>
       <c r="L24" t="n">
-        <v>161.99</v>
+        <v>163.06</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>178.73</v>
+        <v>179.71</v>
       </c>
       <c r="K25" t="n">
-        <v>-234.72</v>
+        <v>-236.01</v>
       </c>
       <c r="L25" t="n">
-        <v>295.02</v>
+        <v>296.64</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-297.42</v>
+        <v>-299.65</v>
       </c>
       <c r="K26" t="n">
-        <v>-477.93</v>
+        <v>-481.52</v>
       </c>
       <c r="L26" t="n">
-        <v>562.92</v>
+        <v>567.14</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>65.42</v>
+        <v>67.23</v>
       </c>
       <c r="K27" t="n">
-        <v>153.77</v>
+        <v>158.03</v>
       </c>
       <c r="L27" t="n">
-        <v>167.11</v>
+        <v>171.73</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-10.5</v>
+        <v>-10.78</v>
       </c>
       <c r="K28" t="n">
-        <v>-217.04</v>
+        <v>-222.85</v>
       </c>
       <c r="L28" t="n">
-        <v>217.29</v>
+        <v>223.11</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-122.85</v>
+        <v>-112.11</v>
       </c>
       <c r="K29" t="n">
-        <v>-18.89</v>
+        <v>-17.23</v>
       </c>
       <c r="L29" t="n">
-        <v>124.29</v>
+        <v>113.42</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-128.6</v>
+        <v>-116.03</v>
       </c>
       <c r="K30" t="n">
-        <v>-51.04</v>
+        <v>-46.05</v>
       </c>
       <c r="L30" t="n">
-        <v>138.36</v>
+        <v>124.84</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-86.48</v>
+        <v>-80.16</v>
       </c>
       <c r="K31" t="n">
-        <v>58.1</v>
+        <v>53.86</v>
       </c>
       <c r="L31" t="n">
-        <v>104.19</v>
+        <v>96.58</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-84.29000000000001</v>
+        <v>-79.42</v>
       </c>
       <c r="K32" t="n">
-        <v>-36.69</v>
+        <v>-34.57</v>
       </c>
       <c r="L32" t="n">
-        <v>91.93000000000001</v>
+        <v>86.61</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>-75.76000000000001</v>
+        <v>-70.2</v>
       </c>
       <c r="K33" t="n">
-        <v>-47.77</v>
+        <v>-44.27</v>
       </c>
       <c r="L33" t="n">
-        <v>89.56</v>
+        <v>82.98999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>141.86</v>
+        <v>135.67</v>
       </c>
       <c r="K34" t="n">
-        <v>-9.619999999999999</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>142.18</v>
+        <v>135.98</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-21.62</v>
+        <v>-21.51</v>
       </c>
       <c r="K35" t="n">
-        <v>189.92</v>
+        <v>188.94</v>
       </c>
       <c r="L35" t="n">
-        <v>191.15</v>
+        <v>190.16</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>224.42</v>
+        <v>223.59</v>
       </c>
       <c r="K36" t="n">
-        <v>-132.46</v>
+        <v>-131.97</v>
       </c>
       <c r="L36" t="n">
-        <v>260.6</v>
+        <v>259.64</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>67.04000000000001</v>
+        <v>66.69</v>
       </c>
       <c r="K37" t="n">
-        <v>-319.75</v>
+        <v>-318.1</v>
       </c>
       <c r="L37" t="n">
-        <v>326.7</v>
+        <v>325.02</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>42.78</v>
+        <v>43.65</v>
       </c>
       <c r="K38" t="n">
-        <v>-312.49</v>
+        <v>-318.88</v>
       </c>
       <c r="L38" t="n">
-        <v>315.41</v>
+        <v>321.85</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>52.23</v>
+        <v>53.23</v>
       </c>
       <c r="K39" t="n">
-        <v>-200</v>
+        <v>-203.83</v>
       </c>
       <c r="L39" t="n">
-        <v>206.7</v>
+        <v>210.66</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>131.03</v>
+        <v>133.15</v>
       </c>
       <c r="K40" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="L40" t="n">
-        <v>131.04</v>
+        <v>133.16</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-288.91</v>
+        <v>-296.78</v>
       </c>
       <c r="K41" t="n">
-        <v>11.8</v>
+        <v>12.12</v>
       </c>
       <c r="L41" t="n">
-        <v>289.15</v>
+        <v>297.03</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>483.73</v>
+        <v>495.87</v>
       </c>
       <c r="K42" t="n">
-        <v>-26.08</v>
+        <v>-26.73</v>
       </c>
       <c r="L42" t="n">
-        <v>484.43</v>
+        <v>496.59</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>307.21</v>
+        <v>315.55</v>
       </c>
       <c r="K43" t="n">
-        <v>-256.53</v>
+        <v>-263.49</v>
       </c>
       <c r="L43" t="n">
-        <v>400.23</v>
+        <v>411.1</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>50.66</v>
+        <v>45.62</v>
       </c>
       <c r="K44" t="n">
-        <v>86.19</v>
+        <v>77.62</v>
       </c>
       <c r="L44" t="n">
-        <v>99.98</v>
+        <v>90.03</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>53.76</v>
+        <v>49.78</v>
       </c>
       <c r="K45" t="n">
-        <v>66.65000000000001</v>
+        <v>61.71</v>
       </c>
       <c r="L45" t="n">
-        <v>85.63</v>
+        <v>79.29000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-93.2</v>
+        <v>-86.23</v>
       </c>
       <c r="K46" t="n">
-        <v>44</v>
+        <v>40.71</v>
       </c>
       <c r="L46" t="n">
-        <v>103.07</v>
+        <v>95.34999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-22.06</v>
+        <v>-21.05</v>
       </c>
       <c r="K47" t="n">
-        <v>171.5</v>
+        <v>163.67</v>
       </c>
       <c r="L47" t="n">
-        <v>172.91</v>
+        <v>165.01</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-100.98</v>
+        <v>-96.39</v>
       </c>
       <c r="K48" t="n">
-        <v>-112.93</v>
+        <v>-107.79</v>
       </c>
       <c r="L48" t="n">
-        <v>151.49</v>
+        <v>144.6</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>105.99</v>
+        <v>99.56</v>
       </c>
       <c r="K49" t="n">
-        <v>115.74</v>
+        <v>108.73</v>
       </c>
       <c r="L49" t="n">
-        <v>156.94</v>
+        <v>147.42</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>268.01</v>
+        <v>264.45</v>
       </c>
       <c r="K50" t="n">
-        <v>-201.65</v>
+        <v>-198.98</v>
       </c>
       <c r="L50" t="n">
-        <v>335.4</v>
+        <v>330.95</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>28</v>
       </c>
       <c r="J51" t="n">
-        <v>-130.8</v>
+        <v>-126.34</v>
       </c>
       <c r="K51" t="n">
-        <v>-130.66</v>
+        <v>-126.2</v>
       </c>
       <c r="L51" t="n">
-        <v>184.88</v>
+        <v>178.57</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="K52" t="n">
-        <v>174.61</v>
+        <v>172.29</v>
       </c>
       <c r="L52" t="n">
-        <v>174.61</v>
+        <v>172.3</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-139.39</v>
+        <v>-139.51</v>
       </c>
       <c r="K53" t="n">
-        <v>161.19</v>
+        <v>161.32</v>
       </c>
       <c r="L53" t="n">
-        <v>213.1</v>
+        <v>213.28</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-86.98999999999999</v>
+        <v>-87.58</v>
       </c>
       <c r="K54" t="n">
-        <v>-229</v>
+        <v>-230.57</v>
       </c>
       <c r="L54" t="n">
-        <v>244.97</v>
+        <v>246.64</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-99.08</v>
+        <v>-98.37</v>
       </c>
       <c r="K55" t="n">
-        <v>-191.2</v>
+        <v>-189.83</v>
       </c>
       <c r="L55" t="n">
-        <v>215.35</v>
+        <v>213.8</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-136.27</v>
+        <v>-142.9</v>
       </c>
       <c r="K56" t="n">
-        <v>-223.97</v>
+        <v>-234.88</v>
       </c>
       <c r="L56" t="n">
-        <v>262.17</v>
+        <v>274.93</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-14.28</v>
+        <v>-14.42</v>
       </c>
       <c r="K57" t="n">
-        <v>-358.77</v>
+        <v>-362.25</v>
       </c>
       <c r="L57" t="n">
-        <v>359.05</v>
+        <v>362.54</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>24.94</v>
+        <v>25.57</v>
       </c>
       <c r="K58" t="n">
-        <v>289.59</v>
+        <v>296.88</v>
       </c>
       <c r="L58" t="n">
-        <v>290.66</v>
+        <v>297.98</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>143.29</v>
+        <v>131.99</v>
       </c>
       <c r="K59" t="n">
-        <v>-42.81</v>
+        <v>-39.44</v>
       </c>
       <c r="L59" t="n">
-        <v>149.54</v>
+        <v>137.76</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>41.19</v>
+        <v>37.76</v>
       </c>
       <c r="K60" t="n">
-        <v>68.2</v>
+        <v>62.52</v>
       </c>
       <c r="L60" t="n">
-        <v>79.67</v>
+        <v>73.03</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>100.55</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>9.199999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>100.97</v>
+        <v>94.83</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-35.09</v>
+        <v>-33.63</v>
       </c>
       <c r="K62" t="n">
-        <v>-162.17</v>
+        <v>-155.41</v>
       </c>
       <c r="L62" t="n">
-        <v>165.92</v>
+        <v>159.01</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>-102.41</v>
+        <v>-97.02</v>
       </c>
       <c r="K63" t="n">
-        <v>140.09</v>
+        <v>132.72</v>
       </c>
       <c r="L63" t="n">
-        <v>173.53</v>
+        <v>164.41</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>78.12</v>
+        <v>74.3</v>
       </c>
       <c r="K64" t="n">
-        <v>-38.62</v>
+        <v>-36.73</v>
       </c>
       <c r="L64" t="n">
-        <v>87.15000000000001</v>
+        <v>82.88</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-186.84</v>
+        <v>-187.18</v>
       </c>
       <c r="K65" t="n">
-        <v>50.64</v>
+        <v>50.73</v>
       </c>
       <c r="L65" t="n">
-        <v>193.58</v>
+        <v>193.93</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-7.1</v>
+        <v>-7.02</v>
       </c>
       <c r="K66" t="n">
-        <v>-116.42</v>
+        <v>-115.12</v>
       </c>
       <c r="L66" t="n">
-        <v>116.64</v>
+        <v>115.33</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>254.32</v>
+        <v>246.09</v>
       </c>
       <c r="K67" t="n">
-        <v>-152.41</v>
+        <v>-147.47</v>
       </c>
       <c r="L67" t="n">
-        <v>296.49</v>
+        <v>286.89</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>56.66</v>
+        <v>57.29</v>
       </c>
       <c r="K68" t="n">
-        <v>-326.46</v>
+        <v>-330.09</v>
       </c>
       <c r="L68" t="n">
-        <v>331.34</v>
+        <v>335.02</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-206.65</v>
+        <v>-203.92</v>
       </c>
       <c r="K69" t="n">
-        <v>-144.68</v>
+        <v>-142.77</v>
       </c>
       <c r="L69" t="n">
-        <v>252.26</v>
+        <v>248.93</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-271.94</v>
+        <v>-276.87</v>
       </c>
       <c r="K70" t="n">
-        <v>162.85</v>
+        <v>165.8</v>
       </c>
       <c r="L70" t="n">
-        <v>316.97</v>
+        <v>322.72</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>205.49</v>
+        <v>206.32</v>
       </c>
       <c r="K71" t="n">
-        <v>116.09</v>
+        <v>116.56</v>
       </c>
       <c r="L71" t="n">
-        <v>236.02</v>
+        <v>236.97</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>90.09999999999999</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>402.72</v>
+        <v>409.27</v>
       </c>
       <c r="L72" t="n">
-        <v>412.67</v>
+        <v>419.39</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-198.55</v>
+        <v>-200.54</v>
       </c>
       <c r="K73" t="n">
-        <v>281.64</v>
+        <v>284.46</v>
       </c>
       <c r="L73" t="n">
-        <v>344.59</v>
+        <v>348.04</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>21.91</v>
+        <v>20.27</v>
       </c>
       <c r="K74" t="n">
-        <v>-96.95999999999999</v>
+        <v>-89.70999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>99.41</v>
+        <v>91.97</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>51.86</v>
+        <v>47.55</v>
       </c>
       <c r="K75" t="n">
-        <v>-91.04000000000001</v>
+        <v>-83.48</v>
       </c>
       <c r="L75" t="n">
-        <v>104.78</v>
+        <v>96.06999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>-143.89</v>
+        <v>-134.47</v>
       </c>
       <c r="K76" t="n">
-        <v>22.08</v>
+        <v>20.63</v>
       </c>
       <c r="L76" t="n">
-        <v>145.57</v>
+        <v>136.04</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-116.82</v>
+        <v>-109.59</v>
       </c>
       <c r="K77" t="n">
-        <v>154.5</v>
+        <v>144.93</v>
       </c>
       <c r="L77" t="n">
-        <v>193.69</v>
+        <v>181.7</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-38.72</v>
+        <v>-37.27</v>
       </c>
       <c r="K78" t="n">
-        <v>129.8</v>
+        <v>124.93</v>
       </c>
       <c r="L78" t="n">
-        <v>135.46</v>
+        <v>130.37</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>3.97</v>
+        <v>3.71</v>
       </c>
       <c r="K79" t="n">
-        <v>249.76</v>
+        <v>232.9</v>
       </c>
       <c r="L79" t="n">
-        <v>249.8</v>
+        <v>232.93</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>142.75</v>
+        <v>142.22</v>
       </c>
       <c r="K80" t="n">
-        <v>189.94</v>
+        <v>189.24</v>
       </c>
       <c r="L80" t="n">
-        <v>237.6</v>
+        <v>236.72</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-69.08</v>
+        <v>-67.38</v>
       </c>
       <c r="K81" t="n">
-        <v>97.51000000000001</v>
+        <v>95.11</v>
       </c>
       <c r="L81" t="n">
-        <v>119.5</v>
+        <v>116.56</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-93.63</v>
+        <v>-90.83</v>
       </c>
       <c r="K82" t="n">
-        <v>180.34</v>
+        <v>174.94</v>
       </c>
       <c r="L82" t="n">
-        <v>203.19</v>
+        <v>197.11</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-206.55</v>
+        <v>-211.09</v>
       </c>
       <c r="K83" t="n">
-        <v>-151.77</v>
+        <v>-155.11</v>
       </c>
       <c r="L83" t="n">
-        <v>256.32</v>
+        <v>261.95</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>143.54</v>
+        <v>144.35</v>
       </c>
       <c r="K84" t="n">
-        <v>234.45</v>
+        <v>235.77</v>
       </c>
       <c r="L84" t="n">
-        <v>274.9</v>
+        <v>276.45</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>185</v>
+        <v>185.96</v>
       </c>
       <c r="K85" t="n">
-        <v>116.81</v>
+        <v>117.41</v>
       </c>
       <c r="L85" t="n">
-        <v>218.79</v>
+        <v>219.93</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-363.66</v>
+        <v>-369.14</v>
       </c>
       <c r="K86" t="n">
-        <v>29.03</v>
+        <v>29.47</v>
       </c>
       <c r="L86" t="n">
-        <v>364.82</v>
+        <v>370.32</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>33.52</v>
+        <v>34.17</v>
       </c>
       <c r="K87" t="n">
-        <v>-293.81</v>
+        <v>-299.5</v>
       </c>
       <c r="L87" t="n">
-        <v>295.72</v>
+        <v>301.44</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>143.13</v>
+        <v>145.12</v>
       </c>
       <c r="K88" t="n">
-        <v>-269.66</v>
+        <v>-273.41</v>
       </c>
       <c r="L88" t="n">
-        <v>305.29</v>
+        <v>309.54</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-22.xlsx
+++ b/output/2024-05-22.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-21.25</v>
+        <v>-12.34</v>
       </c>
       <c r="K14" t="n">
-        <v>77.84999999999999</v>
+        <v>45.19</v>
       </c>
       <c r="L14" t="n">
-        <v>80.7</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-17.31</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>133.2</v>
+        <v>73.98</v>
       </c>
       <c r="L15" t="n">
-        <v>134.32</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-34.91</v>
+        <v>-20.3</v>
       </c>
       <c r="K16" t="n">
-        <v>-105.91</v>
+        <v>-61.59</v>
       </c>
       <c r="L16" t="n">
-        <v>111.51</v>
+        <v>64.84999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>75.18000000000001</v>
+        <v>44.27</v>
       </c>
       <c r="K17" t="n">
-        <v>2.25</v>
+        <v>1.32</v>
       </c>
       <c r="L17" t="n">
-        <v>75.20999999999999</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>105.01</v>
+        <v>60.03</v>
       </c>
       <c r="K18" t="n">
-        <v>73.59</v>
+        <v>42.07</v>
       </c>
       <c r="L18" t="n">
-        <v>128.23</v>
+        <v>73.31</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-72.2</v>
+        <v>-45.73</v>
       </c>
       <c r="K19" t="n">
-        <v>90.09999999999999</v>
+        <v>57.06</v>
       </c>
       <c r="L19" t="n">
-        <v>115.46</v>
+        <v>73.12</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>-52.45</v>
+        <v>-28.15</v>
       </c>
       <c r="K20" t="n">
-        <v>149.83</v>
+        <v>80.42</v>
       </c>
       <c r="L20" t="n">
-        <v>158.74</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-139.91</v>
+        <v>-74.31999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>239.74</v>
+        <v>127.35</v>
       </c>
       <c r="L21" t="n">
-        <v>277.58</v>
+        <v>147.46</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-82.76000000000001</v>
+        <v>-44.7</v>
       </c>
       <c r="K22" t="n">
-        <v>183.86</v>
+        <v>99.31</v>
       </c>
       <c r="L22" t="n">
-        <v>201.63</v>
+        <v>108.9</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-190.07</v>
+        <v>-108.94</v>
       </c>
       <c r="K23" t="n">
-        <v>20.07</v>
+        <v>11.51</v>
       </c>
       <c r="L23" t="n">
-        <v>191.13</v>
+        <v>109.55</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-93.78</v>
+        <v>-55.08</v>
       </c>
       <c r="K24" t="n">
-        <v>-133.4</v>
+        <v>-78.34</v>
       </c>
       <c r="L24" t="n">
-        <v>163.06</v>
+        <v>95.77</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>179.71</v>
+        <v>101.82</v>
       </c>
       <c r="K25" t="n">
-        <v>-236.01</v>
+        <v>-133.72</v>
       </c>
       <c r="L25" t="n">
-        <v>296.64</v>
+        <v>168.07</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-299.65</v>
+        <v>-183.34</v>
       </c>
       <c r="K26" t="n">
-        <v>-481.52</v>
+        <v>-294.62</v>
       </c>
       <c r="L26" t="n">
-        <v>567.14</v>
+        <v>347.01</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>67.23</v>
+        <v>42.8</v>
       </c>
       <c r="K27" t="n">
-        <v>158.03</v>
+        <v>100.6</v>
       </c>
       <c r="L27" t="n">
-        <v>171.73</v>
+        <v>109.32</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-10.78</v>
+        <v>-6.57</v>
       </c>
       <c r="K28" t="n">
-        <v>-222.85</v>
+        <v>-135.86</v>
       </c>
       <c r="L28" t="n">
-        <v>223.11</v>
+        <v>136.02</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-112.11</v>
+        <v>-58.86</v>
       </c>
       <c r="K29" t="n">
-        <v>-17.23</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>113.42</v>
+        <v>59.56</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-116.03</v>
+        <v>-66.45999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>-46.05</v>
+        <v>-26.38</v>
       </c>
       <c r="L30" t="n">
-        <v>124.84</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-80.16</v>
+        <v>-48.2</v>
       </c>
       <c r="K31" t="n">
-        <v>53.86</v>
+        <v>32.38</v>
       </c>
       <c r="L31" t="n">
-        <v>96.58</v>
+        <v>58.07</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-79.42</v>
+        <v>-41.63</v>
       </c>
       <c r="K32" t="n">
-        <v>-34.57</v>
+        <v>-18.12</v>
       </c>
       <c r="L32" t="n">
-        <v>86.61</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>-70.2</v>
+        <v>-45.11</v>
       </c>
       <c r="K33" t="n">
-        <v>-44.27</v>
+        <v>-28.45</v>
       </c>
       <c r="L33" t="n">
-        <v>82.98999999999999</v>
+        <v>53.33</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>135.67</v>
+        <v>69.88</v>
       </c>
       <c r="K34" t="n">
-        <v>-9.199999999999999</v>
+        <v>-4.74</v>
       </c>
       <c r="L34" t="n">
-        <v>135.98</v>
+        <v>70.04000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-21.51</v>
+        <v>-12.4</v>
       </c>
       <c r="K35" t="n">
-        <v>188.94</v>
+        <v>108.93</v>
       </c>
       <c r="L35" t="n">
-        <v>190.16</v>
+        <v>109.63</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>223.59</v>
+        <v>114.45</v>
       </c>
       <c r="K36" t="n">
-        <v>-131.97</v>
+        <v>-67.55</v>
       </c>
       <c r="L36" t="n">
-        <v>259.64</v>
+        <v>132.9</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>66.69</v>
+        <v>33.84</v>
       </c>
       <c r="K37" t="n">
-        <v>-318.1</v>
+        <v>-161.39</v>
       </c>
       <c r="L37" t="n">
-        <v>325.02</v>
+        <v>164.9</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>43.65</v>
+        <v>25.74</v>
       </c>
       <c r="K38" t="n">
-        <v>-318.88</v>
+        <v>-188.06</v>
       </c>
       <c r="L38" t="n">
-        <v>321.85</v>
+        <v>189.82</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>53.23</v>
+        <v>31.05</v>
       </c>
       <c r="K39" t="n">
-        <v>-203.83</v>
+        <v>-118.89</v>
       </c>
       <c r="L39" t="n">
-        <v>210.66</v>
+        <v>122.87</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>133.15</v>
+        <v>79.55</v>
       </c>
       <c r="K40" t="n">
-        <v>1.73</v>
+        <v>1.03</v>
       </c>
       <c r="L40" t="n">
-        <v>133.16</v>
+        <v>79.56</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-296.78</v>
+        <v>-165.05</v>
       </c>
       <c r="K41" t="n">
-        <v>12.12</v>
+        <v>6.74</v>
       </c>
       <c r="L41" t="n">
-        <v>297.03</v>
+        <v>165.18</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>495.87</v>
+        <v>280.01</v>
       </c>
       <c r="K42" t="n">
-        <v>-26.73</v>
+        <v>-15.09</v>
       </c>
       <c r="L42" t="n">
-        <v>496.59</v>
+        <v>280.42</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>315.55</v>
+        <v>177.25</v>
       </c>
       <c r="K43" t="n">
-        <v>-263.49</v>
+        <v>-148.01</v>
       </c>
       <c r="L43" t="n">
-        <v>411.1</v>
+        <v>230.93</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>45.62</v>
+        <v>25.49</v>
       </c>
       <c r="K44" t="n">
-        <v>77.62</v>
+        <v>43.36</v>
       </c>
       <c r="L44" t="n">
-        <v>90.03</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>49.78</v>
+        <v>27.26</v>
       </c>
       <c r="K45" t="n">
-        <v>61.71</v>
+        <v>33.8</v>
       </c>
       <c r="L45" t="n">
-        <v>79.29000000000001</v>
+        <v>43.42</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-86.23</v>
+        <v>-48.92</v>
       </c>
       <c r="K46" t="n">
-        <v>40.71</v>
+        <v>23.09</v>
       </c>
       <c r="L46" t="n">
-        <v>95.34999999999999</v>
+        <v>54.09</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-21.05</v>
+        <v>-9.44</v>
       </c>
       <c r="K47" t="n">
-        <v>163.67</v>
+        <v>73.38</v>
       </c>
       <c r="L47" t="n">
-        <v>165.01</v>
+        <v>73.98999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-96.39</v>
+        <v>-52.94</v>
       </c>
       <c r="K48" t="n">
-        <v>-107.79</v>
+        <v>-59.21</v>
       </c>
       <c r="L48" t="n">
-        <v>144.6</v>
+        <v>79.43000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>99.56</v>
+        <v>49.12</v>
       </c>
       <c r="K49" t="n">
-        <v>108.73</v>
+        <v>53.64</v>
       </c>
       <c r="L49" t="n">
-        <v>147.42</v>
+        <v>72.73</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>264.45</v>
+        <v>134.34</v>
       </c>
       <c r="K50" t="n">
-        <v>-198.98</v>
+        <v>-101.08</v>
       </c>
       <c r="L50" t="n">
-        <v>330.95</v>
+        <v>168.11</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>28</v>
       </c>
       <c r="J51" t="n">
-        <v>-126.34</v>
+        <v>-65.91</v>
       </c>
       <c r="K51" t="n">
-        <v>-126.2</v>
+        <v>-65.84</v>
       </c>
       <c r="L51" t="n">
-        <v>178.57</v>
+        <v>93.16</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>0.66</v>
+        <v>0.34</v>
       </c>
       <c r="K52" t="n">
-        <v>172.29</v>
+        <v>89.53</v>
       </c>
       <c r="L52" t="n">
-        <v>172.3</v>
+        <v>89.53</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-139.51</v>
+        <v>-80.34</v>
       </c>
       <c r="K53" t="n">
-        <v>161.32</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>213.28</v>
+        <v>122.82</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-87.58</v>
+        <v>-51.37</v>
       </c>
       <c r="K54" t="n">
-        <v>-230.57</v>
+        <v>-135.22</v>
       </c>
       <c r="L54" t="n">
-        <v>246.64</v>
+        <v>144.65</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-98.37</v>
+        <v>-59.74</v>
       </c>
       <c r="K55" t="n">
-        <v>-189.83</v>
+        <v>-115.29</v>
       </c>
       <c r="L55" t="n">
-        <v>213.8</v>
+        <v>129.85</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-142.9</v>
+        <v>-79.47</v>
       </c>
       <c r="K56" t="n">
-        <v>-234.88</v>
+        <v>-130.62</v>
       </c>
       <c r="L56" t="n">
-        <v>274.93</v>
+        <v>152.9</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-14.42</v>
+        <v>-8.02</v>
       </c>
       <c r="K57" t="n">
-        <v>-362.25</v>
+        <v>-201.57</v>
       </c>
       <c r="L57" t="n">
-        <v>362.54</v>
+        <v>201.73</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>25.57</v>
+        <v>15.07</v>
       </c>
       <c r="K58" t="n">
-        <v>296.88</v>
+        <v>174.98</v>
       </c>
       <c r="L58" t="n">
-        <v>297.98</v>
+        <v>175.63</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>131.99</v>
+        <v>73.2</v>
       </c>
       <c r="K59" t="n">
-        <v>-39.44</v>
+        <v>-21.87</v>
       </c>
       <c r="L59" t="n">
-        <v>137.76</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>37.76</v>
+        <v>21.74</v>
       </c>
       <c r="K60" t="n">
-        <v>62.52</v>
+        <v>35.99</v>
       </c>
       <c r="L60" t="n">
-        <v>73.03</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>94.43000000000001</v>
+        <v>46.69</v>
       </c>
       <c r="K61" t="n">
-        <v>8.640000000000001</v>
+        <v>4.27</v>
       </c>
       <c r="L61" t="n">
-        <v>94.83</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-33.63</v>
+        <v>-18.03</v>
       </c>
       <c r="K62" t="n">
-        <v>-155.41</v>
+        <v>-83.33</v>
       </c>
       <c r="L62" t="n">
-        <v>159.01</v>
+        <v>85.26000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>-97.02</v>
+        <v>-50.97</v>
       </c>
       <c r="K63" t="n">
-        <v>132.72</v>
+        <v>69.73</v>
       </c>
       <c r="L63" t="n">
-        <v>164.41</v>
+        <v>86.37</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>74.3</v>
+        <v>40.95</v>
       </c>
       <c r="K64" t="n">
-        <v>-36.73</v>
+        <v>-20.24</v>
       </c>
       <c r="L64" t="n">
-        <v>82.88</v>
+        <v>45.68</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-187.18</v>
+        <v>-94.23</v>
       </c>
       <c r="K65" t="n">
-        <v>50.73</v>
+        <v>25.54</v>
       </c>
       <c r="L65" t="n">
-        <v>193.93</v>
+        <v>97.63</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-7.02</v>
+        <v>-3.58</v>
       </c>
       <c r="K66" t="n">
-        <v>-115.12</v>
+        <v>-58.62</v>
       </c>
       <c r="L66" t="n">
-        <v>115.33</v>
+        <v>58.73</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>246.09</v>
+        <v>125.01</v>
       </c>
       <c r="K67" t="n">
-        <v>-147.47</v>
+        <v>-74.91</v>
       </c>
       <c r="L67" t="n">
-        <v>286.89</v>
+        <v>145.74</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>57.29</v>
+        <v>30.78</v>
       </c>
       <c r="K68" t="n">
-        <v>-330.09</v>
+        <v>-177.37</v>
       </c>
       <c r="L68" t="n">
-        <v>335.02</v>
+        <v>180.02</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-203.92</v>
+        <v>-111.72</v>
       </c>
       <c r="K69" t="n">
-        <v>-142.77</v>
+        <v>-78.22</v>
       </c>
       <c r="L69" t="n">
-        <v>248.93</v>
+        <v>136.38</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-276.87</v>
+        <v>-141.91</v>
       </c>
       <c r="K70" t="n">
-        <v>165.8</v>
+        <v>84.98</v>
       </c>
       <c r="L70" t="n">
-        <v>322.72</v>
+        <v>165.41</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>206.32</v>
+        <v>116.51</v>
       </c>
       <c r="K71" t="n">
-        <v>116.56</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>236.97</v>
+        <v>133.82</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>91.56999999999999</v>
+        <v>50.76</v>
       </c>
       <c r="K72" t="n">
-        <v>409.27</v>
+        <v>226.88</v>
       </c>
       <c r="L72" t="n">
-        <v>419.39</v>
+        <v>232.49</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-200.54</v>
+        <v>-113.11</v>
       </c>
       <c r="K73" t="n">
-        <v>284.46</v>
+        <v>160.44</v>
       </c>
       <c r="L73" t="n">
-        <v>348.04</v>
+        <v>196.3</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>20.27</v>
+        <v>9.59</v>
       </c>
       <c r="K74" t="n">
-        <v>-89.70999999999999</v>
+        <v>-42.46</v>
       </c>
       <c r="L74" t="n">
-        <v>91.97</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>47.55</v>
+        <v>22.11</v>
       </c>
       <c r="K75" t="n">
-        <v>-83.48</v>
+        <v>-38.82</v>
       </c>
       <c r="L75" t="n">
-        <v>96.06999999999999</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>-134.47</v>
+        <v>-66.17</v>
       </c>
       <c r="K76" t="n">
-        <v>20.63</v>
+        <v>10.15</v>
       </c>
       <c r="L76" t="n">
-        <v>136.04</v>
+        <v>66.94</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-109.59</v>
+        <v>-49.29</v>
       </c>
       <c r="K77" t="n">
-        <v>144.93</v>
+        <v>65.19</v>
       </c>
       <c r="L77" t="n">
-        <v>181.7</v>
+        <v>81.73</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-37.27</v>
+        <v>-20.43</v>
       </c>
       <c r="K78" t="n">
-        <v>124.93</v>
+        <v>68.5</v>
       </c>
       <c r="L78" t="n">
-        <v>130.37</v>
+        <v>71.48</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>3.71</v>
+        <v>1.54</v>
       </c>
       <c r="K79" t="n">
-        <v>232.9</v>
+        <v>96.62</v>
       </c>
       <c r="L79" t="n">
-        <v>232.93</v>
+        <v>96.64</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>142.22</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>189.24</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>236.72</v>
+        <v>117.22</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-67.38</v>
+        <v>-38.21</v>
       </c>
       <c r="K81" t="n">
-        <v>95.11</v>
+        <v>53.93</v>
       </c>
       <c r="L81" t="n">
-        <v>116.56</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-90.83</v>
+        <v>-47.2</v>
       </c>
       <c r="K82" t="n">
-        <v>174.94</v>
+        <v>90.91</v>
       </c>
       <c r="L82" t="n">
-        <v>197.11</v>
+        <v>102.43</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-211.09</v>
+        <v>-124.85</v>
       </c>
       <c r="K83" t="n">
-        <v>-155.11</v>
+        <v>-91.73999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>261.95</v>
+        <v>154.93</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>144.35</v>
+        <v>74.73</v>
       </c>
       <c r="K84" t="n">
-        <v>235.77</v>
+        <v>122.06</v>
       </c>
       <c r="L84" t="n">
-        <v>276.45</v>
+        <v>143.12</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>185.96</v>
+        <v>97.25</v>
       </c>
       <c r="K85" t="n">
-        <v>117.41</v>
+        <v>61.41</v>
       </c>
       <c r="L85" t="n">
-        <v>219.93</v>
+        <v>115.02</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-369.14</v>
+        <v>-206.08</v>
       </c>
       <c r="K86" t="n">
-        <v>29.47</v>
+        <v>16.45</v>
       </c>
       <c r="L86" t="n">
-        <v>370.32</v>
+        <v>206.73</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>34.17</v>
+        <v>19.07</v>
       </c>
       <c r="K87" t="n">
-        <v>-299.5</v>
+        <v>-167.2</v>
       </c>
       <c r="L87" t="n">
-        <v>301.44</v>
+        <v>168.28</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>145.12</v>
+        <v>83.53</v>
       </c>
       <c r="K88" t="n">
-        <v>-273.41</v>
+        <v>-157.36</v>
       </c>
       <c r="L88" t="n">
-        <v>309.54</v>
+        <v>178.16</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-22.xlsx
+++ b/output/2024-05-22.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-12.34</v>
+        <v>-12.73</v>
       </c>
       <c r="K14" t="n">
-        <v>45.19</v>
+        <v>46.63</v>
       </c>
       <c r="L14" t="n">
-        <v>46.85</v>
+        <v>48.34</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.609999999999999</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>73.98</v>
+        <v>72.89</v>
       </c>
       <c r="L15" t="n">
-        <v>74.59999999999999</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-20.3</v>
+        <v>-20.03</v>
       </c>
       <c r="K16" t="n">
-        <v>-61.59</v>
+        <v>-60.77</v>
       </c>
       <c r="L16" t="n">
-        <v>64.84999999999999</v>
+        <v>63.98</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>44.27</v>
+        <v>47.26</v>
       </c>
       <c r="K17" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="L17" t="n">
-        <v>44.29</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>60.03</v>
+        <v>60.26</v>
       </c>
       <c r="K18" t="n">
-        <v>42.07</v>
+        <v>42.23</v>
       </c>
       <c r="L18" t="n">
-        <v>73.31</v>
+        <v>73.58</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-45.73</v>
+        <v>-45.17</v>
       </c>
       <c r="K19" t="n">
-        <v>57.06</v>
+        <v>56.37</v>
       </c>
       <c r="L19" t="n">
-        <v>73.12</v>
+        <v>72.23</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>-28.15</v>
+        <v>-28.53</v>
       </c>
       <c r="K20" t="n">
-        <v>80.42</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>85.2</v>
+        <v>86.34</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-74.31999999999999</v>
+        <v>-71.59</v>
       </c>
       <c r="K21" t="n">
-        <v>127.35</v>
+        <v>122.66</v>
       </c>
       <c r="L21" t="n">
-        <v>147.46</v>
+        <v>142.02</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-44.7</v>
+        <v>-44.16</v>
       </c>
       <c r="K22" t="n">
-        <v>99.31</v>
+        <v>98.12</v>
       </c>
       <c r="L22" t="n">
-        <v>108.9</v>
+        <v>107.6</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-108.94</v>
+        <v>-113.07</v>
       </c>
       <c r="K23" t="n">
-        <v>11.51</v>
+        <v>11.94</v>
       </c>
       <c r="L23" t="n">
-        <v>109.55</v>
+        <v>113.69</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-55.08</v>
+        <v>-58.58</v>
       </c>
       <c r="K24" t="n">
-        <v>-78.34</v>
+        <v>-83.33</v>
       </c>
       <c r="L24" t="n">
-        <v>95.77</v>
+        <v>101.86</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>101.82</v>
+        <v>100.28</v>
       </c>
       <c r="K25" t="n">
-        <v>-133.72</v>
+        <v>-131.7</v>
       </c>
       <c r="L25" t="n">
-        <v>168.07</v>
+        <v>165.53</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-183.34</v>
+        <v>-172.2</v>
       </c>
       <c r="K26" t="n">
-        <v>-294.62</v>
+        <v>-276.72</v>
       </c>
       <c r="L26" t="n">
-        <v>347.01</v>
+        <v>325.93</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>42.8</v>
+        <v>46.54</v>
       </c>
       <c r="K27" t="n">
-        <v>100.6</v>
+        <v>109.4</v>
       </c>
       <c r="L27" t="n">
-        <v>109.32</v>
+        <v>118.88</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-6.57</v>
+        <v>-6.91</v>
       </c>
       <c r="K28" t="n">
-        <v>-135.86</v>
+        <v>-142.88</v>
       </c>
       <c r="L28" t="n">
-        <v>136.02</v>
+        <v>143.04</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-58.86</v>
+        <v>-58.52</v>
       </c>
       <c r="K29" t="n">
-        <v>-9.050000000000001</v>
+        <v>-9</v>
       </c>
       <c r="L29" t="n">
-        <v>59.56</v>
+        <v>59.21</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-66.45999999999999</v>
+        <v>-64.42</v>
       </c>
       <c r="K30" t="n">
-        <v>-26.38</v>
+        <v>-25.57</v>
       </c>
       <c r="L30" t="n">
-        <v>71.5</v>
+        <v>69.31</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-48.2</v>
+        <v>-47.94</v>
       </c>
       <c r="K31" t="n">
-        <v>32.38</v>
+        <v>32.21</v>
       </c>
       <c r="L31" t="n">
-        <v>58.07</v>
+        <v>57.75</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-41.63</v>
+        <v>-44.01</v>
       </c>
       <c r="K32" t="n">
-        <v>-18.12</v>
+        <v>-19.16</v>
       </c>
       <c r="L32" t="n">
-        <v>45.4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>-45.11</v>
+        <v>-45.72</v>
       </c>
       <c r="K33" t="n">
-        <v>-28.45</v>
+        <v>-28.83</v>
       </c>
       <c r="L33" t="n">
-        <v>53.33</v>
+        <v>54.05</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>69.88</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.74</v>
+        <v>-4.73</v>
       </c>
       <c r="L34" t="n">
-        <v>70.04000000000001</v>
+        <v>69.95</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-12.4</v>
+        <v>-12.22</v>
       </c>
       <c r="K35" t="n">
-        <v>108.93</v>
+        <v>107.33</v>
       </c>
       <c r="L35" t="n">
-        <v>109.63</v>
+        <v>108.02</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>114.45</v>
+        <v>111.38</v>
       </c>
       <c r="K36" t="n">
-        <v>-67.55</v>
+        <v>-65.73999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>132.9</v>
+        <v>129.34</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>33.84</v>
+        <v>32.26</v>
       </c>
       <c r="K37" t="n">
-        <v>-161.39</v>
+        <v>-153.87</v>
       </c>
       <c r="L37" t="n">
-        <v>164.9</v>
+        <v>157.22</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>25.74</v>
+        <v>24.97</v>
       </c>
       <c r="K38" t="n">
-        <v>-188.06</v>
+        <v>-182.39</v>
       </c>
       <c r="L38" t="n">
-        <v>189.82</v>
+        <v>184.1</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>31.05</v>
+        <v>31.73</v>
       </c>
       <c r="K39" t="n">
-        <v>-118.89</v>
+        <v>-121.51</v>
       </c>
       <c r="L39" t="n">
-        <v>122.87</v>
+        <v>125.58</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>79.55</v>
+        <v>86.53</v>
       </c>
       <c r="K40" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="L40" t="n">
-        <v>79.56</v>
+        <v>86.54000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-165.05</v>
+        <v>-171.75</v>
       </c>
       <c r="K41" t="n">
-        <v>6.74</v>
+        <v>7.01</v>
       </c>
       <c r="L41" t="n">
-        <v>165.18</v>
+        <v>171.89</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>280.01</v>
+        <v>270.15</v>
       </c>
       <c r="K42" t="n">
-        <v>-15.09</v>
+        <v>-14.56</v>
       </c>
       <c r="L42" t="n">
-        <v>280.42</v>
+        <v>270.55</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>177.25</v>
+        <v>175.39</v>
       </c>
       <c r="K43" t="n">
-        <v>-148.01</v>
+        <v>-146.46</v>
       </c>
       <c r="L43" t="n">
-        <v>230.93</v>
+        <v>228.5</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>25.49</v>
+        <v>25.65</v>
       </c>
       <c r="K44" t="n">
-        <v>43.36</v>
+        <v>43.64</v>
       </c>
       <c r="L44" t="n">
-        <v>50.3</v>
+        <v>50.62</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>27.26</v>
+        <v>28.59</v>
       </c>
       <c r="K45" t="n">
-        <v>33.8</v>
+        <v>35.45</v>
       </c>
       <c r="L45" t="n">
-        <v>43.42</v>
+        <v>45.54</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-48.92</v>
+        <v>-49.28</v>
       </c>
       <c r="K46" t="n">
-        <v>23.09</v>
+        <v>23.27</v>
       </c>
       <c r="L46" t="n">
-        <v>54.09</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-9.44</v>
+        <v>-9.19</v>
       </c>
       <c r="K47" t="n">
-        <v>73.38</v>
+        <v>71.45</v>
       </c>
       <c r="L47" t="n">
-        <v>73.98999999999999</v>
+        <v>72.04000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-52.94</v>
+        <v>-51.78</v>
       </c>
       <c r="K48" t="n">
-        <v>-59.21</v>
+        <v>-57.91</v>
       </c>
       <c r="L48" t="n">
-        <v>79.43000000000001</v>
+        <v>77.68000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>49.12</v>
+        <v>48.08</v>
       </c>
       <c r="K49" t="n">
-        <v>53.64</v>
+        <v>52.51</v>
       </c>
       <c r="L49" t="n">
-        <v>72.73</v>
+        <v>71.19</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>134.34</v>
+        <v>127.31</v>
       </c>
       <c r="K50" t="n">
-        <v>-101.08</v>
+        <v>-95.79000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>168.11</v>
+        <v>159.32</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>28</v>
       </c>
       <c r="J51" t="n">
-        <v>-65.91</v>
+        <v>-65.45999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-65.84</v>
+        <v>-65.39</v>
       </c>
       <c r="L51" t="n">
-        <v>93.16</v>
+        <v>92.52</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="K52" t="n">
-        <v>89.53</v>
+        <v>90.3</v>
       </c>
       <c r="L52" t="n">
-        <v>89.53</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-80.34</v>
+        <v>-81.19</v>
       </c>
       <c r="K53" t="n">
-        <v>92.90000000000001</v>
+        <v>93.88</v>
       </c>
       <c r="L53" t="n">
-        <v>122.82</v>
+        <v>124.12</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-51.37</v>
+        <v>-50.89</v>
       </c>
       <c r="K54" t="n">
-        <v>-135.22</v>
+        <v>-133.97</v>
       </c>
       <c r="L54" t="n">
-        <v>144.65</v>
+        <v>143.31</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-59.74</v>
+        <v>-59.24</v>
       </c>
       <c r="K55" t="n">
-        <v>-115.29</v>
+        <v>-114.32</v>
       </c>
       <c r="L55" t="n">
-        <v>129.85</v>
+        <v>128.76</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-79.47</v>
+        <v>-84.06</v>
       </c>
       <c r="K56" t="n">
-        <v>-130.62</v>
+        <v>-138.16</v>
       </c>
       <c r="L56" t="n">
-        <v>152.9</v>
+        <v>161.72</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-8.02</v>
+        <v>-8.06</v>
       </c>
       <c r="K57" t="n">
-        <v>-201.57</v>
+        <v>-202.4</v>
       </c>
       <c r="L57" t="n">
-        <v>201.73</v>
+        <v>202.56</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>15.07</v>
+        <v>15.12</v>
       </c>
       <c r="K58" t="n">
-        <v>174.98</v>
+        <v>175.49</v>
       </c>
       <c r="L58" t="n">
-        <v>175.63</v>
+        <v>176.14</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>73.2</v>
+        <v>71.33</v>
       </c>
       <c r="K59" t="n">
-        <v>-21.87</v>
+        <v>-21.31</v>
       </c>
       <c r="L59" t="n">
-        <v>76.40000000000001</v>
+        <v>74.45</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>21.74</v>
+        <v>22.62</v>
       </c>
       <c r="K60" t="n">
-        <v>35.99</v>
+        <v>37.46</v>
       </c>
       <c r="L60" t="n">
-        <v>42.04</v>
+        <v>43.76</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>46.69</v>
+        <v>48.39</v>
       </c>
       <c r="K61" t="n">
-        <v>4.27</v>
+        <v>4.43</v>
       </c>
       <c r="L61" t="n">
-        <v>46.88</v>
+        <v>48.59</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-18.03</v>
+        <v>-17.65</v>
       </c>
       <c r="K62" t="n">
-        <v>-83.33</v>
+        <v>-81.55</v>
       </c>
       <c r="L62" t="n">
-        <v>85.26000000000001</v>
+        <v>83.44</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>-50.97</v>
+        <v>-49.51</v>
       </c>
       <c r="K63" t="n">
-        <v>69.73</v>
+        <v>67.73</v>
       </c>
       <c r="L63" t="n">
-        <v>86.37</v>
+        <v>83.89</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>40.95</v>
+        <v>43.33</v>
       </c>
       <c r="K64" t="n">
-        <v>-20.24</v>
+        <v>-21.42</v>
       </c>
       <c r="L64" t="n">
-        <v>45.68</v>
+        <v>48.34</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-94.23</v>
+        <v>-95.06</v>
       </c>
       <c r="K65" t="n">
-        <v>25.54</v>
+        <v>25.76</v>
       </c>
       <c r="L65" t="n">
-        <v>97.63</v>
+        <v>98.48999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.58</v>
+        <v>-3.89</v>
       </c>
       <c r="K66" t="n">
-        <v>-58.62</v>
+        <v>-63.77</v>
       </c>
       <c r="L66" t="n">
-        <v>58.73</v>
+        <v>63.89</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>125.01</v>
+        <v>119.26</v>
       </c>
       <c r="K67" t="n">
-        <v>-74.91</v>
+        <v>-71.47</v>
       </c>
       <c r="L67" t="n">
-        <v>145.74</v>
+        <v>139.04</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>30.78</v>
+        <v>30.07</v>
       </c>
       <c r="K68" t="n">
-        <v>-177.37</v>
+        <v>-173.27</v>
       </c>
       <c r="L68" t="n">
-        <v>180.02</v>
+        <v>175.86</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-111.72</v>
+        <v>-111.28</v>
       </c>
       <c r="K69" t="n">
-        <v>-78.22</v>
+        <v>-77.91</v>
       </c>
       <c r="L69" t="n">
-        <v>136.38</v>
+        <v>135.84</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-141.91</v>
+        <v>-140.42</v>
       </c>
       <c r="K70" t="n">
-        <v>84.98</v>
+        <v>84.09</v>
       </c>
       <c r="L70" t="n">
-        <v>165.41</v>
+        <v>163.67</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>116.51</v>
+        <v>121.03</v>
       </c>
       <c r="K71" t="n">
-        <v>65.81999999999999</v>
+        <v>68.37</v>
       </c>
       <c r="L71" t="n">
-        <v>133.82</v>
+        <v>139</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>50.76</v>
+        <v>50.61</v>
       </c>
       <c r="K72" t="n">
-        <v>226.88</v>
+        <v>226.2</v>
       </c>
       <c r="L72" t="n">
-        <v>232.49</v>
+        <v>231.79</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-113.11</v>
+        <v>-112.44</v>
       </c>
       <c r="K73" t="n">
-        <v>160.44</v>
+        <v>159.49</v>
       </c>
       <c r="L73" t="n">
-        <v>196.3</v>
+        <v>195.14</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>9.59</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-42.46</v>
+        <v>-43.7</v>
       </c>
       <c r="L74" t="n">
-        <v>43.53</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>22.11</v>
+        <v>22.54</v>
       </c>
       <c r="K75" t="n">
-        <v>-38.82</v>
+        <v>-39.57</v>
       </c>
       <c r="L75" t="n">
-        <v>44.68</v>
+        <v>45.54</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>-66.17</v>
+        <v>-64.90000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>10.15</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>66.94</v>
+        <v>65.66</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-49.29</v>
+        <v>-47.13</v>
       </c>
       <c r="K77" t="n">
-        <v>65.19</v>
+        <v>62.34</v>
       </c>
       <c r="L77" t="n">
-        <v>81.73</v>
+        <v>78.15000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-20.43</v>
+        <v>-20.4</v>
       </c>
       <c r="K78" t="n">
-        <v>68.5</v>
+        <v>68.38</v>
       </c>
       <c r="L78" t="n">
-        <v>71.48</v>
+        <v>71.34999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="K79" t="n">
-        <v>96.62</v>
+        <v>89.75</v>
       </c>
       <c r="L79" t="n">
-        <v>96.64</v>
+        <v>89.76000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>70.43000000000001</v>
+        <v>69.58</v>
       </c>
       <c r="K80" t="n">
-        <v>93.70999999999999</v>
+        <v>92.58</v>
       </c>
       <c r="L80" t="n">
-        <v>117.22</v>
+        <v>115.81</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-38.21</v>
+        <v>-39.72</v>
       </c>
       <c r="K81" t="n">
-        <v>53.93</v>
+        <v>56.07</v>
       </c>
       <c r="L81" t="n">
-        <v>66.09999999999999</v>
+        <v>68.70999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-47.2</v>
+        <v>-46.45</v>
       </c>
       <c r="K82" t="n">
-        <v>90.91</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>102.43</v>
+        <v>100.8</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-124.85</v>
+        <v>-123.3</v>
       </c>
       <c r="K83" t="n">
-        <v>-91.73999999999999</v>
+        <v>-90.59999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>154.93</v>
+        <v>153.01</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>74.73</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>122.06</v>
+        <v>122.1</v>
       </c>
       <c r="L84" t="n">
-        <v>143.12</v>
+        <v>143.17</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>97.25</v>
+        <v>100.04</v>
       </c>
       <c r="K85" t="n">
-        <v>61.41</v>
+        <v>63.16</v>
       </c>
       <c r="L85" t="n">
-        <v>115.02</v>
+        <v>118.31</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-206.08</v>
+        <v>-205.78</v>
       </c>
       <c r="K86" t="n">
-        <v>16.45</v>
+        <v>16.43</v>
       </c>
       <c r="L86" t="n">
-        <v>206.73</v>
+        <v>206.44</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>19.07</v>
+        <v>19.61</v>
       </c>
       <c r="K87" t="n">
-        <v>-167.2</v>
+        <v>-171.86</v>
       </c>
       <c r="L87" t="n">
-        <v>168.28</v>
+        <v>172.98</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>83.53</v>
+        <v>83.37</v>
       </c>
       <c r="K88" t="n">
-        <v>-157.36</v>
+        <v>-157.08</v>
       </c>
       <c r="L88" t="n">
-        <v>178.16</v>
+        <v>177.83</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-22.xlsx
+++ b/output/2024-05-22.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-12.73</v>
+        <v>-13.18</v>
       </c>
       <c r="K14" t="n">
-        <v>46.63</v>
+        <v>48.28</v>
       </c>
       <c r="L14" t="n">
-        <v>48.34</v>
+        <v>50.04</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.470000000000001</v>
+        <v>-9.31</v>
       </c>
       <c r="K15" t="n">
-        <v>72.89</v>
+        <v>71.63</v>
       </c>
       <c r="L15" t="n">
-        <v>73.5</v>
+        <v>72.23999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-20.03</v>
+        <v>-19.72</v>
       </c>
       <c r="K16" t="n">
-        <v>-60.77</v>
+        <v>-59.83</v>
       </c>
       <c r="L16" t="n">
-        <v>63.98</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>47.26</v>
+        <v>50.68</v>
       </c>
       <c r="K17" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="L17" t="n">
-        <v>47.28</v>
+        <v>50.71</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>60.26</v>
+        <v>60.52</v>
       </c>
       <c r="K18" t="n">
-        <v>42.23</v>
+        <v>42.41</v>
       </c>
       <c r="L18" t="n">
-        <v>73.58</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-45.17</v>
+        <v>-44.54</v>
       </c>
       <c r="K19" t="n">
-        <v>56.37</v>
+        <v>55.58</v>
       </c>
       <c r="L19" t="n">
-        <v>72.23</v>
+        <v>71.22</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>-28.53</v>
+        <v>-28.96</v>
       </c>
       <c r="K20" t="n">
-        <v>81.48999999999999</v>
+        <v>82.73</v>
       </c>
       <c r="L20" t="n">
-        <v>86.34</v>
+        <v>87.65000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-71.59</v>
+        <v>-68.45999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>122.66</v>
+        <v>117.3</v>
       </c>
       <c r="L21" t="n">
-        <v>142.02</v>
+        <v>135.82</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-44.16</v>
+        <v>-43.55</v>
       </c>
       <c r="K22" t="n">
-        <v>98.12</v>
+        <v>96.77</v>
       </c>
       <c r="L22" t="n">
-        <v>107.6</v>
+        <v>106.12</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-113.07</v>
+        <v>-117.74</v>
       </c>
       <c r="K23" t="n">
-        <v>11.94</v>
+        <v>12.43</v>
       </c>
       <c r="L23" t="n">
-        <v>113.69</v>
+        <v>118.4</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-58.58</v>
+        <v>-62.58</v>
       </c>
       <c r="K24" t="n">
-        <v>-83.33</v>
+        <v>-89.02</v>
       </c>
       <c r="L24" t="n">
-        <v>101.86</v>
+        <v>108.82</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>100.28</v>
+        <v>98.44</v>
       </c>
       <c r="K25" t="n">
-        <v>-131.7</v>
+        <v>-129.29</v>
       </c>
       <c r="L25" t="n">
-        <v>165.53</v>
+        <v>162.5</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-172.2</v>
+        <v>-159.47</v>
       </c>
       <c r="K26" t="n">
-        <v>-276.72</v>
+        <v>-256.27</v>
       </c>
       <c r="L26" t="n">
-        <v>325.93</v>
+        <v>301.83</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>46.54</v>
+        <v>50.81</v>
       </c>
       <c r="K27" t="n">
-        <v>109.4</v>
+        <v>119.45</v>
       </c>
       <c r="L27" t="n">
-        <v>118.88</v>
+        <v>129.81</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-6.91</v>
+        <v>-7.3</v>
       </c>
       <c r="K28" t="n">
-        <v>-142.88</v>
+        <v>-150.9</v>
       </c>
       <c r="L28" t="n">
-        <v>143.04</v>
+        <v>151.08</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-58.52</v>
+        <v>-58.42</v>
       </c>
       <c r="K29" t="n">
-        <v>-9</v>
+        <v>-8.98</v>
       </c>
       <c r="L29" t="n">
-        <v>59.21</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-64.42</v>
+        <v>-62.08</v>
       </c>
       <c r="K30" t="n">
-        <v>-25.57</v>
+        <v>-24.64</v>
       </c>
       <c r="L30" t="n">
-        <v>69.31</v>
+        <v>66.79000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-47.94</v>
+        <v>-47.65</v>
       </c>
       <c r="K31" t="n">
-        <v>32.21</v>
+        <v>32.01</v>
       </c>
       <c r="L31" t="n">
-        <v>57.75</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-44.01</v>
+        <v>-46.93</v>
       </c>
       <c r="K32" t="n">
-        <v>-19.16</v>
+        <v>-20.43</v>
       </c>
       <c r="L32" t="n">
-        <v>48</v>
+        <v>51.18</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>-45.72</v>
+        <v>-46.4</v>
       </c>
       <c r="K33" t="n">
-        <v>-28.83</v>
+        <v>-29.26</v>
       </c>
       <c r="L33" t="n">
-        <v>54.05</v>
+        <v>54.86</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>69.79000000000001</v>
+        <v>70.19</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.73</v>
+        <v>-4.76</v>
       </c>
       <c r="L34" t="n">
-        <v>69.95</v>
+        <v>70.34999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-12.22</v>
+        <v>-12.01</v>
       </c>
       <c r="K35" t="n">
-        <v>107.33</v>
+        <v>105.5</v>
       </c>
       <c r="L35" t="n">
-        <v>108.02</v>
+        <v>106.18</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>111.38</v>
+        <v>108.05</v>
       </c>
       <c r="K36" t="n">
-        <v>-65.73999999999999</v>
+        <v>-63.77</v>
       </c>
       <c r="L36" t="n">
-        <v>129.34</v>
+        <v>125.46</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>32.26</v>
+        <v>30.57</v>
       </c>
       <c r="K37" t="n">
-        <v>-153.87</v>
+        <v>-145.8</v>
       </c>
       <c r="L37" t="n">
-        <v>157.22</v>
+        <v>148.97</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>24.97</v>
+        <v>24.08</v>
       </c>
       <c r="K38" t="n">
-        <v>-182.39</v>
+        <v>-175.92</v>
       </c>
       <c r="L38" t="n">
-        <v>184.1</v>
+        <v>177.56</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>31.73</v>
+        <v>32.51</v>
       </c>
       <c r="K39" t="n">
-        <v>-121.51</v>
+        <v>-124.5</v>
       </c>
       <c r="L39" t="n">
-        <v>125.58</v>
+        <v>128.68</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>86.53</v>
+        <v>94.52</v>
       </c>
       <c r="K40" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="L40" t="n">
-        <v>86.54000000000001</v>
+        <v>94.52</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-171.75</v>
+        <v>-176.07</v>
       </c>
       <c r="K41" t="n">
-        <v>7.01</v>
+        <v>7.19</v>
       </c>
       <c r="L41" t="n">
-        <v>171.89</v>
+        <v>176.22</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>270.15</v>
+        <v>257.66</v>
       </c>
       <c r="K42" t="n">
-        <v>-14.56</v>
+        <v>-13.89</v>
       </c>
       <c r="L42" t="n">
-        <v>270.55</v>
+        <v>258.03</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>175.39</v>
+        <v>171.51</v>
       </c>
       <c r="K43" t="n">
-        <v>-146.46</v>
+        <v>-143.22</v>
       </c>
       <c r="L43" t="n">
-        <v>228.5</v>
+        <v>223.44</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>25.65</v>
+        <v>25.84</v>
       </c>
       <c r="K44" t="n">
-        <v>43.64</v>
+        <v>43.97</v>
       </c>
       <c r="L44" t="n">
-        <v>50.62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>28.59</v>
+        <v>30.12</v>
       </c>
       <c r="K45" t="n">
-        <v>35.45</v>
+        <v>37.34</v>
       </c>
       <c r="L45" t="n">
-        <v>45.54</v>
+        <v>47.97</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-49.28</v>
+        <v>-49.7</v>
       </c>
       <c r="K46" t="n">
-        <v>23.27</v>
+        <v>23.46</v>
       </c>
       <c r="L46" t="n">
-        <v>54.5</v>
+        <v>54.96</v>
       </c>
     </row>
     <row r="47">
@@ -2029,10 +2029,10 @@
         <v>-9.19</v>
       </c>
       <c r="K47" t="n">
-        <v>71.45</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>72.04000000000001</v>
+        <v>72.08</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-51.78</v>
+        <v>-50.45</v>
       </c>
       <c r="K48" t="n">
-        <v>-57.91</v>
+        <v>-56.42</v>
       </c>
       <c r="L48" t="n">
-        <v>77.68000000000001</v>
+        <v>75.69</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>48.08</v>
+        <v>47.59</v>
       </c>
       <c r="K49" t="n">
-        <v>52.51</v>
+        <v>51.97</v>
       </c>
       <c r="L49" t="n">
-        <v>71.19</v>
+        <v>70.47</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>127.31</v>
+        <v>119.68</v>
       </c>
       <c r="K50" t="n">
-        <v>-95.79000000000001</v>
+        <v>-90.05</v>
       </c>
       <c r="L50" t="n">
-        <v>159.32</v>
+        <v>149.77</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>28</v>
       </c>
       <c r="J51" t="n">
-        <v>-65.45999999999999</v>
+        <v>-64.95</v>
       </c>
       <c r="K51" t="n">
-        <v>-65.39</v>
+        <v>-64.88</v>
       </c>
       <c r="L51" t="n">
-        <v>92.52</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="52">
@@ -2239,10 +2239,10 @@
         <v>0.35</v>
       </c>
       <c r="K52" t="n">
-        <v>90.3</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>90.3</v>
+        <v>91.18000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-81.19</v>
+        <v>-82.15000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>93.88</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>124.12</v>
+        <v>125.58</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-50.89</v>
+        <v>-50.34</v>
       </c>
       <c r="K54" t="n">
-        <v>-133.97</v>
+        <v>-132.53</v>
       </c>
       <c r="L54" t="n">
-        <v>143.31</v>
+        <v>141.77</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-59.24</v>
+        <v>-58.67</v>
       </c>
       <c r="K55" t="n">
-        <v>-114.32</v>
+        <v>-113.22</v>
       </c>
       <c r="L55" t="n">
-        <v>128.76</v>
+        <v>127.51</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-84.06</v>
+        <v>-87.69</v>
       </c>
       <c r="K56" t="n">
-        <v>-138.16</v>
+        <v>-144.14</v>
       </c>
       <c r="L56" t="n">
-        <v>161.72</v>
+        <v>168.72</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-8.06</v>
+        <v>-7.94</v>
       </c>
       <c r="K57" t="n">
-        <v>-202.4</v>
+        <v>-199.37</v>
       </c>
       <c r="L57" t="n">
-        <v>202.56</v>
+        <v>199.52</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>15.12</v>
+        <v>15.17</v>
       </c>
       <c r="K58" t="n">
-        <v>175.49</v>
+        <v>176.06</v>
       </c>
       <c r="L58" t="n">
-        <v>176.14</v>
+        <v>176.71</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>71.33</v>
+        <v>69.19</v>
       </c>
       <c r="K59" t="n">
-        <v>-21.31</v>
+        <v>-20.67</v>
       </c>
       <c r="L59" t="n">
-        <v>74.45</v>
+        <v>72.22</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>22.62</v>
+        <v>23.64</v>
       </c>
       <c r="K60" t="n">
-        <v>37.46</v>
+        <v>39.14</v>
       </c>
       <c r="L60" t="n">
-        <v>43.76</v>
+        <v>45.73</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>48.39</v>
+        <v>50.92</v>
       </c>
       <c r="K61" t="n">
-        <v>4.43</v>
+        <v>4.66</v>
       </c>
       <c r="L61" t="n">
-        <v>48.59</v>
+        <v>51.13</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-17.65</v>
+        <v>-17.23</v>
       </c>
       <c r="K62" t="n">
-        <v>-81.55</v>
+        <v>-79.61</v>
       </c>
       <c r="L62" t="n">
-        <v>83.44</v>
+        <v>81.45</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>-49.51</v>
+        <v>-48.05</v>
       </c>
       <c r="K63" t="n">
-        <v>67.73</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>83.89</v>
+        <v>81.43000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>43.33</v>
+        <v>46.06</v>
       </c>
       <c r="K64" t="n">
-        <v>-21.42</v>
+        <v>-22.77</v>
       </c>
       <c r="L64" t="n">
-        <v>48.34</v>
+        <v>51.38</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-95.06</v>
+        <v>-96.45999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>25.76</v>
+        <v>26.14</v>
       </c>
       <c r="L65" t="n">
-        <v>98.48999999999999</v>
+        <v>99.94</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.89</v>
+        <v>-4.26</v>
       </c>
       <c r="K66" t="n">
-        <v>-63.77</v>
+        <v>-69.79000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>63.89</v>
+        <v>69.92</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>119.26</v>
+        <v>113.07</v>
       </c>
       <c r="K67" t="n">
-        <v>-71.47</v>
+        <v>-67.76000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>139.04</v>
+        <v>131.82</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>30.07</v>
+        <v>29.17</v>
       </c>
       <c r="K68" t="n">
-        <v>-173.27</v>
+        <v>-168.09</v>
       </c>
       <c r="L68" t="n">
-        <v>175.86</v>
+        <v>170.6</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-111.28</v>
+        <v>-110.55</v>
       </c>
       <c r="K69" t="n">
-        <v>-77.91</v>
+        <v>-77.40000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>135.84</v>
+        <v>134.95</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-140.42</v>
+        <v>-138.06</v>
       </c>
       <c r="K70" t="n">
-        <v>84.09</v>
+        <v>82.67</v>
       </c>
       <c r="L70" t="n">
-        <v>163.67</v>
+        <v>160.92</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>121.03</v>
+        <v>125.69</v>
       </c>
       <c r="K71" t="n">
-        <v>68.37</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>139</v>
+        <v>144.36</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>50.61</v>
+        <v>49.23</v>
       </c>
       <c r="K72" t="n">
-        <v>226.2</v>
+        <v>220.02</v>
       </c>
       <c r="L72" t="n">
-        <v>231.79</v>
+        <v>225.46</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-112.44</v>
+        <v>-111.05</v>
       </c>
       <c r="K73" t="n">
-        <v>159.49</v>
+        <v>157.51</v>
       </c>
       <c r="L73" t="n">
-        <v>195.14</v>
+        <v>192.72</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>9.880000000000001</v>
+        <v>10.38</v>
       </c>
       <c r="K74" t="n">
-        <v>-43.7</v>
+        <v>-45.92</v>
       </c>
       <c r="L74" t="n">
-        <v>44.8</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>22.54</v>
+        <v>23.49</v>
       </c>
       <c r="K75" t="n">
-        <v>-39.57</v>
+        <v>-41.25</v>
       </c>
       <c r="L75" t="n">
-        <v>45.54</v>
+        <v>47.47</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>-64.90000000000001</v>
+        <v>-64.34</v>
       </c>
       <c r="K76" t="n">
-        <v>9.960000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>65.66</v>
+        <v>65.09</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-47.13</v>
+        <v>-46.16</v>
       </c>
       <c r="K77" t="n">
-        <v>62.34</v>
+        <v>61.05</v>
       </c>
       <c r="L77" t="n">
-        <v>78.15000000000001</v>
+        <v>76.53</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-20.4</v>
+        <v>-20.36</v>
       </c>
       <c r="K78" t="n">
-        <v>68.38</v>
+        <v>68.23</v>
       </c>
       <c r="L78" t="n">
-        <v>71.34999999999999</v>
+        <v>71.20999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="K79" t="n">
-        <v>89.75</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>89.76000000000001</v>
+        <v>86.72</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>69.58</v>
+        <v>69.19</v>
       </c>
       <c r="K80" t="n">
-        <v>92.58</v>
+        <v>92.06</v>
       </c>
       <c r="L80" t="n">
-        <v>115.81</v>
+        <v>115.16</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-39.72</v>
+        <v>-41.45</v>
       </c>
       <c r="K81" t="n">
-        <v>56.07</v>
+        <v>58.51</v>
       </c>
       <c r="L81" t="n">
-        <v>68.70999999999999</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-46.45</v>
+        <v>-45.59</v>
       </c>
       <c r="K82" t="n">
-        <v>89.45999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="L82" t="n">
-        <v>100.8</v>
+        <v>98.93000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-123.3</v>
+        <v>-121.54</v>
       </c>
       <c r="K83" t="n">
-        <v>-90.59999999999999</v>
+        <v>-89.31</v>
       </c>
       <c r="L83" t="n">
-        <v>153.01</v>
+        <v>150.82</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>74.76000000000001</v>
+        <v>74.47</v>
       </c>
       <c r="K84" t="n">
-        <v>122.1</v>
+        <v>121.63</v>
       </c>
       <c r="L84" t="n">
-        <v>143.17</v>
+        <v>142.62</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>100.04</v>
+        <v>102.85</v>
       </c>
       <c r="K85" t="n">
-        <v>63.16</v>
+        <v>64.94</v>
       </c>
       <c r="L85" t="n">
-        <v>118.31</v>
+        <v>121.64</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-205.78</v>
+        <v>-202.08</v>
       </c>
       <c r="K86" t="n">
-        <v>16.43</v>
+        <v>16.13</v>
       </c>
       <c r="L86" t="n">
-        <v>206.44</v>
+        <v>202.72</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>19.61</v>
+        <v>19.9</v>
       </c>
       <c r="K87" t="n">
-        <v>-171.86</v>
+        <v>-174.47</v>
       </c>
       <c r="L87" t="n">
-        <v>172.98</v>
+        <v>175.61</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>83.37</v>
+        <v>83.2</v>
       </c>
       <c r="K88" t="n">
-        <v>-157.08</v>
+        <v>-156.75</v>
       </c>
       <c r="L88" t="n">
-        <v>177.83</v>
+        <v>177.46</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-22.xlsx
+++ b/output/2024-05-22.xlsx
@@ -628,31 +628,31 @@
         <v>2.84</v>
       </c>
       <c r="F14" t="n">
-        <v>10.24</v>
+        <v>5.15</v>
       </c>
       <c r="G14" t="n">
-        <v>44</v>
+        <v>57.5</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>-13.18</v>
+        <v>40.28</v>
       </c>
       <c r="K14" t="n">
-        <v>48.28</v>
+        <v>25.07</v>
       </c>
       <c r="L14" t="n">
-        <v>50.04</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:51:24</t>
+          <t>04:50:24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="F15" t="n">
-        <v>9.9</v>
+        <v>8.35</v>
       </c>
       <c r="G15" t="n">
-        <v>60.5</v>
+        <v>56.4</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.31</v>
+        <v>63.79</v>
       </c>
       <c r="K15" t="n">
-        <v>71.63</v>
+        <v>-18.62</v>
       </c>
       <c r="L15" t="n">
-        <v>72.23999999999999</v>
+        <v>66.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:52:44</t>
+          <t>04:52:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.83</v>
+        <v>3.09</v>
       </c>
       <c r="F16" t="n">
-        <v>9.279999999999999</v>
+        <v>7.18</v>
       </c>
       <c r="G16" t="n">
-        <v>50.2</v>
+        <v>52.3</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>-19.72</v>
+        <v>-60.35</v>
       </c>
       <c r="K16" t="n">
-        <v>-59.83</v>
+        <v>-26.53</v>
       </c>
       <c r="L16" t="n">
-        <v>63</v>
+        <v>65.92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:55:37</t>
+          <t>04:55:27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.78</v>
+        <v>3.07</v>
       </c>
       <c r="F17" t="n">
-        <v>9.859999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="G17" t="n">
-        <v>34.3</v>
+        <v>50.6</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="I17" t="n">
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>50.68</v>
+        <v>6.65</v>
       </c>
       <c r="K17" t="n">
-        <v>1.52</v>
+        <v>-21.21</v>
       </c>
       <c r="L17" t="n">
-        <v>50.71</v>
+        <v>22.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:58:16</t>
+          <t>04:57:07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.93</v>
+        <v>3.88</v>
       </c>
       <c r="F18" t="n">
-        <v>9.59</v>
+        <v>10.34</v>
       </c>
       <c r="G18" t="n">
-        <v>65.90000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>60.52</v>
+        <v>-82.75</v>
       </c>
       <c r="K18" t="n">
-        <v>42.41</v>
+        <v>56.51</v>
       </c>
       <c r="L18" t="n">
-        <v>73.90000000000001</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:59:22</t>
+          <t>04:58:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="F19" t="n">
-        <v>9.130000000000001</v>
+        <v>5.95</v>
       </c>
       <c r="G19" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
       <c r="H19" t="n">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>-44.54</v>
+        <v>21.56</v>
       </c>
       <c r="K19" t="n">
-        <v>55.58</v>
+        <v>-46.92</v>
       </c>
       <c r="L19" t="n">
-        <v>71.22</v>
+        <v>51.64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:05:13</t>
+          <t>05:03:17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="F20" t="n">
-        <v>9.59</v>
+        <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>44.7</v>
+        <v>51.9</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-28.96</v>
+        <v>31.23</v>
       </c>
       <c r="K20" t="n">
-        <v>82.73</v>
+        <v>-107.12</v>
       </c>
       <c r="L20" t="n">
-        <v>87.65000000000001</v>
+        <v>111.58</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:06:52</t>
+          <t>05:05:50</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="F21" t="n">
-        <v>9.9</v>
+        <v>7.88</v>
       </c>
       <c r="G21" t="n">
-        <v>50.8</v>
+        <v>45.8</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>-68.45999999999999</v>
+        <v>22.9</v>
       </c>
       <c r="K21" t="n">
-        <v>117.3</v>
+        <v>10.66</v>
       </c>
       <c r="L21" t="n">
-        <v>135.82</v>
+        <v>25.26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:09:13</t>
+          <t>05:07:53</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,13 +961,13 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="F22" t="n">
-        <v>9.390000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="G22" t="n">
-        <v>64.5</v>
+        <v>49.7</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -976,19 +976,19 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-43.55</v>
+        <v>91.25</v>
       </c>
       <c r="K22" t="n">
-        <v>96.77</v>
+        <v>-13.16</v>
       </c>
       <c r="L22" t="n">
-        <v>106.12</v>
+        <v>92.19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:12:32</t>
+          <t>05:11:48</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.29</v>
+        <v>3.46</v>
       </c>
       <c r="F23" t="n">
-        <v>9.529999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>53</v>
+        <v>48.4</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="I23" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J23" t="n">
-        <v>-117.74</v>
+        <v>57.62</v>
       </c>
       <c r="K23" t="n">
-        <v>12.43</v>
+        <v>-144.23</v>
       </c>
       <c r="L23" t="n">
-        <v>118.4</v>
+        <v>155.31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:14:05</t>
+          <t>05:13:59</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,13 +1045,13 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.14</v>
+        <v>2.98</v>
       </c>
       <c r="F24" t="n">
-        <v>10.01</v>
+        <v>9.83</v>
       </c>
       <c r="G24" t="n">
-        <v>52.7</v>
+        <v>52</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1060,19 +1060,19 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-62.58</v>
+        <v>155.78</v>
       </c>
       <c r="K24" t="n">
-        <v>-89.02</v>
+        <v>19.1</v>
       </c>
       <c r="L24" t="n">
-        <v>108.82</v>
+        <v>156.95</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:14:52</t>
+          <t>05:16:18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="F25" t="n">
-        <v>9.699999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>51.8</v>
+        <v>62</v>
       </c>
       <c r="H25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>98.44</v>
+        <v>-79.56999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-129.29</v>
+        <v>102.12</v>
       </c>
       <c r="L25" t="n">
-        <v>162.5</v>
+        <v>129.46</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:21:10</t>
+          <t>05:22:05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.81</v>
+        <v>3.44</v>
       </c>
       <c r="F26" t="n">
-        <v>10.15</v>
+        <v>11.04</v>
       </c>
       <c r="G26" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="H26" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-159.47</v>
+        <v>-219.9</v>
       </c>
       <c r="K26" t="n">
-        <v>-256.27</v>
+        <v>49.56</v>
       </c>
       <c r="L26" t="n">
-        <v>301.83</v>
+        <v>225.42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:23:18</t>
+          <t>05:22:45</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="F27" t="n">
-        <v>9.16</v>
+        <v>7.34</v>
       </c>
       <c r="G27" t="n">
-        <v>50.7</v>
+        <v>55.4</v>
       </c>
       <c r="H27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>50.81</v>
+        <v>-68.44</v>
       </c>
       <c r="K27" t="n">
-        <v>119.45</v>
+        <v>167.95</v>
       </c>
       <c r="L27" t="n">
-        <v>129.81</v>
+        <v>181.36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:24:42</t>
+          <t>05:23:55</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="F28" t="n">
-        <v>9.380000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="G28" t="n">
-        <v>48.1</v>
+        <v>54</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>-7.3</v>
+        <v>131.04</v>
       </c>
       <c r="K28" t="n">
-        <v>-150.9</v>
+        <v>249.33</v>
       </c>
       <c r="L28" t="n">
-        <v>151.08</v>
+        <v>281.66</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:34:26</t>
+          <t>05:31:25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.39</v>
+        <v>3.16</v>
       </c>
       <c r="F29" t="n">
-        <v>9.359999999999999</v>
+        <v>10.42</v>
       </c>
       <c r="G29" t="n">
-        <v>63.4</v>
+        <v>44.8</v>
       </c>
       <c r="H29" t="n">
-        <v>4.9</v>
+        <v>0.1</v>
       </c>
       <c r="I29" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J29" t="n">
-        <v>-58.42</v>
+        <v>-43.14</v>
       </c>
       <c r="K29" t="n">
-        <v>-8.98</v>
+        <v>-27</v>
       </c>
       <c r="L29" t="n">
-        <v>59.1</v>
+        <v>50.89</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:36:00</t>
+          <t>05:32:55</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.92</v>
+        <v>3.21</v>
       </c>
       <c r="F30" t="n">
-        <v>9.81</v>
+        <v>8.58</v>
       </c>
       <c r="G30" t="n">
-        <v>52.8</v>
+        <v>49.1</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-62.08</v>
+        <v>24.55</v>
       </c>
       <c r="K30" t="n">
-        <v>-24.64</v>
+        <v>47.3</v>
       </c>
       <c r="L30" t="n">
-        <v>66.79000000000001</v>
+        <v>53.29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:38:12</t>
+          <t>05:34:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.65</v>
+        <v>3.18</v>
       </c>
       <c r="F31" t="n">
-        <v>9.699999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>48.8</v>
+        <v>61</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>-47.65</v>
+        <v>52.21</v>
       </c>
       <c r="K31" t="n">
-        <v>32.01</v>
+        <v>-31.21</v>
       </c>
       <c r="L31" t="n">
-        <v>57.4</v>
+        <v>60.83</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:43:34</t>
+          <t>05:38:11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="F32" t="n">
-        <v>9.4</v>
+        <v>10.68</v>
       </c>
       <c r="G32" t="n">
-        <v>64.5</v>
+        <v>53.3</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-46.93</v>
+        <v>-48.67</v>
       </c>
       <c r="K32" t="n">
-        <v>-20.43</v>
+        <v>29.99</v>
       </c>
       <c r="L32" t="n">
-        <v>51.18</v>
+        <v>57.16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:44:57</t>
+          <t>05:40:55</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.39</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>9.140000000000001</v>
+        <v>6.24</v>
       </c>
       <c r="G33" t="n">
-        <v>69.09999999999999</v>
+        <v>50.6</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-46.4</v>
+        <v>66.27</v>
       </c>
       <c r="K33" t="n">
-        <v>-29.26</v>
+        <v>-28.18</v>
       </c>
       <c r="L33" t="n">
-        <v>54.86</v>
+        <v>72.02</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:46:32</t>
+          <t>05:42:21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.46</v>
+        <v>2.91</v>
       </c>
       <c r="F34" t="n">
-        <v>9.140000000000001</v>
+        <v>10.26</v>
       </c>
       <c r="G34" t="n">
-        <v>49.3</v>
+        <v>54.3</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="I34" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J34" t="n">
-        <v>70.19</v>
+        <v>-70.22</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.76</v>
+        <v>11.99</v>
       </c>
       <c r="L34" t="n">
-        <v>70.34999999999999</v>
+        <v>71.23999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:51:59</t>
+          <t>05:48:34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.73</v>
+        <v>3.31</v>
       </c>
       <c r="F35" t="n">
-        <v>9.470000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="G35" t="n">
-        <v>38.6</v>
+        <v>67</v>
       </c>
       <c r="H35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>-12.01</v>
+        <v>-85.25</v>
       </c>
       <c r="K35" t="n">
-        <v>105.5</v>
+        <v>-20.26</v>
       </c>
       <c r="L35" t="n">
-        <v>106.18</v>
+        <v>87.63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:54:04</t>
+          <t>05:50:28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.36</v>
+        <v>3.11</v>
       </c>
       <c r="F36" t="n">
-        <v>9.220000000000001</v>
+        <v>6.93</v>
       </c>
       <c r="G36" t="n">
-        <v>54.1</v>
+        <v>47.3</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>108.05</v>
+        <v>-61.67</v>
       </c>
       <c r="K36" t="n">
-        <v>-63.77</v>
+        <v>21.71</v>
       </c>
       <c r="L36" t="n">
-        <v>125.46</v>
+        <v>65.39</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:56:14</t>
+          <t>05:51:42</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="F37" t="n">
-        <v>9.83</v>
+        <v>10.2</v>
       </c>
       <c r="G37" t="n">
-        <v>50.3</v>
+        <v>35.4</v>
       </c>
       <c r="H37" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J37" t="n">
-        <v>30.57</v>
+        <v>79.08</v>
       </c>
       <c r="K37" t="n">
-        <v>-145.8</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>148.97</v>
+        <v>101.83</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:01:12</t>
+          <t>05:56:33</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.11</v>
+        <v>2.77</v>
       </c>
       <c r="F38" t="n">
-        <v>9.130000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="G38" t="n">
-        <v>44.7</v>
+        <v>38.8</v>
       </c>
       <c r="H38" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>24.08</v>
+        <v>105.47</v>
       </c>
       <c r="K38" t="n">
-        <v>-175.92</v>
+        <v>-12.42</v>
       </c>
       <c r="L38" t="n">
-        <v>177.56</v>
+        <v>106.19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:03:53</t>
+          <t>05:58:47</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.19</v>
+        <v>3.34</v>
       </c>
       <c r="F39" t="n">
-        <v>9.380000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="G39" t="n">
-        <v>56.9</v>
+        <v>47.5</v>
       </c>
       <c r="H39" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>32.51</v>
+        <v>65.66</v>
       </c>
       <c r="K39" t="n">
-        <v>-124.5</v>
+        <v>147.45</v>
       </c>
       <c r="L39" t="n">
-        <v>128.68</v>
+        <v>161.41</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:05:22</t>
+          <t>06:00:46</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="F40" t="n">
-        <v>9.82</v>
+        <v>6.33</v>
       </c>
       <c r="G40" t="n">
-        <v>54.8</v>
+        <v>54.6</v>
       </c>
       <c r="H40" t="n">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>94.52</v>
+        <v>-90.81999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>1.23</v>
+        <v>-16.82</v>
       </c>
       <c r="L40" t="n">
-        <v>94.52</v>
+        <v>92.36</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:11:46</t>
+          <t>06:06:23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.59</v>
+        <v>3.52</v>
       </c>
       <c r="F41" t="n">
-        <v>9.16</v>
+        <v>7.92</v>
       </c>
       <c r="G41" t="n">
-        <v>54.4</v>
+        <v>54.6</v>
       </c>
       <c r="H41" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>-176.07</v>
+        <v>148.39</v>
       </c>
       <c r="K41" t="n">
-        <v>7.19</v>
+        <v>10.49</v>
       </c>
       <c r="L41" t="n">
-        <v>176.22</v>
+        <v>148.76</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:12:29</t>
+          <t>06:08:10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="F42" t="n">
-        <v>9.51</v>
+        <v>6.88</v>
       </c>
       <c r="G42" t="n">
-        <v>53.6</v>
+        <v>53.3</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>257.66</v>
+        <v>-4.5</v>
       </c>
       <c r="K42" t="n">
-        <v>-13.89</v>
+        <v>-37.31</v>
       </c>
       <c r="L42" t="n">
-        <v>258.03</v>
+        <v>37.58</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:15:02</t>
+          <t>06:10:13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.41</v>
+        <v>3.07</v>
       </c>
       <c r="F43" t="n">
-        <v>9.539999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="G43" t="n">
-        <v>42.7</v>
+        <v>45.5</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="I43" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J43" t="n">
-        <v>171.51</v>
+        <v>-70.56</v>
       </c>
       <c r="K43" t="n">
-        <v>-143.22</v>
+        <v>198.27</v>
       </c>
       <c r="L43" t="n">
-        <v>223.44</v>
+        <v>210.45</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:25:32</t>
+          <t>06:20:14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="F44" t="n">
-        <v>10.18</v>
+        <v>10.04</v>
       </c>
       <c r="G44" t="n">
-        <v>47.9</v>
+        <v>44.1</v>
       </c>
       <c r="H44" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>25.84</v>
+        <v>41.91</v>
       </c>
       <c r="K44" t="n">
-        <v>43.97</v>
+        <v>-58.31</v>
       </c>
       <c r="L44" t="n">
-        <v>51</v>
+        <v>71.81</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:27:39</t>
+          <t>06:21:30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.22</v>
+        <v>3.36</v>
       </c>
       <c r="F45" t="n">
-        <v>9.76</v>
+        <v>10.12</v>
       </c>
       <c r="G45" t="n">
-        <v>45</v>
+        <v>47.3</v>
       </c>
       <c r="H45" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J45" t="n">
-        <v>30.12</v>
+        <v>-19.8</v>
       </c>
       <c r="K45" t="n">
-        <v>37.34</v>
+        <v>-90.13</v>
       </c>
       <c r="L45" t="n">
-        <v>47.97</v>
+        <v>92.28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:29:51</t>
+          <t>06:23:37</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="F46" t="n">
-        <v>8.5</v>
+        <v>10.54</v>
       </c>
       <c r="G46" t="n">
-        <v>50.1</v>
+        <v>55.2</v>
       </c>
       <c r="H46" t="n">
-        <v>2.9</v>
+        <v>5.6</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J46" t="n">
-        <v>-49.7</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>23.46</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>54.96</v>
+        <v>71.65000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:34:44</t>
+          <t>06:28:06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.21</v>
+        <v>2.94</v>
       </c>
       <c r="F47" t="n">
-        <v>9.6</v>
+        <v>9.48</v>
       </c>
       <c r="G47" t="n">
-        <v>46.6</v>
+        <v>51.6</v>
       </c>
       <c r="H47" t="n">
-        <v>6.3</v>
+        <v>4.6</v>
       </c>
       <c r="I47" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>-9.19</v>
+        <v>94.03</v>
       </c>
       <c r="K47" t="n">
-        <v>71.48999999999999</v>
+        <v>14.14</v>
       </c>
       <c r="L47" t="n">
-        <v>72.08</v>
+        <v>95.09</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:35:26</t>
+          <t>06:29:19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.15</v>
+        <v>3.43</v>
       </c>
       <c r="F48" t="n">
-        <v>9.82</v>
+        <v>7.66</v>
       </c>
       <c r="G48" t="n">
-        <v>57.4</v>
+        <v>65.2</v>
       </c>
       <c r="H48" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-50.45</v>
+        <v>-21.7</v>
       </c>
       <c r="K48" t="n">
-        <v>-56.42</v>
+        <v>6.87</v>
       </c>
       <c r="L48" t="n">
-        <v>75.69</v>
+        <v>22.76</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:36:56</t>
+          <t>06:30:31</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.67</v>
+        <v>2.54</v>
       </c>
       <c r="F49" t="n">
-        <v>9.52</v>
+        <v>5.9</v>
       </c>
       <c r="G49" t="n">
-        <v>36</v>
+        <v>59.7</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I49" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>47.59</v>
+        <v>-62.52</v>
       </c>
       <c r="K49" t="n">
-        <v>51.97</v>
+        <v>26.99</v>
       </c>
       <c r="L49" t="n">
-        <v>70.47</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:43:09</t>
+          <t>06:34:53</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,13 +2137,13 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="F50" t="n">
-        <v>9.85</v>
+        <v>11.04</v>
       </c>
       <c r="G50" t="n">
-        <v>59.8</v>
+        <v>52</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2152,19 +2152,19 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>119.68</v>
+        <v>81.14</v>
       </c>
       <c r="K50" t="n">
-        <v>-90.05</v>
+        <v>34.49</v>
       </c>
       <c r="L50" t="n">
-        <v>149.77</v>
+        <v>88.16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:45:36</t>
+          <t>06:36:30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="F51" t="n">
-        <v>10.01</v>
+        <v>7.23</v>
       </c>
       <c r="G51" t="n">
-        <v>53.2</v>
+        <v>52.2</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-64.95</v>
+        <v>18.96</v>
       </c>
       <c r="K51" t="n">
-        <v>-64.88</v>
+        <v>-7.83</v>
       </c>
       <c r="L51" t="n">
-        <v>91.8</v>
+        <v>20.51</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:47:48</t>
+          <t>06:38:45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.21</v>
+        <v>3.05</v>
       </c>
       <c r="F52" t="n">
-        <v>9.289999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="G52" t="n">
-        <v>53.8</v>
+        <v>53.5</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="I52" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>0.35</v>
+        <v>-74.04000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>91.18000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="L52" t="n">
-        <v>91.18000000000001</v>
+        <v>76.39</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:51:23</t>
+          <t>06:41:45</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.27</v>
+        <v>3.52</v>
       </c>
       <c r="F53" t="n">
-        <v>9.44</v>
+        <v>10.93</v>
       </c>
       <c r="G53" t="n">
-        <v>60.8</v>
+        <v>50.5</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>-82.15000000000001</v>
+        <v>32.46</v>
       </c>
       <c r="K53" t="n">
-        <v>94.98999999999999</v>
+        <v>165.48</v>
       </c>
       <c r="L53" t="n">
-        <v>125.58</v>
+        <v>168.64</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:53:31</t>
+          <t>06:44:12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="F54" t="n">
-        <v>9.140000000000001</v>
+        <v>7.36</v>
       </c>
       <c r="G54" t="n">
-        <v>67.3</v>
+        <v>44</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-50.34</v>
+        <v>65.5</v>
       </c>
       <c r="K54" t="n">
-        <v>-132.53</v>
+        <v>-80.81999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>141.77</v>
+        <v>104.03</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:55:01</t>
+          <t>06:45:23</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.91</v>
+        <v>3.19</v>
       </c>
       <c r="F55" t="n">
-        <v>9.359999999999999</v>
+        <v>11.04</v>
       </c>
       <c r="G55" t="n">
-        <v>52</v>
+        <v>61.5</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-58.67</v>
+        <v>211.49</v>
       </c>
       <c r="K55" t="n">
-        <v>-113.22</v>
+        <v>-33.35</v>
       </c>
       <c r="L55" t="n">
-        <v>127.51</v>
+        <v>214.11</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:59:42</t>
+          <t>06:50:44</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="F56" t="n">
-        <v>9.94</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>50.9</v>
+        <v>61</v>
       </c>
       <c r="H56" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>-87.69</v>
+        <v>-172.73</v>
       </c>
       <c r="K56" t="n">
-        <v>-144.14</v>
+        <v>-152.17</v>
       </c>
       <c r="L56" t="n">
-        <v>168.72</v>
+        <v>230.19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:01:54</t>
+          <t>06:52:30</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.58</v>
+        <v>2.55</v>
       </c>
       <c r="F57" t="n">
-        <v>9.84</v>
+        <v>6.86</v>
       </c>
       <c r="G57" t="n">
-        <v>34.8</v>
+        <v>46.3</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J57" t="n">
-        <v>-7.94</v>
+        <v>-99.56999999999999</v>
       </c>
       <c r="K57" t="n">
-        <v>-199.37</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="L57" t="n">
-        <v>199.52</v>
+        <v>139.35</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:02:50</t>
+          <t>06:53:30</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.02</v>
+        <v>3.51</v>
       </c>
       <c r="F58" t="n">
-        <v>9.83</v>
+        <v>10.04</v>
       </c>
       <c r="G58" t="n">
-        <v>56</v>
+        <v>48.5</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="I58" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>15.17</v>
+        <v>-8.83</v>
       </c>
       <c r="K58" t="n">
-        <v>176.06</v>
+        <v>-223.18</v>
       </c>
       <c r="L58" t="n">
-        <v>176.71</v>
+        <v>223.35</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:13:56</t>
+          <t>07:05:21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.13</v>
+        <v>3.37</v>
       </c>
       <c r="F59" t="n">
-        <v>9.289999999999999</v>
+        <v>6.36</v>
       </c>
       <c r="G59" t="n">
-        <v>55.2</v>
+        <v>42</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J59" t="n">
-        <v>69.19</v>
+        <v>-29.81</v>
       </c>
       <c r="K59" t="n">
-        <v>-20.67</v>
+        <v>47.82</v>
       </c>
       <c r="L59" t="n">
-        <v>72.22</v>
+        <v>56.35</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:14:59</t>
+          <t>07:06:58</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.89</v>
+        <v>3.14</v>
       </c>
       <c r="F60" t="n">
-        <v>9.31</v>
+        <v>9.67</v>
       </c>
       <c r="G60" t="n">
-        <v>63.8</v>
+        <v>61.2</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I60" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>23.64</v>
+        <v>36.06</v>
       </c>
       <c r="K60" t="n">
-        <v>39.14</v>
+        <v>48.92</v>
       </c>
       <c r="L60" t="n">
-        <v>45.73</v>
+        <v>60.77</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:15:44</t>
+          <t>07:08:31</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.63</v>
+        <v>3.43</v>
       </c>
       <c r="F61" t="n">
-        <v>9.539999999999999</v>
+        <v>7.43</v>
       </c>
       <c r="G61" t="n">
-        <v>56.7</v>
+        <v>51.8</v>
       </c>
       <c r="H61" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>50.92</v>
+        <v>-51.6</v>
       </c>
       <c r="K61" t="n">
-        <v>4.66</v>
+        <v>61.91</v>
       </c>
       <c r="L61" t="n">
-        <v>51.13</v>
+        <v>80.59</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:21:42</t>
+          <t>07:13:55</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="F62" t="n">
-        <v>9.59</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G62" t="n">
-        <v>68.3</v>
+        <v>54</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>-17.23</v>
+        <v>64.86</v>
       </c>
       <c r="K62" t="n">
-        <v>-79.61</v>
+        <v>-12.93</v>
       </c>
       <c r="L62" t="n">
-        <v>81.45</v>
+        <v>66.14</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:22:40</t>
+          <t>07:15:48</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.37</v>
+        <v>2.72</v>
       </c>
       <c r="F63" t="n">
-        <v>8.98</v>
+        <v>11.04</v>
       </c>
       <c r="G63" t="n">
-        <v>37.6</v>
+        <v>47.6</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="I63" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>-48.05</v>
+        <v>46.81</v>
       </c>
       <c r="K63" t="n">
-        <v>65.73999999999999</v>
+        <v>-53.67</v>
       </c>
       <c r="L63" t="n">
-        <v>81.43000000000001</v>
+        <v>71.20999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:24:25</t>
+          <t>07:18:24</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.13</v>
+        <v>3.89</v>
       </c>
       <c r="F64" t="n">
-        <v>10.24</v>
+        <v>11.04</v>
       </c>
       <c r="G64" t="n">
-        <v>48.5</v>
+        <v>60.4</v>
       </c>
       <c r="H64" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>46.06</v>
+        <v>-2.47</v>
       </c>
       <c r="K64" t="n">
-        <v>-22.77</v>
+        <v>93.89</v>
       </c>
       <c r="L64" t="n">
-        <v>51.38</v>
+        <v>93.92</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:29:47</t>
+          <t>07:22:59</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.63</v>
+        <v>3.22</v>
       </c>
       <c r="F65" t="n">
-        <v>9.91</v>
+        <v>10.23</v>
       </c>
       <c r="G65" t="n">
-        <v>50.2</v>
+        <v>55.2</v>
       </c>
       <c r="H65" t="n">
-        <v>6.9</v>
+        <v>0.9</v>
       </c>
       <c r="I65" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-96.45999999999999</v>
+        <v>79.48</v>
       </c>
       <c r="K65" t="n">
-        <v>26.14</v>
+        <v>39.59</v>
       </c>
       <c r="L65" t="n">
-        <v>99.94</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:31:41</t>
+          <t>07:25:04</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.44</v>
+        <v>3.39</v>
       </c>
       <c r="F66" t="n">
-        <v>9.57</v>
+        <v>9.74</v>
       </c>
       <c r="G66" t="n">
-        <v>56.3</v>
+        <v>56.2</v>
       </c>
       <c r="H66" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-4.26</v>
+        <v>158.94</v>
       </c>
       <c r="K66" t="n">
-        <v>-69.79000000000001</v>
+        <v>-72.63</v>
       </c>
       <c r="L66" t="n">
-        <v>69.92</v>
+        <v>174.75</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:33:04</t>
+          <t>07:27:02</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.48</v>
+        <v>3.24</v>
       </c>
       <c r="F67" t="n">
-        <v>9.369999999999999</v>
+        <v>11.04</v>
       </c>
       <c r="G67" t="n">
-        <v>43.8</v>
+        <v>57.1</v>
       </c>
       <c r="H67" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="I67" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>113.07</v>
+        <v>100.89</v>
       </c>
       <c r="K67" t="n">
-        <v>-67.76000000000001</v>
+        <v>95.17</v>
       </c>
       <c r="L67" t="n">
-        <v>131.82</v>
+        <v>138.7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:38:30</t>
+          <t>07:32:04</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.58</v>
+        <v>4.43</v>
       </c>
       <c r="F68" t="n">
-        <v>10.09</v>
+        <v>11.04</v>
       </c>
       <c r="G68" t="n">
-        <v>65</v>
+        <v>53.6</v>
       </c>
       <c r="H68" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>29.17</v>
+        <v>81.69</v>
       </c>
       <c r="K68" t="n">
-        <v>-168.09</v>
+        <v>-164.01</v>
       </c>
       <c r="L68" t="n">
-        <v>170.6</v>
+        <v>183.23</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:41:01</t>
+          <t>07:33:20</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="F69" t="n">
-        <v>8.92</v>
+        <v>8.73</v>
       </c>
       <c r="G69" t="n">
-        <v>58.3</v>
+        <v>64.3</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I69" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>-110.55</v>
+        <v>-45.49</v>
       </c>
       <c r="K69" t="n">
-        <v>-77.40000000000001</v>
+        <v>168.95</v>
       </c>
       <c r="L69" t="n">
-        <v>134.95</v>
+        <v>174.97</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:42:41</t>
+          <t>07:34:57</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.81</v>
+        <v>2.99</v>
       </c>
       <c r="F70" t="n">
-        <v>9.289999999999999</v>
+        <v>7.92</v>
       </c>
       <c r="G70" t="n">
-        <v>67.59999999999999</v>
+        <v>60</v>
       </c>
       <c r="H70" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J70" t="n">
-        <v>-138.06</v>
+        <v>122.6</v>
       </c>
       <c r="K70" t="n">
-        <v>82.67</v>
+        <v>38.35</v>
       </c>
       <c r="L70" t="n">
-        <v>160.92</v>
+        <v>128.46</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:48:05</t>
+          <t>07:41:34</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="F71" t="n">
-        <v>9.69</v>
+        <v>10.82</v>
       </c>
       <c r="G71" t="n">
-        <v>62.4</v>
+        <v>61.8</v>
       </c>
       <c r="H71" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="I71" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>125.69</v>
+        <v>39.95</v>
       </c>
       <c r="K71" t="n">
-        <v>71.01000000000001</v>
+        <v>-215.76</v>
       </c>
       <c r="L71" t="n">
-        <v>144.36</v>
+        <v>219.43</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:50:35</t>
+          <t>07:43:55</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="F72" t="n">
-        <v>9.550000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>42.1</v>
+        <v>61.2</v>
       </c>
       <c r="H72" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="I72" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J72" t="n">
-        <v>49.23</v>
+        <v>-45.09</v>
       </c>
       <c r="K72" t="n">
-        <v>220.02</v>
+        <v>146.44</v>
       </c>
       <c r="L72" t="n">
-        <v>225.46</v>
+        <v>153.23</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:52:15</t>
+          <t>07:45:35</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.34</v>
+        <v>2.58</v>
       </c>
       <c r="F73" t="n">
-        <v>9.75</v>
+        <v>9.5</v>
       </c>
       <c r="G73" t="n">
-        <v>50.9</v>
+        <v>62.2</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I73" t="n">
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-111.05</v>
+        <v>179.59</v>
       </c>
       <c r="K73" t="n">
-        <v>157.51</v>
+        <v>-26.57</v>
       </c>
       <c r="L73" t="n">
-        <v>192.72</v>
+        <v>181.55</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:03:48</t>
+          <t>07:55:42</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.82</v>
+        <v>3.53</v>
       </c>
       <c r="F74" t="n">
-        <v>9.82</v>
+        <v>11.04</v>
       </c>
       <c r="G74" t="n">
-        <v>56.8</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H74" t="n">
-        <v>3.5</v>
+        <v>6.1</v>
       </c>
       <c r="I74" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>10.38</v>
+        <v>-44.75</v>
       </c>
       <c r="K74" t="n">
-        <v>-45.92</v>
+        <v>63.54</v>
       </c>
       <c r="L74" t="n">
-        <v>47.08</v>
+        <v>77.72</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:05:42</t>
+          <t>07:57:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.9</v>
+        <v>3.66</v>
       </c>
       <c r="F75" t="n">
-        <v>10.11</v>
+        <v>9.75</v>
       </c>
       <c r="G75" t="n">
-        <v>47.5</v>
+        <v>60.2</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J75" t="n">
-        <v>23.49</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>-41.25</v>
+        <v>28.52</v>
       </c>
       <c r="L75" t="n">
-        <v>47.47</v>
+        <v>71.12</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:06:58</t>
+          <t>07:57:55</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.65</v>
+        <v>3.07</v>
       </c>
       <c r="F76" t="n">
-        <v>10.25</v>
+        <v>11.04</v>
       </c>
       <c r="G76" t="n">
-        <v>66.09999999999999</v>
+        <v>54.6</v>
       </c>
       <c r="H76" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>-64.34</v>
+        <v>22.71</v>
       </c>
       <c r="K76" t="n">
-        <v>9.869999999999999</v>
+        <v>87.55</v>
       </c>
       <c r="L76" t="n">
-        <v>65.09</v>
+        <v>90.45</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:11:26</t>
+          <t>08:01:47</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.19</v>
+        <v>3.28</v>
       </c>
       <c r="F77" t="n">
-        <v>10.59</v>
+        <v>11.04</v>
       </c>
       <c r="G77" t="n">
-        <v>60</v>
+        <v>54.6</v>
       </c>
       <c r="H77" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-46.16</v>
+        <v>59.47</v>
       </c>
       <c r="K77" t="n">
-        <v>61.05</v>
+        <v>44.05</v>
       </c>
       <c r="L77" t="n">
-        <v>76.53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:12:51</t>
+          <t>08:03:38</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.16</v>
+        <v>3.39</v>
       </c>
       <c r="F78" t="n">
-        <v>9.85</v>
+        <v>11.04</v>
       </c>
       <c r="G78" t="n">
-        <v>63.4</v>
+        <v>55.9</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>-20.36</v>
+        <v>-59.9</v>
       </c>
       <c r="K78" t="n">
-        <v>68.23</v>
+        <v>-17.55</v>
       </c>
       <c r="L78" t="n">
-        <v>71.20999999999999</v>
+        <v>62.42</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:14:20</t>
+          <t>08:05:45</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.77</v>
+        <v>3.94</v>
       </c>
       <c r="F79" t="n">
-        <v>9.51</v>
+        <v>11.04</v>
       </c>
       <c r="G79" t="n">
-        <v>50</v>
+        <v>65.8</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>1.38</v>
+        <v>-86.86</v>
       </c>
       <c r="K79" t="n">
-        <v>86.70999999999999</v>
+        <v>39.95</v>
       </c>
       <c r="L79" t="n">
-        <v>86.72</v>
+        <v>95.61</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:18:11</t>
+          <t>08:10:04</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.93</v>
+        <v>3.84</v>
       </c>
       <c r="F80" t="n">
-        <v>9.58</v>
+        <v>10.02</v>
       </c>
       <c r="G80" t="n">
-        <v>65.8</v>
+        <v>61</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>69.19</v>
+        <v>-64.41</v>
       </c>
       <c r="K80" t="n">
-        <v>92.06</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>115.16</v>
+        <v>107.99</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:20:05</t>
+          <t>08:11:53</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.8</v>
+        <v>3.39</v>
       </c>
       <c r="F81" t="n">
-        <v>9.27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G81" t="n">
-        <v>51</v>
+        <v>57.1</v>
       </c>
       <c r="H81" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="I81" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>-41.45</v>
+        <v>-39.44</v>
       </c>
       <c r="K81" t="n">
-        <v>58.51</v>
+        <v>-75.22</v>
       </c>
       <c r="L81" t="n">
-        <v>71.7</v>
+        <v>84.93000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:21:56</t>
+          <t>08:13:22</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.21</v>
+        <v>3.95</v>
       </c>
       <c r="F82" t="n">
-        <v>9.970000000000001</v>
+        <v>11.04</v>
       </c>
       <c r="G82" t="n">
-        <v>57.1</v>
+        <v>62</v>
       </c>
       <c r="H82" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="I82" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-45.59</v>
+        <v>-95.79000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>87.8</v>
+        <v>-15.27</v>
       </c>
       <c r="L82" t="n">
-        <v>98.93000000000001</v>
+        <v>97</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:25:59</t>
+          <t>08:17:21</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.09</v>
+        <v>3.14</v>
       </c>
       <c r="F83" t="n">
-        <v>9.27</v>
+        <v>10.5</v>
       </c>
       <c r="G83" t="n">
-        <v>49.6</v>
+        <v>60.5</v>
       </c>
       <c r="H83" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>-121.54</v>
+        <v>175.86</v>
       </c>
       <c r="K83" t="n">
-        <v>-89.31</v>
+        <v>71.56</v>
       </c>
       <c r="L83" t="n">
-        <v>150.82</v>
+        <v>189.86</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:27:33</t>
+          <t>08:19:20</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.76</v>
+        <v>3.87</v>
       </c>
       <c r="F84" t="n">
-        <v>9.779999999999999</v>
+        <v>11.04</v>
       </c>
       <c r="G84" t="n">
-        <v>60.5</v>
+        <v>54.1</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>74.47</v>
+        <v>14.84</v>
       </c>
       <c r="K84" t="n">
-        <v>121.63</v>
+        <v>125.39</v>
       </c>
       <c r="L84" t="n">
-        <v>142.62</v>
+        <v>126.27</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:29:10</t>
+          <t>08:21:27</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="F85" t="n">
-        <v>9.5</v>
+        <v>10.93</v>
       </c>
       <c r="G85" t="n">
-        <v>54.8</v>
+        <v>57.9</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="I85" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J85" t="n">
-        <v>102.85</v>
+        <v>14.41</v>
       </c>
       <c r="K85" t="n">
-        <v>64.94</v>
+        <v>-160.95</v>
       </c>
       <c r="L85" t="n">
-        <v>121.64</v>
+        <v>161.59</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:32:55</t>
+          <t>08:25:02</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.52</v>
+        <v>3.57</v>
       </c>
       <c r="F86" t="n">
-        <v>9.19</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="G86" t="n">
-        <v>57.9</v>
+        <v>45.9</v>
       </c>
       <c r="H86" t="n">
-        <v>4.4</v>
+        <v>6.3</v>
       </c>
       <c r="I86" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J86" t="n">
-        <v>-202.08</v>
+        <v>257.05</v>
       </c>
       <c r="K86" t="n">
-        <v>16.13</v>
+        <v>140.85</v>
       </c>
       <c r="L86" t="n">
-        <v>202.72</v>
+        <v>293.11</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:33:58</t>
+          <t>08:27:10</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="F87" t="n">
-        <v>10.47</v>
+        <v>8.31</v>
       </c>
       <c r="G87" t="n">
-        <v>60.8</v>
+        <v>49.3</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>19.9</v>
+        <v>45.45</v>
       </c>
       <c r="K87" t="n">
-        <v>-174.47</v>
+        <v>168.7</v>
       </c>
       <c r="L87" t="n">
-        <v>175.61</v>
+        <v>174.72</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:36:18</t>
+          <t>08:29:05</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="F88" t="n">
-        <v>9.470000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="G88" t="n">
-        <v>49.3</v>
+        <v>69.8</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>83.2</v>
+        <v>-187.33</v>
       </c>
       <c r="K88" t="n">
-        <v>-156.75</v>
+        <v>84.17</v>
       </c>
       <c r="L88" t="n">
-        <v>177.46</v>
+        <v>205.37</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-22.xlsx
+++ b/output/2024-05-22.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>40.28</v>
+        <v>35.81</v>
       </c>
       <c r="K14" t="n">
-        <v>25.07</v>
+        <v>22.29</v>
       </c>
       <c r="L14" t="n">
-        <v>47.45</v>
+        <v>42.18</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>29</v>
       </c>
       <c r="J15" t="n">
-        <v>63.79</v>
+        <v>56.7</v>
       </c>
       <c r="K15" t="n">
-        <v>-18.62</v>
+        <v>-16.55</v>
       </c>
       <c r="L15" t="n">
-        <v>66.45</v>
+        <v>59.07</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>-60.35</v>
+        <v>-56.5</v>
       </c>
       <c r="K16" t="n">
-        <v>-26.53</v>
+        <v>-24.84</v>
       </c>
       <c r="L16" t="n">
-        <v>65.92</v>
+        <v>61.71</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>6.65</v>
+        <v>6.38</v>
       </c>
       <c r="K17" t="n">
-        <v>-21.21</v>
+        <v>-20.33</v>
       </c>
       <c r="L17" t="n">
-        <v>22.23</v>
+        <v>21.31</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-82.75</v>
+        <v>-79.06</v>
       </c>
       <c r="K18" t="n">
-        <v>56.51</v>
+        <v>53.99</v>
       </c>
       <c r="L18" t="n">
-        <v>100.2</v>
+        <v>95.73</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>21.56</v>
+        <v>20.18</v>
       </c>
       <c r="K19" t="n">
-        <v>-46.92</v>
+        <v>-43.93</v>
       </c>
       <c r="L19" t="n">
-        <v>51.64</v>
+        <v>48.34</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>31.23</v>
+        <v>30.59</v>
       </c>
       <c r="K20" t="n">
-        <v>-107.12</v>
+        <v>-104.93</v>
       </c>
       <c r="L20" t="n">
-        <v>111.58</v>
+        <v>109.3</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>22.9</v>
+        <v>20.35</v>
       </c>
       <c r="K21" t="n">
-        <v>10.66</v>
+        <v>9.48</v>
       </c>
       <c r="L21" t="n">
-        <v>25.26</v>
+        <v>22.45</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>91.25</v>
+        <v>87.45</v>
       </c>
       <c r="K22" t="n">
-        <v>-13.16</v>
+        <v>-12.61</v>
       </c>
       <c r="L22" t="n">
-        <v>92.19</v>
+        <v>88.34999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>29</v>
       </c>
       <c r="J23" t="n">
-        <v>57.62</v>
+        <v>51.23</v>
       </c>
       <c r="K23" t="n">
-        <v>-144.23</v>
+        <v>-128.24</v>
       </c>
       <c r="L23" t="n">
-        <v>155.31</v>
+        <v>138.09</v>
       </c>
     </row>
     <row r="24">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>-79.56999999999999</v>
+        <v>-74.52</v>
       </c>
       <c r="K25" t="n">
-        <v>102.12</v>
+        <v>95.64</v>
       </c>
       <c r="L25" t="n">
-        <v>129.46</v>
+        <v>121.25</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-219.9</v>
+        <v>-215.77</v>
       </c>
       <c r="K26" t="n">
-        <v>49.56</v>
+        <v>48.62</v>
       </c>
       <c r="L26" t="n">
-        <v>225.42</v>
+        <v>221.18</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>-68.44</v>
+        <v>-62.49</v>
       </c>
       <c r="K27" t="n">
-        <v>167.95</v>
+        <v>153.34</v>
       </c>
       <c r="L27" t="n">
-        <v>181.36</v>
+        <v>165.59</v>
       </c>
     </row>
     <row r="28">
@@ -1270,13 +1270,13 @@
         <v>30</v>
       </c>
       <c r="J29" t="n">
-        <v>-43.14</v>
+        <v>-37.26</v>
       </c>
       <c r="K29" t="n">
-        <v>-27</v>
+        <v>-23.32</v>
       </c>
       <c r="L29" t="n">
-        <v>50.89</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="30">
@@ -1354,13 +1354,13 @@
         <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>52.21</v>
+        <v>48.88</v>
       </c>
       <c r="K31" t="n">
-        <v>-31.21</v>
+        <v>-29.21</v>
       </c>
       <c r="L31" t="n">
-        <v>60.83</v>
+        <v>56.95</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-48.67</v>
+        <v>-48.61</v>
       </c>
       <c r="K32" t="n">
-        <v>29.99</v>
+        <v>29.95</v>
       </c>
       <c r="L32" t="n">
-        <v>57.16</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>66.27</v>
+        <v>58.91</v>
       </c>
       <c r="K33" t="n">
-        <v>-28.18</v>
+        <v>-25.05</v>
       </c>
       <c r="L33" t="n">
-        <v>72.02</v>
+        <v>64.01000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>30</v>
       </c>
       <c r="J34" t="n">
-        <v>-70.22</v>
+        <v>-60.64</v>
       </c>
       <c r="K34" t="n">
-        <v>11.99</v>
+        <v>10.36</v>
       </c>
       <c r="L34" t="n">
-        <v>71.23999999999999</v>
+        <v>61.52</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>-85.25</v>
+        <v>-75.77</v>
       </c>
       <c r="K35" t="n">
-        <v>-20.26</v>
+        <v>-18</v>
       </c>
       <c r="L35" t="n">
-        <v>87.63</v>
+        <v>77.88</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>-61.67</v>
+        <v>-53.26</v>
       </c>
       <c r="K36" t="n">
-        <v>21.71</v>
+        <v>18.75</v>
       </c>
       <c r="L36" t="n">
-        <v>65.39</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>29</v>
       </c>
       <c r="J37" t="n">
-        <v>79.08</v>
+        <v>70.28</v>
       </c>
       <c r="K37" t="n">
-        <v>64.15000000000001</v>
+        <v>57.02</v>
       </c>
       <c r="L37" t="n">
-        <v>101.83</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="38">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>65.66</v>
+        <v>59.95</v>
       </c>
       <c r="K39" t="n">
-        <v>147.45</v>
+        <v>134.65</v>
       </c>
       <c r="L39" t="n">
-        <v>161.41</v>
+        <v>147.39</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>-90.81999999999999</v>
+        <v>-82.92</v>
       </c>
       <c r="K40" t="n">
-        <v>-16.82</v>
+        <v>-15.36</v>
       </c>
       <c r="L40" t="n">
-        <v>92.36</v>
+        <v>84.33</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>148.39</v>
+        <v>132.21</v>
       </c>
       <c r="K41" t="n">
-        <v>10.49</v>
+        <v>9.35</v>
       </c>
       <c r="L41" t="n">
-        <v>148.76</v>
+        <v>132.54</v>
       </c>
     </row>
     <row r="42">
@@ -1858,13 +1858,13 @@
         <v>29</v>
       </c>
       <c r="J43" t="n">
-        <v>-70.56</v>
+        <v>-62.72</v>
       </c>
       <c r="K43" t="n">
-        <v>198.27</v>
+        <v>176.24</v>
       </c>
       <c r="L43" t="n">
-        <v>210.45</v>
+        <v>187.06</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>41.91</v>
+        <v>41.06</v>
       </c>
       <c r="K44" t="n">
-        <v>-58.31</v>
+        <v>-57.12</v>
       </c>
       <c r="L44" t="n">
-        <v>71.81</v>
+        <v>70.34999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>29</v>
       </c>
       <c r="J45" t="n">
-        <v>-19.8</v>
+        <v>-17.59</v>
       </c>
       <c r="K45" t="n">
-        <v>-90.13</v>
+        <v>-80.08</v>
       </c>
       <c r="L45" t="n">
-        <v>92.28</v>
+        <v>81.98</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>29</v>
       </c>
       <c r="J46" t="n">
-        <v>8.390000000000001</v>
+        <v>7.45</v>
       </c>
       <c r="K46" t="n">
-        <v>71.15000000000001</v>
+        <v>63.19</v>
       </c>
       <c r="L46" t="n">
-        <v>71.65000000000001</v>
+        <v>63.62</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>94.03</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>14.14</v>
+        <v>12.91</v>
       </c>
       <c r="L47" t="n">
-        <v>95.09</v>
+        <v>86.81999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-21.7</v>
+        <v>-21.24</v>
       </c>
       <c r="K48" t="n">
-        <v>6.87</v>
+        <v>6.73</v>
       </c>
       <c r="L48" t="n">
-        <v>22.76</v>
+        <v>22.28</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>-62.52</v>
+        <v>-54</v>
       </c>
       <c r="K49" t="n">
-        <v>26.99</v>
+        <v>23.31</v>
       </c>
       <c r="L49" t="n">
-        <v>68.09999999999999</v>
+        <v>58.81</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>81.14</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>34.49</v>
+        <v>34.48</v>
       </c>
       <c r="L50" t="n">
-        <v>88.16</v>
+        <v>88.13</v>
       </c>
     </row>
     <row r="51">
@@ -2236,13 +2236,13 @@
         <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>-74.04000000000001</v>
+        <v>-67.61</v>
       </c>
       <c r="K52" t="n">
-        <v>18.8</v>
+        <v>17.17</v>
       </c>
       <c r="L52" t="n">
-        <v>76.39</v>
+        <v>69.75</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>32.46</v>
+        <v>28.04</v>
       </c>
       <c r="K53" t="n">
-        <v>165.48</v>
+        <v>142.96</v>
       </c>
       <c r="L53" t="n">
-        <v>168.64</v>
+        <v>145.69</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>65.5</v>
+        <v>64.16</v>
       </c>
       <c r="K54" t="n">
-        <v>-80.81999999999999</v>
+        <v>-79.17</v>
       </c>
       <c r="L54" t="n">
-        <v>104.03</v>
+        <v>101.91</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>211.49</v>
+        <v>207.18</v>
       </c>
       <c r="K55" t="n">
-        <v>-33.35</v>
+        <v>-32.67</v>
       </c>
       <c r="L55" t="n">
-        <v>214.11</v>
+        <v>209.74</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>-172.73</v>
+        <v>-173.21</v>
       </c>
       <c r="K56" t="n">
-        <v>-152.17</v>
+        <v>-152.59</v>
       </c>
       <c r="L56" t="n">
-        <v>230.19</v>
+        <v>230.83</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>29</v>
       </c>
       <c r="J57" t="n">
-        <v>-99.56999999999999</v>
+        <v>-88.5</v>
       </c>
       <c r="K57" t="n">
-        <v>97.48999999999999</v>
+        <v>86.66</v>
       </c>
       <c r="L57" t="n">
-        <v>139.35</v>
+        <v>123.87</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-8.83</v>
+        <v>-8.67</v>
       </c>
       <c r="K58" t="n">
-        <v>-223.18</v>
+        <v>-219.11</v>
       </c>
       <c r="L58" t="n">
-        <v>223.35</v>
+        <v>219.28</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>30</v>
       </c>
       <c r="J59" t="n">
-        <v>-29.81</v>
+        <v>-25.73</v>
       </c>
       <c r="K59" t="n">
-        <v>47.82</v>
+        <v>41.28</v>
       </c>
       <c r="L59" t="n">
-        <v>56.35</v>
+        <v>48.64</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>36.06</v>
+        <v>35.33</v>
       </c>
       <c r="K60" t="n">
-        <v>48.92</v>
+        <v>47.92</v>
       </c>
       <c r="L60" t="n">
-        <v>60.77</v>
+        <v>59.53</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-51.6</v>
+        <v>-50.51</v>
       </c>
       <c r="K61" t="n">
-        <v>61.91</v>
+        <v>60.59</v>
       </c>
       <c r="L61" t="n">
-        <v>80.59</v>
+        <v>78.88</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>64.86</v>
+        <v>63.5</v>
       </c>
       <c r="K62" t="n">
-        <v>-12.93</v>
+        <v>-12.65</v>
       </c>
       <c r="L62" t="n">
-        <v>66.14</v>
+        <v>64.73999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>46.81</v>
+        <v>42.74</v>
       </c>
       <c r="K63" t="n">
-        <v>-53.67</v>
+        <v>-49</v>
       </c>
       <c r="L63" t="n">
-        <v>71.20999999999999</v>
+        <v>65.02</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.47</v>
+        <v>-2.41</v>
       </c>
       <c r="K64" t="n">
-        <v>93.89</v>
+        <v>91.69</v>
       </c>
       <c r="L64" t="n">
-        <v>93.92</v>
+        <v>91.72</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>79.48</v>
+        <v>77.86</v>
       </c>
       <c r="K65" t="n">
-        <v>39.59</v>
+        <v>38.78</v>
       </c>
       <c r="L65" t="n">
-        <v>88.8</v>
+        <v>86.98999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>158.94</v>
+        <v>158.9</v>
       </c>
       <c r="K66" t="n">
-        <v>-72.63</v>
+        <v>-72.61</v>
       </c>
       <c r="L66" t="n">
-        <v>174.75</v>
+        <v>174.7</v>
       </c>
     </row>
     <row r="67">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>81.69</v>
+        <v>81.8</v>
       </c>
       <c r="K68" t="n">
-        <v>-164.01</v>
+        <v>-164.23</v>
       </c>
       <c r="L68" t="n">
-        <v>183.23</v>
+        <v>183.48</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>-45.49</v>
+        <v>-45.5</v>
       </c>
       <c r="K69" t="n">
-        <v>168.95</v>
+        <v>169</v>
       </c>
       <c r="L69" t="n">
-        <v>174.97</v>
+        <v>175.02</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>30</v>
       </c>
       <c r="J70" t="n">
-        <v>122.6</v>
+        <v>105.88</v>
       </c>
       <c r="K70" t="n">
-        <v>38.35</v>
+        <v>33.12</v>
       </c>
       <c r="L70" t="n">
-        <v>128.46</v>
+        <v>110.94</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>39.95</v>
+        <v>40.04</v>
       </c>
       <c r="K71" t="n">
-        <v>-215.76</v>
+        <v>-216.22</v>
       </c>
       <c r="L71" t="n">
-        <v>219.43</v>
+        <v>219.9</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>30</v>
       </c>
       <c r="J72" t="n">
-        <v>-45.09</v>
+        <v>-39.04</v>
       </c>
       <c r="K72" t="n">
-        <v>146.44</v>
+        <v>126.79</v>
       </c>
       <c r="L72" t="n">
-        <v>153.23</v>
+        <v>132.67</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>179.59</v>
+        <v>172.11</v>
       </c>
       <c r="K73" t="n">
-        <v>-26.57</v>
+        <v>-25.46</v>
       </c>
       <c r="L73" t="n">
-        <v>181.55</v>
+        <v>173.98</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-44.75</v>
+        <v>-43.77</v>
       </c>
       <c r="K74" t="n">
-        <v>63.54</v>
+        <v>62.16</v>
       </c>
       <c r="L74" t="n">
-        <v>77.72</v>
+        <v>76.03</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>30</v>
       </c>
       <c r="J75" t="n">
-        <v>65.15000000000001</v>
+        <v>56.15</v>
       </c>
       <c r="K75" t="n">
-        <v>28.52</v>
+        <v>24.58</v>
       </c>
       <c r="L75" t="n">
-        <v>71.12</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>22.71</v>
+        <v>20.74</v>
       </c>
       <c r="K76" t="n">
-        <v>87.55</v>
+        <v>79.94</v>
       </c>
       <c r="L76" t="n">
-        <v>90.45</v>
+        <v>82.58</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>59.47</v>
+        <v>59.46</v>
       </c>
       <c r="K77" t="n">
         <v>44.05</v>
       </c>
       <c r="L77" t="n">
-        <v>74</v>
+        <v>73.98999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>-59.9</v>
+        <v>-54.65</v>
       </c>
       <c r="K78" t="n">
-        <v>-17.55</v>
+        <v>-16.01</v>
       </c>
       <c r="L78" t="n">
-        <v>62.42</v>
+        <v>56.95</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-86.86</v>
+        <v>-84.8</v>
       </c>
       <c r="K79" t="n">
-        <v>39.95</v>
+        <v>39</v>
       </c>
       <c r="L79" t="n">
-        <v>95.61</v>
+        <v>93.34</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-64.41</v>
+        <v>-61.66</v>
       </c>
       <c r="K80" t="n">
-        <v>86.68000000000001</v>
+        <v>82.98</v>
       </c>
       <c r="L80" t="n">
-        <v>107.99</v>
+        <v>103.38</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>-39.44</v>
+        <v>-35.04</v>
       </c>
       <c r="K81" t="n">
-        <v>-75.22</v>
+        <v>-66.84999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>84.93000000000001</v>
+        <v>75.48</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-95.79000000000001</v>
+        <v>-91.69</v>
       </c>
       <c r="K82" t="n">
-        <v>-15.27</v>
+        <v>-14.61</v>
       </c>
       <c r="L82" t="n">
-        <v>97</v>
+        <v>92.84</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>175.86</v>
+        <v>172.27</v>
       </c>
       <c r="K83" t="n">
-        <v>71.56</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>189.86</v>
+        <v>185.98</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>14.84</v>
+        <v>13.56</v>
       </c>
       <c r="K84" t="n">
-        <v>125.39</v>
+        <v>114.57</v>
       </c>
       <c r="L84" t="n">
-        <v>126.27</v>
+        <v>115.37</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>29</v>
       </c>
       <c r="J85" t="n">
-        <v>14.41</v>
+        <v>12.82</v>
       </c>
       <c r="K85" t="n">
-        <v>-160.95</v>
+        <v>-143.15</v>
       </c>
       <c r="L85" t="n">
-        <v>161.59</v>
+        <v>143.72</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>29</v>
       </c>
       <c r="J86" t="n">
-        <v>257.05</v>
+        <v>229.11</v>
       </c>
       <c r="K86" t="n">
-        <v>140.85</v>
+        <v>125.54</v>
       </c>
       <c r="L86" t="n">
-        <v>293.11</v>
+        <v>261.25</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>45.45</v>
+        <v>43.67</v>
       </c>
       <c r="K87" t="n">
-        <v>168.7</v>
+        <v>162.09</v>
       </c>
       <c r="L87" t="n">
-        <v>174.72</v>
+        <v>167.87</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-187.33</v>
+        <v>-179.53</v>
       </c>
       <c r="K88" t="n">
-        <v>84.17</v>
+        <v>80.66</v>
       </c>
       <c r="L88" t="n">
-        <v>205.37</v>
+        <v>196.81</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-22.xlsx
+++ b/output/2024-05-22.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="F14" t="n">
-        <v>5.15</v>
+        <v>6.27</v>
       </c>
       <c r="G14" t="n">
-        <v>57.5</v>
+        <v>63</v>
       </c>
       <c r="H14" t="n">
-        <v>6.4</v>
+        <v>26.3</v>
       </c>
       <c r="I14" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>35.81</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>22.29</v>
+        <v>37.57</v>
       </c>
       <c r="L14" t="n">
-        <v>42.18</v>
+        <v>38.56</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:50:24</t>
+          <t>04:50:15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="F15" t="n">
-        <v>8.35</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>56.4</v>
+        <v>54</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>23.9</v>
       </c>
       <c r="I15" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>56.7</v>
+        <v>-36.19</v>
       </c>
       <c r="K15" t="n">
-        <v>-16.55</v>
+        <v>55.29</v>
       </c>
       <c r="L15" t="n">
-        <v>59.07</v>
+        <v>66.08</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:52:00</t>
+          <t>04:50:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.09</v>
+        <v>2.58</v>
       </c>
       <c r="F16" t="n">
-        <v>7.18</v>
+        <v>3.26</v>
       </c>
       <c r="G16" t="n">
-        <v>52.3</v>
+        <v>60.2</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="I16" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J16" t="n">
-        <v>-56.5</v>
+        <v>23.88</v>
       </c>
       <c r="K16" t="n">
-        <v>-24.84</v>
+        <v>14.93</v>
       </c>
       <c r="L16" t="n">
-        <v>61.71</v>
+        <v>28.17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:55:27</t>
+          <t>04:57:05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="F17" t="n">
-        <v>9.15</v>
+        <v>11.04</v>
       </c>
       <c r="G17" t="n">
-        <v>50.6</v>
+        <v>46.7</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6</v>
+        <v>64.2</v>
       </c>
       <c r="I17" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>6.38</v>
+        <v>-10.16</v>
       </c>
       <c r="K17" t="n">
-        <v>-20.33</v>
+        <v>59.21</v>
       </c>
       <c r="L17" t="n">
-        <v>21.31</v>
+        <v>60.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:57:07</t>
+          <t>04:58:18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.88</v>
+        <v>2.97</v>
       </c>
       <c r="F18" t="n">
-        <v>10.34</v>
+        <v>8.82</v>
       </c>
       <c r="G18" t="n">
-        <v>62.6</v>
+        <v>49.5</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3</v>
+        <v>24.2</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J18" t="n">
-        <v>-79.06</v>
+        <v>-3.47</v>
       </c>
       <c r="K18" t="n">
-        <v>53.99</v>
+        <v>12.42</v>
       </c>
       <c r="L18" t="n">
-        <v>95.73</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:58:30</t>
+          <t>05:00:13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.85</v>
+        <v>3.49</v>
       </c>
       <c r="F19" t="n">
-        <v>5.95</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>47.4</v>
+        <v>60.4</v>
       </c>
       <c r="H19" t="n">
-        <v>7.9</v>
+        <v>36.7</v>
       </c>
       <c r="I19" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J19" t="n">
-        <v>20.18</v>
+        <v>-11.24</v>
       </c>
       <c r="K19" t="n">
-        <v>-43.93</v>
+        <v>102.06</v>
       </c>
       <c r="L19" t="n">
-        <v>48.34</v>
+        <v>102.67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:03:17</t>
+          <t>05:04:51</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.99</v>
+        <v>3.36</v>
       </c>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>11.04</v>
       </c>
       <c r="G20" t="n">
-        <v>51.9</v>
+        <v>44.5</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>34.1</v>
       </c>
       <c r="I20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>30.59</v>
+        <v>-83.5</v>
       </c>
       <c r="K20" t="n">
-        <v>-104.93</v>
+        <v>111.06</v>
       </c>
       <c r="L20" t="n">
-        <v>109.3</v>
+        <v>138.95</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:05:50</t>
+          <t>05:06:32</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="F21" t="n">
-        <v>7.88</v>
+        <v>8.84</v>
       </c>
       <c r="G21" t="n">
-        <v>45.8</v>
+        <v>55.5</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="I21" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J21" t="n">
-        <v>20.35</v>
+        <v>21.36</v>
       </c>
       <c r="K21" t="n">
-        <v>9.48</v>
+        <v>117.53</v>
       </c>
       <c r="L21" t="n">
-        <v>22.45</v>
+        <v>119.46</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:07:53</t>
+          <t>05:08:01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="F22" t="n">
-        <v>6.9</v>
+        <v>11.04</v>
       </c>
       <c r="G22" t="n">
-        <v>49.7</v>
+        <v>55.1</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>40.9</v>
       </c>
       <c r="I22" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J22" t="n">
-        <v>87.45</v>
+        <v>-104.61</v>
       </c>
       <c r="K22" t="n">
-        <v>-12.61</v>
+        <v>-25.18</v>
       </c>
       <c r="L22" t="n">
-        <v>88.34999999999999</v>
+        <v>107.59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:11:48</t>
+          <t>05:13:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.46</v>
+        <v>3.04</v>
       </c>
       <c r="F23" t="n">
-        <v>8.880000000000001</v>
+        <v>7.23</v>
       </c>
       <c r="G23" t="n">
-        <v>48.4</v>
+        <v>46.1</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3</v>
+        <v>53.1</v>
       </c>
       <c r="I23" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J23" t="n">
-        <v>51.23</v>
+        <v>51.47</v>
       </c>
       <c r="K23" t="n">
-        <v>-128.24</v>
+        <v>110.3</v>
       </c>
       <c r="L23" t="n">
-        <v>138.09</v>
+        <v>121.72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:13:59</t>
+          <t>05:14:36</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.98</v>
+        <v>3.27</v>
       </c>
       <c r="F24" t="n">
-        <v>9.83</v>
+        <v>11.04</v>
       </c>
       <c r="G24" t="n">
-        <v>52</v>
+        <v>51.4</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J24" t="n">
-        <v>155.78</v>
+        <v>172.24</v>
       </c>
       <c r="K24" t="n">
-        <v>19.1</v>
+        <v>-89.44</v>
       </c>
       <c r="L24" t="n">
-        <v>156.95</v>
+        <v>194.08</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:16:18</t>
+          <t>05:16:41</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.6</v>
+        <v>2.89</v>
       </c>
       <c r="F25" t="n">
-        <v>9.039999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>62</v>
+        <v>60.3</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>56.6</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J25" t="n">
-        <v>-74.52</v>
+        <v>86.12</v>
       </c>
       <c r="K25" t="n">
-        <v>95.64</v>
+        <v>-67.72</v>
       </c>
       <c r="L25" t="n">
-        <v>121.25</v>
+        <v>109.55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:22:05</t>
+          <t>05:21:46</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.44</v>
+        <v>2.89</v>
       </c>
       <c r="F26" t="n">
-        <v>11.04</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>40</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J26" t="n">
-        <v>-215.77</v>
+        <v>183.08</v>
       </c>
       <c r="K26" t="n">
-        <v>48.62</v>
+        <v>-57.69</v>
       </c>
       <c r="L26" t="n">
-        <v>221.18</v>
+        <v>191.96</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:22:45</t>
+          <t>05:23:43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="F27" t="n">
-        <v>7.34</v>
+        <v>8.1</v>
       </c>
       <c r="G27" t="n">
-        <v>55.4</v>
+        <v>63.4</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>49.1</v>
       </c>
       <c r="I27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-62.49</v>
+        <v>64.34</v>
       </c>
       <c r="K27" t="n">
-        <v>153.34</v>
+        <v>-173.62</v>
       </c>
       <c r="L27" t="n">
-        <v>165.59</v>
+        <v>185.15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:23:55</t>
+          <t>05:25:09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="F28" t="n">
-        <v>6.9</v>
+        <v>7.42</v>
       </c>
       <c r="G28" t="n">
-        <v>54</v>
+        <v>59.8</v>
       </c>
       <c r="H28" t="n">
-        <v>4.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>131.04</v>
+        <v>205.89</v>
       </c>
       <c r="K28" t="n">
-        <v>249.33</v>
+        <v>-11.58</v>
       </c>
       <c r="L28" t="n">
-        <v>281.66</v>
+        <v>206.21</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:31:25</t>
+          <t>05:34:23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>10.42</v>
+        <v>9.67</v>
       </c>
       <c r="G29" t="n">
-        <v>44.8</v>
+        <v>60.3</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1</v>
+        <v>33.1</v>
       </c>
       <c r="I29" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-37.26</v>
+        <v>34.7</v>
       </c>
       <c r="K29" t="n">
-        <v>-23.32</v>
+        <v>-35.47</v>
       </c>
       <c r="L29" t="n">
-        <v>43.95</v>
+        <v>49.62</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:32:55</t>
+          <t>05:35:56</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.21</v>
+        <v>2.86</v>
       </c>
       <c r="F30" t="n">
-        <v>8.58</v>
+        <v>9.24</v>
       </c>
       <c r="G30" t="n">
-        <v>49.1</v>
+        <v>41</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>26.8</v>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>24.55</v>
+        <v>-13.27</v>
       </c>
       <c r="K30" t="n">
-        <v>47.3</v>
+        <v>35.94</v>
       </c>
       <c r="L30" t="n">
-        <v>53.29</v>
+        <v>38.31</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:34:00</t>
+          <t>05:37:10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="F31" t="n">
-        <v>9.130000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="G31" t="n">
-        <v>61</v>
+        <v>51.1</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>27.6</v>
       </c>
       <c r="I31" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J31" t="n">
-        <v>48.88</v>
+        <v>9.43</v>
       </c>
       <c r="K31" t="n">
-        <v>-29.21</v>
+        <v>59.34</v>
       </c>
       <c r="L31" t="n">
-        <v>56.95</v>
+        <v>60.08</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:38:11</t>
+          <t>05:41:37</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="F32" t="n">
-        <v>10.68</v>
+        <v>7.97</v>
       </c>
       <c r="G32" t="n">
-        <v>53.3</v>
+        <v>58.7</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>37.4</v>
       </c>
       <c r="I32" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>-48.61</v>
+        <v>57.04</v>
       </c>
       <c r="K32" t="n">
-        <v>29.95</v>
+        <v>-73.76000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>57.1</v>
+        <v>93.25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:40:55</t>
+          <t>05:44:02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="F33" t="n">
-        <v>6.24</v>
+        <v>11.04</v>
       </c>
       <c r="G33" t="n">
-        <v>50.6</v>
+        <v>30.4</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>58.1</v>
       </c>
       <c r="I33" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>58.91</v>
+        <v>-12.44</v>
       </c>
       <c r="K33" t="n">
-        <v>-25.05</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>64.01000000000001</v>
+        <v>83.42</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:42:21</t>
+          <t>05:46:09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.91</v>
+        <v>3.27</v>
       </c>
       <c r="F34" t="n">
-        <v>10.26</v>
+        <v>10.97</v>
       </c>
       <c r="G34" t="n">
-        <v>54.3</v>
+        <v>51.3</v>
       </c>
       <c r="H34" t="n">
-        <v>4.5</v>
+        <v>61.2</v>
       </c>
       <c r="I34" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>-60.64</v>
+        <v>-70.89</v>
       </c>
       <c r="K34" t="n">
-        <v>10.36</v>
+        <v>-45.88</v>
       </c>
       <c r="L34" t="n">
-        <v>61.52</v>
+        <v>84.44</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:48:34</t>
+          <t>05:50:13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.31</v>
+        <v>2.59</v>
       </c>
       <c r="F35" t="n">
-        <v>8.59</v>
+        <v>6.8</v>
       </c>
       <c r="G35" t="n">
-        <v>67</v>
+        <v>70.2</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="I35" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-75.77</v>
+        <v>-67.75</v>
       </c>
       <c r="K35" t="n">
-        <v>-18</v>
+        <v>73.59</v>
       </c>
       <c r="L35" t="n">
-        <v>77.88</v>
+        <v>100.02</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:50:28</t>
+          <t>05:52:04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.11</v>
+        <v>3.38</v>
       </c>
       <c r="F36" t="n">
-        <v>6.93</v>
+        <v>6.28</v>
       </c>
       <c r="G36" t="n">
-        <v>47.3</v>
+        <v>53.5</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I36" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-53.26</v>
+        <v>95.06</v>
       </c>
       <c r="K36" t="n">
-        <v>18.75</v>
+        <v>-84.13</v>
       </c>
       <c r="L36" t="n">
-        <v>56.47</v>
+        <v>126.94</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:51:42</t>
+          <t>05:54:14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.33</v>
+        <v>3.28</v>
       </c>
       <c r="F37" t="n">
-        <v>10.2</v>
+        <v>10.63</v>
       </c>
       <c r="G37" t="n">
-        <v>35.4</v>
+        <v>52</v>
       </c>
       <c r="H37" t="n">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="I37" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>70.28</v>
+        <v>-112.22</v>
       </c>
       <c r="K37" t="n">
-        <v>57.02</v>
+        <v>-32.53</v>
       </c>
       <c r="L37" t="n">
-        <v>90.5</v>
+        <v>116.84</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:56:33</t>
+          <t>05:58:47</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="F38" t="n">
-        <v>6.5</v>
+        <v>7.77</v>
       </c>
       <c r="G38" t="n">
-        <v>38.8</v>
+        <v>58.6</v>
       </c>
       <c r="H38" t="n">
-        <v>0.7</v>
+        <v>48.7</v>
       </c>
       <c r="I38" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J38" t="n">
-        <v>105.47</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>-12.42</v>
+        <v>-98.38</v>
       </c>
       <c r="L38" t="n">
-        <v>106.19</v>
+        <v>98.84999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:58:47</t>
+          <t>06:00:58</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.34</v>
+        <v>3.05</v>
       </c>
       <c r="F39" t="n">
-        <v>8.35</v>
+        <v>7.03</v>
       </c>
       <c r="G39" t="n">
-        <v>47.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5</v>
+        <v>35.1</v>
       </c>
       <c r="I39" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J39" t="n">
-        <v>59.95</v>
+        <v>-62.67</v>
       </c>
       <c r="K39" t="n">
-        <v>134.65</v>
+        <v>-107.78</v>
       </c>
       <c r="L39" t="n">
-        <v>147.39</v>
+        <v>124.68</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:00:46</t>
+          <t>06:02:34</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="F40" t="n">
-        <v>6.33</v>
+        <v>7.76</v>
       </c>
       <c r="G40" t="n">
-        <v>54.6</v>
+        <v>49.9</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="I40" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-82.92</v>
+        <v>7.86</v>
       </c>
       <c r="K40" t="n">
-        <v>-15.36</v>
+        <v>-171.65</v>
       </c>
       <c r="L40" t="n">
-        <v>84.33</v>
+        <v>171.83</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:06:23</t>
+          <t>06:07:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.52</v>
+        <v>3.37</v>
       </c>
       <c r="F41" t="n">
-        <v>7.92</v>
+        <v>10.71</v>
       </c>
       <c r="G41" t="n">
-        <v>54.6</v>
+        <v>46.9</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>33.7</v>
       </c>
       <c r="I41" t="n">
         <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>132.21</v>
+        <v>18.49</v>
       </c>
       <c r="K41" t="n">
-        <v>9.35</v>
+        <v>-212.77</v>
       </c>
       <c r="L41" t="n">
-        <v>132.54</v>
+        <v>213.57</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:08:10</t>
+          <t>06:08:11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="F42" t="n">
-        <v>6.88</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>53.3</v>
+        <v>56.8</v>
       </c>
       <c r="H42" t="n">
-        <v>8.6</v>
+        <v>22.2</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J42" t="n">
-        <v>-4.5</v>
+        <v>200.1</v>
       </c>
       <c r="K42" t="n">
-        <v>-37.31</v>
+        <v>59.72</v>
       </c>
       <c r="L42" t="n">
-        <v>37.58</v>
+        <v>208.83</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:10:13</t>
+          <t>06:09:37</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.07</v>
+        <v>3.33</v>
       </c>
       <c r="F43" t="n">
-        <v>8.32</v>
+        <v>7.96</v>
       </c>
       <c r="G43" t="n">
-        <v>45.5</v>
+        <v>51.2</v>
       </c>
       <c r="H43" t="n">
-        <v>4.7</v>
+        <v>51.1</v>
       </c>
       <c r="I43" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J43" t="n">
-        <v>-62.72</v>
+        <v>17.06</v>
       </c>
       <c r="K43" t="n">
-        <v>176.24</v>
+        <v>185.15</v>
       </c>
       <c r="L43" t="n">
-        <v>187.06</v>
+        <v>185.94</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:20:14</t>
+          <t>06:19:22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.97</v>
+        <v>4.54</v>
       </c>
       <c r="F44" t="n">
-        <v>10.04</v>
+        <v>11.04</v>
       </c>
       <c r="G44" t="n">
-        <v>44.1</v>
+        <v>42.6</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="I44" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J44" t="n">
-        <v>41.06</v>
+        <v>-44.79</v>
       </c>
       <c r="K44" t="n">
-        <v>-57.12</v>
+        <v>-18.36</v>
       </c>
       <c r="L44" t="n">
-        <v>70.34999999999999</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:21:30</t>
+          <t>06:21:12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="F45" t="n">
-        <v>10.12</v>
+        <v>8.08</v>
       </c>
       <c r="G45" t="n">
-        <v>47.3</v>
+        <v>70.8</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>49.7</v>
       </c>
       <c r="I45" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-17.59</v>
+        <v>52.9</v>
       </c>
       <c r="K45" t="n">
-        <v>-80.08</v>
+        <v>-50.5</v>
       </c>
       <c r="L45" t="n">
-        <v>81.98</v>
+        <v>73.13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:23:37</t>
+          <t>06:23:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="F46" t="n">
-        <v>10.54</v>
+        <v>9.93</v>
       </c>
       <c r="G46" t="n">
-        <v>55.2</v>
+        <v>54.6</v>
       </c>
       <c r="H46" t="n">
-        <v>5.6</v>
+        <v>8.5</v>
       </c>
       <c r="I46" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>7.45</v>
+        <v>-13.51</v>
       </c>
       <c r="K46" t="n">
-        <v>63.19</v>
+        <v>62.76</v>
       </c>
       <c r="L46" t="n">
-        <v>63.62</v>
+        <v>64.19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:28:06</t>
+          <t>06:28:09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="F47" t="n">
-        <v>9.48</v>
+        <v>7.94</v>
       </c>
       <c r="G47" t="n">
-        <v>51.6</v>
+        <v>51.1</v>
       </c>
       <c r="H47" t="n">
-        <v>4.6</v>
+        <v>42.7</v>
       </c>
       <c r="I47" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>85.84999999999999</v>
+        <v>-23.46</v>
       </c>
       <c r="K47" t="n">
-        <v>12.91</v>
+        <v>114.22</v>
       </c>
       <c r="L47" t="n">
-        <v>86.81999999999999</v>
+        <v>116.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:29:19</t>
+          <t>06:30:42</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="F48" t="n">
-        <v>7.66</v>
+        <v>11.04</v>
       </c>
       <c r="G48" t="n">
-        <v>65.2</v>
+        <v>56.1</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="I48" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-21.24</v>
+        <v>56.06</v>
       </c>
       <c r="K48" t="n">
-        <v>6.73</v>
+        <v>68.31</v>
       </c>
       <c r="L48" t="n">
-        <v>22.28</v>
+        <v>88.36</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:30:31</t>
+          <t>06:32:19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.54</v>
+        <v>3.21</v>
       </c>
       <c r="F49" t="n">
-        <v>5.9</v>
+        <v>10.09</v>
       </c>
       <c r="G49" t="n">
-        <v>59.7</v>
+        <v>46.9</v>
       </c>
       <c r="H49" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I49" t="n">
         <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>-54</v>
+        <v>-36.04</v>
       </c>
       <c r="K49" t="n">
-        <v>23.31</v>
+        <v>45.74</v>
       </c>
       <c r="L49" t="n">
-        <v>58.81</v>
+        <v>58.23</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:34:53</t>
+          <t>06:36:55</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.47</v>
+        <v>3.24</v>
       </c>
       <c r="F50" t="n">
-        <v>11.04</v>
+        <v>10.58</v>
       </c>
       <c r="G50" t="n">
-        <v>52</v>
+        <v>32.9</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>57.9</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J50" t="n">
-        <v>81.09999999999999</v>
+        <v>-11.58</v>
       </c>
       <c r="K50" t="n">
-        <v>34.48</v>
+        <v>162.21</v>
       </c>
       <c r="L50" t="n">
-        <v>88.13</v>
+        <v>162.62</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:36:30</t>
+          <t>06:39:26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2182,31 +2182,31 @@
         <v>3.21</v>
       </c>
       <c r="F51" t="n">
-        <v>7.23</v>
+        <v>10.99</v>
       </c>
       <c r="G51" t="n">
-        <v>52.2</v>
+        <v>59.3</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>32.7</v>
       </c>
       <c r="I51" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J51" t="n">
-        <v>18.96</v>
+        <v>39.51</v>
       </c>
       <c r="K51" t="n">
-        <v>-7.83</v>
+        <v>-130.6</v>
       </c>
       <c r="L51" t="n">
-        <v>20.51</v>
+        <v>136.44</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:38:45</t>
+          <t>06:41:55</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.05</v>
+        <v>2.64</v>
       </c>
       <c r="F52" t="n">
-        <v>8.58</v>
+        <v>6.22</v>
       </c>
       <c r="G52" t="n">
-        <v>53.5</v>
+        <v>49.7</v>
       </c>
       <c r="H52" t="n">
-        <v>4.3</v>
+        <v>34.9</v>
       </c>
       <c r="I52" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>-67.61</v>
+        <v>-59.92</v>
       </c>
       <c r="K52" t="n">
-        <v>17.17</v>
+        <v>102.35</v>
       </c>
       <c r="L52" t="n">
-        <v>69.75</v>
+        <v>118.6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:41:45</t>
+          <t>06:46:46</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.52</v>
+        <v>3.61</v>
       </c>
       <c r="F53" t="n">
-        <v>10.93</v>
+        <v>11.04</v>
       </c>
       <c r="G53" t="n">
-        <v>50.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="I53" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>28.04</v>
+        <v>161.36</v>
       </c>
       <c r="K53" t="n">
-        <v>142.96</v>
+        <v>101.53</v>
       </c>
       <c r="L53" t="n">
-        <v>145.69</v>
+        <v>190.65</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:44:12</t>
+          <t>06:48:56</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="F54" t="n">
-        <v>7.36</v>
+        <v>11.04</v>
       </c>
       <c r="G54" t="n">
-        <v>44</v>
+        <v>56.5</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>33.8</v>
       </c>
       <c r="I54" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J54" t="n">
-        <v>64.16</v>
+        <v>44.31</v>
       </c>
       <c r="K54" t="n">
-        <v>-79.17</v>
+        <v>202.28</v>
       </c>
       <c r="L54" t="n">
-        <v>101.91</v>
+        <v>207.08</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:45:23</t>
+          <t>06:50:14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.19</v>
+        <v>3.34</v>
       </c>
       <c r="F55" t="n">
-        <v>11.04</v>
+        <v>6.85</v>
       </c>
       <c r="G55" t="n">
-        <v>61.5</v>
+        <v>62</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>52.9</v>
       </c>
       <c r="I55" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>207.18</v>
+        <v>177.58</v>
       </c>
       <c r="K55" t="n">
-        <v>-32.67</v>
+        <v>-84.81999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>209.74</v>
+        <v>196.8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:50:44</t>
+          <t>06:55:36</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.58</v>
+        <v>3.12</v>
       </c>
       <c r="F56" t="n">
-        <v>9.359999999999999</v>
+        <v>10.52</v>
       </c>
       <c r="G56" t="n">
-        <v>61</v>
+        <v>53.5</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="I56" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-173.21</v>
+        <v>-110.43</v>
       </c>
       <c r="K56" t="n">
-        <v>-152.59</v>
+        <v>-191.28</v>
       </c>
       <c r="L56" t="n">
-        <v>230.83</v>
+        <v>220.87</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:52:30</t>
+          <t>06:57:11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="F57" t="n">
-        <v>6.86</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>46.3</v>
+        <v>59.9</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>43.9</v>
       </c>
       <c r="I57" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J57" t="n">
-        <v>-88.5</v>
+        <v>-198.42</v>
       </c>
       <c r="K57" t="n">
-        <v>86.66</v>
+        <v>36.25</v>
       </c>
       <c r="L57" t="n">
-        <v>123.87</v>
+        <v>201.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:53:30</t>
+          <t>06:58:16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.51</v>
+        <v>3.05</v>
       </c>
       <c r="F58" t="n">
-        <v>10.04</v>
+        <v>10.94</v>
       </c>
       <c r="G58" t="n">
-        <v>48.5</v>
+        <v>59.1</v>
       </c>
       <c r="H58" t="n">
-        <v>4.5</v>
+        <v>68.3</v>
       </c>
       <c r="I58" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-8.67</v>
+        <v>6.48</v>
       </c>
       <c r="K58" t="n">
-        <v>-219.11</v>
+        <v>164.42</v>
       </c>
       <c r="L58" t="n">
-        <v>219.28</v>
+        <v>164.55</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:05:21</t>
+          <t>07:05:10</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.37</v>
+        <v>3.52</v>
       </c>
       <c r="F59" t="n">
-        <v>6.36</v>
+        <v>9.84</v>
       </c>
       <c r="G59" t="n">
-        <v>42</v>
+        <v>63.1</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>37.3</v>
       </c>
       <c r="I59" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-25.73</v>
+        <v>46.32</v>
       </c>
       <c r="K59" t="n">
-        <v>41.28</v>
+        <v>16.85</v>
       </c>
       <c r="L59" t="n">
-        <v>48.64</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:06:58</t>
+          <t>07:07:03</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.14</v>
+        <v>3.53</v>
       </c>
       <c r="F60" t="n">
-        <v>9.67</v>
+        <v>6.39</v>
       </c>
       <c r="G60" t="n">
-        <v>61.2</v>
+        <v>47.9</v>
       </c>
       <c r="H60" t="n">
-        <v>2.4</v>
+        <v>45.9</v>
       </c>
       <c r="I60" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>35.33</v>
+        <v>47.64</v>
       </c>
       <c r="K60" t="n">
-        <v>47.92</v>
+        <v>-20.39</v>
       </c>
       <c r="L60" t="n">
-        <v>59.53</v>
+        <v>51.82</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:08:31</t>
+          <t>07:08:19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.43</v>
+        <v>4.13</v>
       </c>
       <c r="F61" t="n">
-        <v>7.43</v>
+        <v>10.01</v>
       </c>
       <c r="G61" t="n">
-        <v>51.8</v>
+        <v>67.3</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>-50.51</v>
+        <v>51.89</v>
       </c>
       <c r="K61" t="n">
-        <v>60.59</v>
+        <v>-25.31</v>
       </c>
       <c r="L61" t="n">
-        <v>78.88</v>
+        <v>57.73</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:13:55</t>
+          <t>07:12:44</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.38</v>
+        <v>3.21</v>
       </c>
       <c r="F62" t="n">
-        <v>9.119999999999999</v>
+        <v>11.04</v>
       </c>
       <c r="G62" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>36.1</v>
       </c>
       <c r="I62" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J62" t="n">
-        <v>63.5</v>
+        <v>77.88</v>
       </c>
       <c r="K62" t="n">
-        <v>-12.65</v>
+        <v>0.6</v>
       </c>
       <c r="L62" t="n">
-        <v>64.73999999999999</v>
+        <v>77.88</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:15:48</t>
+          <t>07:14:39</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.72</v>
+        <v>3.41</v>
       </c>
       <c r="F63" t="n">
-        <v>11.04</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>47.6</v>
+        <v>47.9</v>
       </c>
       <c r="H63" t="n">
-        <v>5.7</v>
+        <v>26.2</v>
       </c>
       <c r="I63" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>42.74</v>
+        <v>61.63</v>
       </c>
       <c r="K63" t="n">
-        <v>-49</v>
+        <v>-6.55</v>
       </c>
       <c r="L63" t="n">
-        <v>65.02</v>
+        <v>61.98</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:18:24</t>
+          <t>07:16:17</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.89</v>
+        <v>3.58</v>
       </c>
       <c r="F64" t="n">
-        <v>11.04</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G64" t="n">
-        <v>60.4</v>
+        <v>49.3</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>34.5</v>
       </c>
       <c r="I64" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.41</v>
+        <v>54.11</v>
       </c>
       <c r="K64" t="n">
-        <v>91.69</v>
+        <v>-81.33</v>
       </c>
       <c r="L64" t="n">
-        <v>91.72</v>
+        <v>97.68000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:22:59</t>
+          <t>07:19:38</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.22</v>
+        <v>3.09</v>
       </c>
       <c r="F65" t="n">
-        <v>10.23</v>
+        <v>10.76</v>
       </c>
       <c r="G65" t="n">
-        <v>55.2</v>
+        <v>61.5</v>
       </c>
       <c r="H65" t="n">
-        <v>0.9</v>
+        <v>21.5</v>
       </c>
       <c r="I65" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>77.86</v>
+        <v>86.36</v>
       </c>
       <c r="K65" t="n">
-        <v>38.78</v>
+        <v>-45.25</v>
       </c>
       <c r="L65" t="n">
-        <v>86.98999999999999</v>
+        <v>97.48999999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:25:04</t>
+          <t>07:21:07</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.39</v>
+        <v>3.96</v>
       </c>
       <c r="F66" t="n">
-        <v>9.74</v>
+        <v>9.56</v>
       </c>
       <c r="G66" t="n">
-        <v>56.2</v>
+        <v>58.6</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>158.9</v>
+        <v>122.74</v>
       </c>
       <c r="K66" t="n">
-        <v>-72.61</v>
+        <v>70.27</v>
       </c>
       <c r="L66" t="n">
-        <v>174.7</v>
+        <v>141.43</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:27:02</t>
+          <t>07:22:05</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.24</v>
+        <v>3.47</v>
       </c>
       <c r="F67" t="n">
-        <v>11.04</v>
+        <v>10.3</v>
       </c>
       <c r="G67" t="n">
-        <v>57.1</v>
+        <v>76</v>
       </c>
       <c r="H67" t="n">
-        <v>1.7</v>
+        <v>33.6</v>
       </c>
       <c r="I67" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>100.89</v>
+        <v>-89.52</v>
       </c>
       <c r="K67" t="n">
-        <v>95.17</v>
+        <v>-57.96</v>
       </c>
       <c r="L67" t="n">
-        <v>138.7</v>
+        <v>106.64</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:32:04</t>
+          <t>07:26:56</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.43</v>
+        <v>3.49</v>
       </c>
       <c r="F68" t="n">
         <v>11.04</v>
       </c>
       <c r="G68" t="n">
-        <v>53.6</v>
+        <v>54.2</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>43.2</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>81.8</v>
+        <v>-31.13</v>
       </c>
       <c r="K68" t="n">
-        <v>-164.23</v>
+        <v>160.58</v>
       </c>
       <c r="L68" t="n">
-        <v>183.48</v>
+        <v>163.57</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:33:20</t>
+          <t>07:28:56</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.48</v>
+        <v>3.13</v>
       </c>
       <c r="F69" t="n">
-        <v>8.73</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>64.3</v>
+        <v>54.6</v>
       </c>
       <c r="H69" t="n">
-        <v>2.4</v>
+        <v>30.6</v>
       </c>
       <c r="I69" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>-45.5</v>
+        <v>-17.3</v>
       </c>
       <c r="K69" t="n">
-        <v>169</v>
+        <v>140.81</v>
       </c>
       <c r="L69" t="n">
-        <v>175.02</v>
+        <v>141.87</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:34:57</t>
+          <t>07:31:01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.99</v>
+        <v>3.29</v>
       </c>
       <c r="F70" t="n">
-        <v>7.92</v>
+        <v>7.12</v>
       </c>
       <c r="G70" t="n">
-        <v>60</v>
+        <v>54.3</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>27.5</v>
       </c>
       <c r="I70" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>105.88</v>
+        <v>7.76</v>
       </c>
       <c r="K70" t="n">
-        <v>33.12</v>
+        <v>-138.44</v>
       </c>
       <c r="L70" t="n">
-        <v>110.94</v>
+        <v>138.66</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:41:34</t>
+          <t>07:36:41</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="F71" t="n">
-        <v>10.82</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="G71" t="n">
-        <v>61.8</v>
+        <v>58.7</v>
       </c>
       <c r="H71" t="n">
-        <v>0.8</v>
+        <v>29.2</v>
       </c>
       <c r="I71" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>40.04</v>
+        <v>255.42</v>
       </c>
       <c r="K71" t="n">
-        <v>-216.22</v>
+        <v>-21.98</v>
       </c>
       <c r="L71" t="n">
-        <v>219.9</v>
+        <v>256.37</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:43:55</t>
+          <t>07:38:28</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="F72" t="n">
-        <v>9.640000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="G72" t="n">
-        <v>61.2</v>
+        <v>69.2</v>
       </c>
       <c r="H72" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>-39.04</v>
+        <v>-252.39</v>
       </c>
       <c r="K72" t="n">
-        <v>126.79</v>
+        <v>33.98</v>
       </c>
       <c r="L72" t="n">
-        <v>132.67</v>
+        <v>254.67</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:45:35</t>
+          <t>07:39:44</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.58</v>
+        <v>2.95</v>
       </c>
       <c r="F73" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>62.2</v>
+        <v>55.3</v>
       </c>
       <c r="H73" t="n">
-        <v>1.5</v>
+        <v>27.9</v>
       </c>
       <c r="I73" t="n">
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>172.11</v>
+        <v>64.33</v>
       </c>
       <c r="K73" t="n">
-        <v>-25.46</v>
+        <v>-192.23</v>
       </c>
       <c r="L73" t="n">
-        <v>173.98</v>
+        <v>202.7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:55:42</t>
+          <t>07:51:48</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.53</v>
+        <v>3.47</v>
       </c>
       <c r="F74" t="n">
-        <v>11.04</v>
+        <v>11.01</v>
       </c>
       <c r="G74" t="n">
-        <v>66.09999999999999</v>
+        <v>45</v>
       </c>
       <c r="H74" t="n">
-        <v>6.1</v>
+        <v>38</v>
       </c>
       <c r="I74" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-43.77</v>
+        <v>-4.5</v>
       </c>
       <c r="K74" t="n">
-        <v>62.16</v>
+        <v>68.5</v>
       </c>
       <c r="L74" t="n">
-        <v>76.03</v>
+        <v>68.65000000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:57:00</t>
+          <t>07:53:19</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.66</v>
+        <v>3.57</v>
       </c>
       <c r="F75" t="n">
-        <v>9.75</v>
+        <v>10.9</v>
       </c>
       <c r="G75" t="n">
-        <v>60.2</v>
+        <v>61.1</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>48.1</v>
       </c>
       <c r="I75" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>56.15</v>
+        <v>55.91</v>
       </c>
       <c r="K75" t="n">
-        <v>24.58</v>
+        <v>14.33</v>
       </c>
       <c r="L75" t="n">
-        <v>61.3</v>
+        <v>57.72</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:57:55</t>
+          <t>07:55:18</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.07</v>
+        <v>3.5</v>
       </c>
       <c r="F76" t="n">
-        <v>11.04</v>
+        <v>8</v>
       </c>
       <c r="G76" t="n">
-        <v>54.6</v>
+        <v>49.3</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>50.9</v>
       </c>
       <c r="I76" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J76" t="n">
-        <v>20.74</v>
+        <v>32.86</v>
       </c>
       <c r="K76" t="n">
-        <v>79.94</v>
+        <v>-57.39</v>
       </c>
       <c r="L76" t="n">
-        <v>82.58</v>
+        <v>66.13</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:01:47</t>
+          <t>08:00:07</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.28</v>
+        <v>4.12</v>
       </c>
       <c r="F77" t="n">
-        <v>11.04</v>
+        <v>10.93</v>
       </c>
       <c r="G77" t="n">
-        <v>54.6</v>
+        <v>54.7</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>48.8</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J77" t="n">
-        <v>59.46</v>
+        <v>12.32</v>
       </c>
       <c r="K77" t="n">
-        <v>44.05</v>
+        <v>-91.95</v>
       </c>
       <c r="L77" t="n">
-        <v>73.98999999999999</v>
+        <v>92.77</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:03:38</t>
+          <t>08:01:10</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.39</v>
+        <v>3.7</v>
       </c>
       <c r="F78" t="n">
-        <v>11.04</v>
+        <v>10.24</v>
       </c>
       <c r="G78" t="n">
-        <v>55.9</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>2.8</v>
+        <v>26.9</v>
       </c>
       <c r="I78" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>-54.65</v>
+        <v>-107.95</v>
       </c>
       <c r="K78" t="n">
-        <v>-16.01</v>
+        <v>2.28</v>
       </c>
       <c r="L78" t="n">
-        <v>56.95</v>
+        <v>107.97</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:05:45</t>
+          <t>08:03:33</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.94</v>
+        <v>3.83</v>
       </c>
       <c r="F79" t="n">
-        <v>11.04</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G79" t="n">
-        <v>65.8</v>
+        <v>65.5</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>29.2</v>
       </c>
       <c r="I79" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J79" t="n">
-        <v>-84.8</v>
+        <v>40.49</v>
       </c>
       <c r="K79" t="n">
-        <v>39</v>
+        <v>85.02</v>
       </c>
       <c r="L79" t="n">
-        <v>93.34</v>
+        <v>94.17</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:10:04</t>
+          <t>08:07:37</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.84</v>
+        <v>3.77</v>
       </c>
       <c r="F80" t="n">
-        <v>10.02</v>
+        <v>10.77</v>
       </c>
       <c r="G80" t="n">
-        <v>61</v>
+        <v>59.8</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I80" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J80" t="n">
-        <v>-61.66</v>
+        <v>5.9</v>
       </c>
       <c r="K80" t="n">
-        <v>82.98</v>
+        <v>-109.89</v>
       </c>
       <c r="L80" t="n">
-        <v>103.38</v>
+        <v>110.05</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:11:53</t>
+          <t>08:09:03</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.39</v>
+        <v>3.11</v>
       </c>
       <c r="F81" t="n">
-        <v>8.199999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="G81" t="n">
-        <v>57.1</v>
+        <v>51.7</v>
       </c>
       <c r="H81" t="n">
-        <v>3</v>
+        <v>26.9</v>
       </c>
       <c r="I81" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>-35.04</v>
+        <v>17.49</v>
       </c>
       <c r="K81" t="n">
-        <v>-66.84999999999999</v>
+        <v>-29.21</v>
       </c>
       <c r="L81" t="n">
-        <v>75.48</v>
+        <v>34.05</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:13:22</t>
+          <t>08:10:56</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="F82" t="n">
-        <v>11.04</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>62</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>5.3</v>
+        <v>20.7</v>
       </c>
       <c r="I82" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>-91.69</v>
+        <v>-45.44</v>
       </c>
       <c r="K82" t="n">
-        <v>-14.61</v>
+        <v>110.79</v>
       </c>
       <c r="L82" t="n">
-        <v>92.84</v>
+        <v>119.75</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:17:21</t>
+          <t>08:15:37</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.14</v>
+        <v>3.89</v>
       </c>
       <c r="F83" t="n">
-        <v>10.5</v>
+        <v>9.58</v>
       </c>
       <c r="G83" t="n">
-        <v>60.5</v>
+        <v>49.1</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>30.3</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>172.27</v>
+        <v>-202.75</v>
       </c>
       <c r="K83" t="n">
-        <v>70.09999999999999</v>
+        <v>83.56</v>
       </c>
       <c r="L83" t="n">
-        <v>185.98</v>
+        <v>219.29</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:19:20</t>
+          <t>08:17:52</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.87</v>
+        <v>3.37</v>
       </c>
       <c r="F84" t="n">
-        <v>11.04</v>
+        <v>10.79</v>
       </c>
       <c r="G84" t="n">
-        <v>54.1</v>
+        <v>44.1</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>35.8</v>
       </c>
       <c r="I84" t="n">
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>13.56</v>
+        <v>-121.68</v>
       </c>
       <c r="K84" t="n">
-        <v>114.57</v>
+        <v>-166.32</v>
       </c>
       <c r="L84" t="n">
-        <v>115.37</v>
+        <v>206.08</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:21:27</t>
+          <t>08:19:52</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="F85" t="n">
-        <v>10.93</v>
+        <v>11.04</v>
       </c>
       <c r="G85" t="n">
-        <v>57.9</v>
+        <v>40.5</v>
       </c>
       <c r="H85" t="n">
-        <v>4.4</v>
+        <v>21.7</v>
       </c>
       <c r="I85" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J85" t="n">
-        <v>12.82</v>
+        <v>-30.38</v>
       </c>
       <c r="K85" t="n">
-        <v>-143.15</v>
+        <v>-139.65</v>
       </c>
       <c r="L85" t="n">
-        <v>143.72</v>
+        <v>142.92</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:25:02</t>
+          <t>08:24:23</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.57</v>
+        <v>3.87</v>
       </c>
       <c r="F86" t="n">
-        <v>9.720000000000001</v>
+        <v>8.34</v>
       </c>
       <c r="G86" t="n">
-        <v>45.9</v>
+        <v>48.3</v>
       </c>
       <c r="H86" t="n">
-        <v>6.3</v>
+        <v>21.5</v>
       </c>
       <c r="I86" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>229.11</v>
+        <v>-73.06</v>
       </c>
       <c r="K86" t="n">
-        <v>125.54</v>
+        <v>-312.66</v>
       </c>
       <c r="L86" t="n">
-        <v>261.25</v>
+        <v>321.08</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:27:10</t>
+          <t>08:26:23</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="F87" t="n">
-        <v>8.31</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>49.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="I87" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>43.67</v>
+        <v>31.6</v>
       </c>
       <c r="K87" t="n">
-        <v>162.09</v>
+        <v>192.62</v>
       </c>
       <c r="L87" t="n">
-        <v>167.87</v>
+        <v>195.2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:29:05</t>
+          <t>08:27:24</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.19</v>
+        <v>3.39</v>
       </c>
       <c r="F88" t="n">
-        <v>9.31</v>
+        <v>11.04</v>
       </c>
       <c r="G88" t="n">
-        <v>69.8</v>
+        <v>49.7</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>28.5</v>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J88" t="n">
-        <v>-179.53</v>
+        <v>-215.19</v>
       </c>
       <c r="K88" t="n">
-        <v>80.66</v>
+        <v>-39</v>
       </c>
       <c r="L88" t="n">
-        <v>196.81</v>
+        <v>218.69</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-22.xlsx
+++ b/output/2024-05-22.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.77</v>
+        <v>3.03</v>
       </c>
       <c r="F14" t="n">
-        <v>6.27</v>
+        <v>5.58</v>
       </c>
       <c r="G14" t="n">
-        <v>63</v>
+        <v>44.9</v>
       </c>
       <c r="H14" t="n">
-        <v>26.3</v>
+        <v>14.6</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.710000000000001</v>
+        <v>-14.55</v>
       </c>
       <c r="K14" t="n">
-        <v>37.57</v>
+        <v>-47.16</v>
       </c>
       <c r="L14" t="n">
-        <v>38.56</v>
+        <v>49.35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:50:15</t>
+          <t>04:51:32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="F15" t="n">
-        <v>9.390000000000001</v>
+        <v>6.69</v>
       </c>
       <c r="G15" t="n">
-        <v>54</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>23.9</v>
+        <v>62.5</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>-36.19</v>
+        <v>39.43</v>
       </c>
       <c r="K15" t="n">
-        <v>55.29</v>
+        <v>21.54</v>
       </c>
       <c r="L15" t="n">
-        <v>66.08</v>
+        <v>44.93</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:50:56</t>
+          <t>04:53:31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.58</v>
+        <v>4.09</v>
       </c>
       <c r="F16" t="n">
-        <v>3.26</v>
+        <v>8.43</v>
       </c>
       <c r="G16" t="n">
-        <v>60.2</v>
+        <v>53.6</v>
       </c>
       <c r="H16" t="n">
-        <v>13.3</v>
+        <v>74.3</v>
       </c>
       <c r="I16" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>23.88</v>
+        <v>38.27</v>
       </c>
       <c r="K16" t="n">
-        <v>14.93</v>
+        <v>37.75</v>
       </c>
       <c r="L16" t="n">
-        <v>28.17</v>
+        <v>53.75</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:57:05</t>
+          <t>04:59:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="F17" t="n">
-        <v>11.04</v>
+        <v>8.51</v>
       </c>
       <c r="G17" t="n">
-        <v>46.7</v>
+        <v>75.7</v>
       </c>
       <c r="H17" t="n">
-        <v>64.2</v>
+        <v>29.7</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>-10.16</v>
+        <v>71.12</v>
       </c>
       <c r="K17" t="n">
-        <v>59.21</v>
+        <v>-5.6</v>
       </c>
       <c r="L17" t="n">
-        <v>60.08</v>
+        <v>71.34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:58:18</t>
+          <t>05:02:08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.97</v>
+        <v>3.17</v>
       </c>
       <c r="F18" t="n">
-        <v>8.82</v>
+        <v>6.85</v>
       </c>
       <c r="G18" t="n">
-        <v>49.5</v>
+        <v>45.8</v>
       </c>
       <c r="H18" t="n">
-        <v>24.2</v>
+        <v>44.9</v>
       </c>
       <c r="I18" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.47</v>
+        <v>-101.84</v>
       </c>
       <c r="K18" t="n">
-        <v>12.42</v>
+        <v>14.81</v>
       </c>
       <c r="L18" t="n">
-        <v>12.9</v>
+        <v>102.91</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:00:13</t>
+          <t>05:04:02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.49</v>
+        <v>2.49</v>
       </c>
       <c r="F19" t="n">
-        <v>8.529999999999999</v>
+        <v>6.26</v>
       </c>
       <c r="G19" t="n">
-        <v>60.4</v>
+        <v>46.6</v>
       </c>
       <c r="H19" t="n">
-        <v>36.7</v>
+        <v>58.9</v>
       </c>
       <c r="I19" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J19" t="n">
-        <v>-11.24</v>
+        <v>50.52</v>
       </c>
       <c r="K19" t="n">
-        <v>102.06</v>
+        <v>5.09</v>
       </c>
       <c r="L19" t="n">
-        <v>102.67</v>
+        <v>50.78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:04:51</t>
+          <t>05:09:18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.36</v>
+        <v>2.94</v>
       </c>
       <c r="F20" t="n">
-        <v>11.04</v>
+        <v>7.87</v>
       </c>
       <c r="G20" t="n">
-        <v>44.5</v>
+        <v>57.6</v>
       </c>
       <c r="H20" t="n">
-        <v>34.1</v>
+        <v>59.6</v>
       </c>
       <c r="I20" t="n">
         <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>-83.5</v>
+        <v>93.88</v>
       </c>
       <c r="K20" t="n">
-        <v>111.06</v>
+        <v>8.18</v>
       </c>
       <c r="L20" t="n">
-        <v>138.95</v>
+        <v>94.23999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:06:32</t>
+          <t>05:11:22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="F21" t="n">
-        <v>8.84</v>
+        <v>7.56</v>
       </c>
       <c r="G21" t="n">
-        <v>55.5</v>
+        <v>58.8</v>
       </c>
       <c r="H21" t="n">
-        <v>41.7</v>
+        <v>30.1</v>
       </c>
       <c r="I21" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>21.36</v>
+        <v>112.72</v>
       </c>
       <c r="K21" t="n">
-        <v>117.53</v>
+        <v>22.24</v>
       </c>
       <c r="L21" t="n">
-        <v>119.46</v>
+        <v>114.89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:08:01</t>
+          <t>05:14:01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="F22" t="n">
-        <v>11.04</v>
+        <v>7.53</v>
       </c>
       <c r="G22" t="n">
-        <v>55.1</v>
+        <v>53.7</v>
       </c>
       <c r="H22" t="n">
-        <v>40.9</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-104.61</v>
+        <v>-114.26</v>
       </c>
       <c r="K22" t="n">
-        <v>-25.18</v>
+        <v>42.44</v>
       </c>
       <c r="L22" t="n">
-        <v>107.59</v>
+        <v>121.89</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:13:04</t>
+          <t>05:17:39</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.04</v>
+        <v>2.86</v>
       </c>
       <c r="F23" t="n">
-        <v>7.23</v>
+        <v>6.66</v>
       </c>
       <c r="G23" t="n">
-        <v>46.1</v>
+        <v>63.3</v>
       </c>
       <c r="H23" t="n">
-        <v>53.1</v>
+        <v>57.2</v>
       </c>
       <c r="I23" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>51.47</v>
+        <v>-134.49</v>
       </c>
       <c r="K23" t="n">
-        <v>110.3</v>
+        <v>49.22</v>
       </c>
       <c r="L23" t="n">
-        <v>121.72</v>
+        <v>143.21</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:14:36</t>
+          <t>05:18:35</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.27</v>
+        <v>2.91</v>
       </c>
       <c r="F24" t="n">
-        <v>11.04</v>
+        <v>8.9</v>
       </c>
       <c r="G24" t="n">
-        <v>51.4</v>
+        <v>54</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>23.9</v>
       </c>
       <c r="I24" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>172.24</v>
+        <v>-123.24</v>
       </c>
       <c r="K24" t="n">
-        <v>-89.44</v>
+        <v>98.03</v>
       </c>
       <c r="L24" t="n">
-        <v>194.08</v>
+        <v>157.48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:16:41</t>
+          <t>05:21:06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.89</v>
+        <v>2.68</v>
       </c>
       <c r="F25" t="n">
-        <v>8.289999999999999</v>
+        <v>3.67</v>
       </c>
       <c r="G25" t="n">
-        <v>60.3</v>
+        <v>53.1</v>
       </c>
       <c r="H25" t="n">
-        <v>56.6</v>
+        <v>50.2</v>
       </c>
       <c r="I25" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>86.12</v>
+        <v>20.29</v>
       </c>
       <c r="K25" t="n">
-        <v>-67.72</v>
+        <v>137.54</v>
       </c>
       <c r="L25" t="n">
-        <v>109.55</v>
+        <v>139.03</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:21:46</t>
+          <t>05:26:34</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.89</v>
+        <v>3.28</v>
       </c>
       <c r="F26" t="n">
-        <v>9.109999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>66.09999999999999</v>
+        <v>46.7</v>
       </c>
       <c r="H26" t="n">
-        <v>10.1</v>
+        <v>64.2</v>
       </c>
       <c r="I26" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>183.08</v>
+        <v>-62.31</v>
       </c>
       <c r="K26" t="n">
-        <v>-57.69</v>
+        <v>155.58</v>
       </c>
       <c r="L26" t="n">
-        <v>191.96</v>
+        <v>167.59</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:23:43</t>
+          <t>05:27:43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
       <c r="F27" t="n">
-        <v>8.1</v>
+        <v>9.25</v>
       </c>
       <c r="G27" t="n">
-        <v>63.4</v>
+        <v>58.9</v>
       </c>
       <c r="H27" t="n">
-        <v>49.1</v>
+        <v>23.4</v>
       </c>
       <c r="I27" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>64.34</v>
+        <v>-69.69</v>
       </c>
       <c r="K27" t="n">
-        <v>-173.62</v>
+        <v>-188.15</v>
       </c>
       <c r="L27" t="n">
-        <v>185.15</v>
+        <v>200.65</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:25:09</t>
+          <t>05:29:35</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.06</v>
+        <v>2.56</v>
       </c>
       <c r="F28" t="n">
-        <v>7.42</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>59.8</v>
+        <v>56</v>
       </c>
       <c r="H28" t="n">
-        <v>65.59999999999999</v>
+        <v>54.2</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>205.89</v>
+        <v>-191.29</v>
       </c>
       <c r="K28" t="n">
-        <v>-11.58</v>
+        <v>90.8</v>
       </c>
       <c r="L28" t="n">
-        <v>206.21</v>
+        <v>211.75</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:34:23</t>
+          <t>05:37:52</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="F29" t="n">
-        <v>9.67</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>60.3</v>
+        <v>70.7</v>
       </c>
       <c r="H29" t="n">
-        <v>33.1</v>
+        <v>63.1</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>34.7</v>
+        <v>-10.31</v>
       </c>
       <c r="K29" t="n">
-        <v>-35.47</v>
+        <v>29.09</v>
       </c>
       <c r="L29" t="n">
-        <v>49.62</v>
+        <v>30.87</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:35:56</t>
+          <t>05:39:15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.86</v>
+        <v>3.65</v>
       </c>
       <c r="F30" t="n">
-        <v>9.24</v>
+        <v>11.04</v>
       </c>
       <c r="G30" t="n">
-        <v>41</v>
+        <v>56.6</v>
       </c>
       <c r="H30" t="n">
-        <v>26.8</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>-13.27</v>
+        <v>26.37</v>
       </c>
       <c r="K30" t="n">
-        <v>35.94</v>
+        <v>-56.06</v>
       </c>
       <c r="L30" t="n">
-        <v>38.31</v>
+        <v>61.95</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:37:10</t>
+          <t>05:41:23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.05</v>
+        <v>3.29</v>
       </c>
       <c r="F31" t="n">
-        <v>5.8</v>
+        <v>7.7</v>
       </c>
       <c r="G31" t="n">
-        <v>51.1</v>
+        <v>59.3</v>
       </c>
       <c r="H31" t="n">
-        <v>27.6</v>
+        <v>15.3</v>
       </c>
       <c r="I31" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>9.43</v>
+        <v>-63.22</v>
       </c>
       <c r="K31" t="n">
-        <v>59.34</v>
+        <v>9.01</v>
       </c>
       <c r="L31" t="n">
-        <v>60.08</v>
+        <v>63.86</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:41:37</t>
+          <t>05:47:38</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.4</v>
+        <v>2.68</v>
       </c>
       <c r="F32" t="n">
-        <v>7.97</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>58.7</v>
+        <v>59.5</v>
       </c>
       <c r="H32" t="n">
-        <v>37.4</v>
+        <v>10</v>
       </c>
       <c r="I32" t="n">
         <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>57.04</v>
+        <v>66.61</v>
       </c>
       <c r="K32" t="n">
-        <v>-73.76000000000001</v>
+        <v>-5.12</v>
       </c>
       <c r="L32" t="n">
-        <v>93.25</v>
+        <v>66.81</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:44:02</t>
+          <t>05:48:52</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.89</v>
+        <v>4.08</v>
       </c>
       <c r="F33" t="n">
         <v>11.04</v>
       </c>
       <c r="G33" t="n">
-        <v>30.4</v>
+        <v>52.9</v>
       </c>
       <c r="H33" t="n">
-        <v>58.1</v>
+        <v>40.1</v>
       </c>
       <c r="I33" t="n">
         <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>-12.44</v>
+        <v>-11.57</v>
       </c>
       <c r="K33" t="n">
-        <v>82.48999999999999</v>
+        <v>-91.11</v>
       </c>
       <c r="L33" t="n">
-        <v>83.42</v>
+        <v>91.84</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:46:09</t>
+          <t>05:51:29</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.27</v>
+        <v>3.49</v>
       </c>
       <c r="F34" t="n">
-        <v>10.97</v>
+        <v>6.73</v>
       </c>
       <c r="G34" t="n">
-        <v>51.3</v>
+        <v>78.3</v>
       </c>
       <c r="H34" t="n">
-        <v>61.2</v>
+        <v>37.4</v>
       </c>
       <c r="I34" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-70.89</v>
+        <v>40.77</v>
       </c>
       <c r="K34" t="n">
-        <v>-45.88</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>84.44</v>
+        <v>80.61</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:50:13</t>
+          <t>05:55:07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.59</v>
+        <v>3.11</v>
       </c>
       <c r="F35" t="n">
-        <v>6.8</v>
+        <v>8.67</v>
       </c>
       <c r="G35" t="n">
-        <v>70.2</v>
+        <v>41.4</v>
       </c>
       <c r="H35" t="n">
-        <v>24.5</v>
+        <v>22.4</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>-67.75</v>
+        <v>86.52</v>
       </c>
       <c r="K35" t="n">
-        <v>73.59</v>
+        <v>27.64</v>
       </c>
       <c r="L35" t="n">
-        <v>100.02</v>
+        <v>90.83</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:52:04</t>
+          <t>05:57:07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="F36" t="n">
-        <v>6.28</v>
+        <v>8.32</v>
       </c>
       <c r="G36" t="n">
-        <v>53.5</v>
+        <v>51.6</v>
       </c>
       <c r="H36" t="n">
-        <v>36</v>
+        <v>45.5</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>95.06</v>
+        <v>-112.98</v>
       </c>
       <c r="K36" t="n">
-        <v>-84.13</v>
+        <v>63.35</v>
       </c>
       <c r="L36" t="n">
-        <v>126.94</v>
+        <v>129.52</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:54:14</t>
+          <t>05:58:14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="F37" t="n">
-        <v>10.63</v>
+        <v>9.23</v>
       </c>
       <c r="G37" t="n">
-        <v>52</v>
+        <v>49.5</v>
       </c>
       <c r="H37" t="n">
-        <v>8.1</v>
+        <v>33.4</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>-112.22</v>
+        <v>-75.31</v>
       </c>
       <c r="K37" t="n">
-        <v>-32.53</v>
+        <v>81.09</v>
       </c>
       <c r="L37" t="n">
-        <v>116.84</v>
+        <v>110.67</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:58:47</t>
+          <t>06:02:30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.72</v>
+        <v>3.45</v>
       </c>
       <c r="F38" t="n">
-        <v>7.77</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>58.6</v>
+        <v>55.5</v>
       </c>
       <c r="H38" t="n">
-        <v>48.7</v>
+        <v>46.7</v>
       </c>
       <c r="I38" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>9.640000000000001</v>
+        <v>26.6</v>
       </c>
       <c r="K38" t="n">
-        <v>-98.38</v>
+        <v>-119.66</v>
       </c>
       <c r="L38" t="n">
-        <v>98.84999999999999</v>
+        <v>122.59</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:00:58</t>
+          <t>06:04:52</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="F39" t="n">
-        <v>7.03</v>
+        <v>6.61</v>
       </c>
       <c r="G39" t="n">
-        <v>79.59999999999999</v>
+        <v>55.8</v>
       </c>
       <c r="H39" t="n">
-        <v>35.1</v>
+        <v>20.7</v>
       </c>
       <c r="I39" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-62.67</v>
+        <v>3.34</v>
       </c>
       <c r="K39" t="n">
-        <v>-107.78</v>
+        <v>-173.39</v>
       </c>
       <c r="L39" t="n">
-        <v>124.68</v>
+        <v>173.42</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:02:34</t>
+          <t>06:07:10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.05</v>
+        <v>4.07</v>
       </c>
       <c r="F40" t="n">
-        <v>7.76</v>
+        <v>10.52</v>
       </c>
       <c r="G40" t="n">
-        <v>49.9</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>9.5</v>
+        <v>56.9</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>7.86</v>
+        <v>225.33</v>
       </c>
       <c r="K40" t="n">
-        <v>-171.65</v>
+        <v>18.44</v>
       </c>
       <c r="L40" t="n">
-        <v>171.83</v>
+        <v>226.08</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:07:12</t>
+          <t>06:12:04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.37</v>
+        <v>2.97</v>
       </c>
       <c r="F41" t="n">
-        <v>10.71</v>
+        <v>9.09</v>
       </c>
       <c r="G41" t="n">
-        <v>46.9</v>
+        <v>60.9</v>
       </c>
       <c r="H41" t="n">
-        <v>33.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>18.49</v>
+        <v>-229.78</v>
       </c>
       <c r="K41" t="n">
-        <v>-212.77</v>
+        <v>42.25</v>
       </c>
       <c r="L41" t="n">
-        <v>213.57</v>
+        <v>233.63</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:08:11</t>
+          <t>06:13:12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="F42" t="n">
-        <v>9.460000000000001</v>
+        <v>4.16</v>
       </c>
       <c r="G42" t="n">
-        <v>56.8</v>
+        <v>63.9</v>
       </c>
       <c r="H42" t="n">
-        <v>22.2</v>
+        <v>33.6</v>
       </c>
       <c r="I42" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>200.1</v>
+        <v>173.15</v>
       </c>
       <c r="K42" t="n">
-        <v>59.72</v>
+        <v>-103.57</v>
       </c>
       <c r="L42" t="n">
-        <v>208.83</v>
+        <v>201.76</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:09:37</t>
+          <t>06:15:21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.33</v>
+        <v>3.57</v>
       </c>
       <c r="F43" t="n">
-        <v>7.96</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>51.2</v>
+        <v>57</v>
       </c>
       <c r="H43" t="n">
-        <v>51.1</v>
+        <v>33.2</v>
       </c>
       <c r="I43" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>17.06</v>
+        <v>-150.25</v>
       </c>
       <c r="K43" t="n">
-        <v>185.15</v>
+        <v>74.55</v>
       </c>
       <c r="L43" t="n">
-        <v>185.94</v>
+        <v>167.72</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:19:22</t>
+          <t>06:24:59</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.54</v>
+        <v>3.34</v>
       </c>
       <c r="F44" t="n">
         <v>11.04</v>
       </c>
       <c r="G44" t="n">
-        <v>42.6</v>
+        <v>57</v>
       </c>
       <c r="H44" t="n">
-        <v>47</v>
+        <v>40.7</v>
       </c>
       <c r="I44" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-44.79</v>
+        <v>54.57</v>
       </c>
       <c r="K44" t="n">
-        <v>-18.36</v>
+        <v>-9.5</v>
       </c>
       <c r="L44" t="n">
-        <v>48.41</v>
+        <v>55.39</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:21:12</t>
+          <t>06:26:54</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.25</v>
+        <v>2.71</v>
       </c>
       <c r="F45" t="n">
-        <v>8.08</v>
+        <v>7.32</v>
       </c>
       <c r="G45" t="n">
-        <v>70.8</v>
+        <v>59.8</v>
       </c>
       <c r="H45" t="n">
-        <v>49.7</v>
+        <v>37.9</v>
       </c>
       <c r="I45" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>52.9</v>
+        <v>-23.02</v>
       </c>
       <c r="K45" t="n">
-        <v>-50.5</v>
+        <v>-21.1</v>
       </c>
       <c r="L45" t="n">
-        <v>73.13</v>
+        <v>31.22</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:23:30</t>
+          <t>06:28:11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.58</v>
+        <v>3.14</v>
       </c>
       <c r="F46" t="n">
-        <v>9.93</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>54.6</v>
+        <v>49.7</v>
       </c>
       <c r="H46" t="n">
-        <v>8.5</v>
+        <v>4.6</v>
       </c>
       <c r="I46" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>-13.51</v>
+        <v>42.92</v>
       </c>
       <c r="K46" t="n">
-        <v>62.76</v>
+        <v>-21.43</v>
       </c>
       <c r="L46" t="n">
-        <v>64.19</v>
+        <v>47.97</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:28:09</t>
+          <t>06:32:03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.4</v>
+        <v>4.16</v>
       </c>
       <c r="F47" t="n">
-        <v>7.94</v>
+        <v>11.04</v>
       </c>
       <c r="G47" t="n">
-        <v>51.1</v>
+        <v>55.8</v>
       </c>
       <c r="H47" t="n">
-        <v>42.7</v>
+        <v>20.6</v>
       </c>
       <c r="I47" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>-23.46</v>
+        <v>-35.47</v>
       </c>
       <c r="K47" t="n">
-        <v>114.22</v>
+        <v>-63.46</v>
       </c>
       <c r="L47" t="n">
-        <v>116.6</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:30:42</t>
+          <t>06:33:05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="F48" t="n">
-        <v>11.04</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>56.1</v>
+        <v>51.7</v>
       </c>
       <c r="H48" t="n">
-        <v>37.5</v>
+        <v>33.7</v>
       </c>
       <c r="I48" t="n">
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>56.06</v>
+        <v>-34.23</v>
       </c>
       <c r="K48" t="n">
-        <v>68.31</v>
+        <v>-55.72</v>
       </c>
       <c r="L48" t="n">
-        <v>88.36</v>
+        <v>65.39</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:32:19</t>
+          <t>06:34:50</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="F49" t="n">
-        <v>10.09</v>
+        <v>10.02</v>
       </c>
       <c r="G49" t="n">
-        <v>46.9</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>11</v>
+        <v>52.4</v>
       </c>
       <c r="I49" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-36.04</v>
+        <v>-58.19</v>
       </c>
       <c r="K49" t="n">
-        <v>45.74</v>
+        <v>-38.83</v>
       </c>
       <c r="L49" t="n">
-        <v>58.23</v>
+        <v>69.95999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:36:55</t>
+          <t>06:39:54</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.24</v>
+        <v>3.47</v>
       </c>
       <c r="F50" t="n">
-        <v>10.58</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>32.9</v>
+        <v>58.8</v>
       </c>
       <c r="H50" t="n">
-        <v>57.9</v>
+        <v>4.4</v>
       </c>
       <c r="I50" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-11.58</v>
+        <v>-108.7</v>
       </c>
       <c r="K50" t="n">
-        <v>162.21</v>
+        <v>-4.41</v>
       </c>
       <c r="L50" t="n">
-        <v>162.62</v>
+        <v>108.79</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:39:26</t>
+          <t>06:40:40</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.21</v>
+        <v>3.49</v>
       </c>
       <c r="F51" t="n">
-        <v>10.99</v>
+        <v>6.54</v>
       </c>
       <c r="G51" t="n">
-        <v>59.3</v>
+        <v>45.5</v>
       </c>
       <c r="H51" t="n">
-        <v>32.7</v>
+        <v>45.7</v>
       </c>
       <c r="I51" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>39.51</v>
+        <v>117.3</v>
       </c>
       <c r="K51" t="n">
-        <v>-130.6</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>136.44</v>
+        <v>117.69</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:41:55</t>
+          <t>06:42:50</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="F52" t="n">
-        <v>6.22</v>
+        <v>6.95</v>
       </c>
       <c r="G52" t="n">
-        <v>49.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>34.9</v>
+        <v>67.7</v>
       </c>
       <c r="I52" t="n">
         <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>-59.92</v>
+        <v>-24.45</v>
       </c>
       <c r="K52" t="n">
-        <v>102.35</v>
+        <v>86.33</v>
       </c>
       <c r="L52" t="n">
-        <v>118.6</v>
+        <v>89.73</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:46:46</t>
+          <t>06:47:10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.61</v>
+        <v>3.76</v>
       </c>
       <c r="F53" t="n">
-        <v>11.04</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>66.09999999999999</v>
+        <v>50.1</v>
       </c>
       <c r="H53" t="n">
-        <v>52</v>
+        <v>43.2</v>
       </c>
       <c r="I53" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J53" t="n">
-        <v>161.36</v>
+        <v>-33.54</v>
       </c>
       <c r="K53" t="n">
-        <v>101.53</v>
+        <v>256.71</v>
       </c>
       <c r="L53" t="n">
-        <v>190.65</v>
+        <v>258.89</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:48:56</t>
+          <t>06:48:02</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="F54" t="n">
-        <v>11.04</v>
+        <v>9.44</v>
       </c>
       <c r="G54" t="n">
-        <v>56.5</v>
+        <v>58</v>
       </c>
       <c r="H54" t="n">
-        <v>33.8</v>
+        <v>59</v>
       </c>
       <c r="I54" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>44.31</v>
+        <v>103.81</v>
       </c>
       <c r="K54" t="n">
-        <v>202.28</v>
+        <v>67.86</v>
       </c>
       <c r="L54" t="n">
-        <v>207.08</v>
+        <v>124.03</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:50:14</t>
+          <t>06:49:05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="F55" t="n">
-        <v>6.85</v>
+        <v>8.1</v>
       </c>
       <c r="G55" t="n">
-        <v>62</v>
+        <v>58.6</v>
       </c>
       <c r="H55" t="n">
-        <v>52.9</v>
+        <v>46.4</v>
       </c>
       <c r="I55" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>177.58</v>
+        <v>131</v>
       </c>
       <c r="K55" t="n">
-        <v>-84.81999999999999</v>
+        <v>102.1</v>
       </c>
       <c r="L55" t="n">
-        <v>196.8</v>
+        <v>166.09</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:55:36</t>
+          <t>06:53:45</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.12</v>
+        <v>3.94</v>
       </c>
       <c r="F56" t="n">
-        <v>10.52</v>
+        <v>11.04</v>
       </c>
       <c r="G56" t="n">
-        <v>53.5</v>
+        <v>61.2</v>
       </c>
       <c r="H56" t="n">
-        <v>14.2</v>
+        <v>54.9</v>
       </c>
       <c r="I56" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>-110.43</v>
+        <v>148.46</v>
       </c>
       <c r="K56" t="n">
-        <v>-191.28</v>
+        <v>-211.16</v>
       </c>
       <c r="L56" t="n">
-        <v>220.87</v>
+        <v>258.13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:57:11</t>
+          <t>06:55:33</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="F57" t="n">
-        <v>8.109999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="G57" t="n">
-        <v>59.9</v>
+        <v>61.4</v>
       </c>
       <c r="H57" t="n">
-        <v>43.9</v>
+        <v>36.6</v>
       </c>
       <c r="I57" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>-198.42</v>
+        <v>18.11</v>
       </c>
       <c r="K57" t="n">
-        <v>36.25</v>
+        <v>-215.63</v>
       </c>
       <c r="L57" t="n">
-        <v>201.7</v>
+        <v>216.39</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:58:16</t>
+          <t>06:57:31</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.05</v>
+        <v>3.43</v>
       </c>
       <c r="F58" t="n">
-        <v>10.94</v>
+        <v>6.19</v>
       </c>
       <c r="G58" t="n">
-        <v>59.1</v>
+        <v>64.5</v>
       </c>
       <c r="H58" t="n">
-        <v>68.3</v>
+        <v>29.8</v>
       </c>
       <c r="I58" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>6.48</v>
+        <v>210.1</v>
       </c>
       <c r="K58" t="n">
-        <v>164.42</v>
+        <v>150.97</v>
       </c>
       <c r="L58" t="n">
-        <v>164.55</v>
+        <v>258.72</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:05:10</t>
+          <t>07:05:35</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.52</v>
+        <v>3.68</v>
       </c>
       <c r="F59" t="n">
-        <v>9.84</v>
+        <v>11.04</v>
       </c>
       <c r="G59" t="n">
-        <v>63.1</v>
+        <v>48.8</v>
       </c>
       <c r="H59" t="n">
-        <v>37.3</v>
+        <v>86.7</v>
       </c>
       <c r="I59" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>46.32</v>
+        <v>-4.95</v>
       </c>
       <c r="K59" t="n">
-        <v>16.85</v>
+        <v>37.88</v>
       </c>
       <c r="L59" t="n">
-        <v>49.29</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:07:03</t>
+          <t>07:08:05</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.53</v>
+        <v>3.7</v>
       </c>
       <c r="F60" t="n">
-        <v>6.39</v>
+        <v>10.29</v>
       </c>
       <c r="G60" t="n">
-        <v>47.9</v>
+        <v>53</v>
       </c>
       <c r="H60" t="n">
-        <v>45.9</v>
+        <v>48</v>
       </c>
       <c r="I60" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J60" t="n">
-        <v>47.64</v>
+        <v>-41.38</v>
       </c>
       <c r="K60" t="n">
-        <v>-20.39</v>
+        <v>55.35</v>
       </c>
       <c r="L60" t="n">
-        <v>51.82</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:08:19</t>
+          <t>07:10:06</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.13</v>
+        <v>3.33</v>
       </c>
       <c r="F61" t="n">
-        <v>10.01</v>
+        <v>9.42</v>
       </c>
       <c r="G61" t="n">
-        <v>67.3</v>
+        <v>46.8</v>
       </c>
       <c r="H61" t="n">
-        <v>72.09999999999999</v>
+        <v>37.1</v>
       </c>
       <c r="I61" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>51.89</v>
+        <v>32.06</v>
       </c>
       <c r="K61" t="n">
-        <v>-25.31</v>
+        <v>30.11</v>
       </c>
       <c r="L61" t="n">
-        <v>57.73</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:12:44</t>
+          <t>07:15:16</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.21</v>
+        <v>3.63</v>
       </c>
       <c r="F62" t="n">
         <v>11.04</v>
       </c>
       <c r="G62" t="n">
-        <v>41</v>
+        <v>58.5</v>
       </c>
       <c r="H62" t="n">
-        <v>36.1</v>
+        <v>65</v>
       </c>
       <c r="I62" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>77.88</v>
+        <v>81.98</v>
       </c>
       <c r="K62" t="n">
-        <v>0.6</v>
+        <v>33.65</v>
       </c>
       <c r="L62" t="n">
-        <v>77.88</v>
+        <v>88.61</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:14:39</t>
+          <t>07:17:17</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="F63" t="n">
-        <v>9.279999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>47.9</v>
+        <v>43.3</v>
       </c>
       <c r="H63" t="n">
-        <v>26.2</v>
+        <v>55.5</v>
       </c>
       <c r="I63" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>61.63</v>
+        <v>10.96</v>
       </c>
       <c r="K63" t="n">
-        <v>-6.55</v>
+        <v>75.78</v>
       </c>
       <c r="L63" t="n">
-        <v>61.98</v>
+        <v>76.56999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:16:17</t>
+          <t>07:19:54</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="F64" t="n">
-        <v>8.539999999999999</v>
+        <v>10.26</v>
       </c>
       <c r="G64" t="n">
-        <v>49.3</v>
+        <v>61.1</v>
       </c>
       <c r="H64" t="n">
-        <v>34.5</v>
+        <v>45.5</v>
       </c>
       <c r="I64" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>54.11</v>
+        <v>19.87</v>
       </c>
       <c r="K64" t="n">
-        <v>-81.33</v>
+        <v>79.53</v>
       </c>
       <c r="L64" t="n">
-        <v>97.68000000000001</v>
+        <v>81.97</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:19:38</t>
+          <t>07:24:18</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.09</v>
+        <v>3.34</v>
       </c>
       <c r="F65" t="n">
-        <v>10.76</v>
+        <v>9.73</v>
       </c>
       <c r="G65" t="n">
-        <v>61.5</v>
+        <v>50.8</v>
       </c>
       <c r="H65" t="n">
-        <v>21.5</v>
+        <v>62.5</v>
       </c>
       <c r="I65" t="n">
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>86.36</v>
+        <v>-23.52</v>
       </c>
       <c r="K65" t="n">
-        <v>-45.25</v>
+        <v>89.27</v>
       </c>
       <c r="L65" t="n">
-        <v>97.48999999999999</v>
+        <v>92.31999999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:21:07</t>
+          <t>07:25:59</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.96</v>
+        <v>3.59</v>
       </c>
       <c r="F66" t="n">
-        <v>9.56</v>
+        <v>9.19</v>
       </c>
       <c r="G66" t="n">
-        <v>58.6</v>
+        <v>46.7</v>
       </c>
       <c r="H66" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="I66" t="n">
         <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>122.74</v>
+        <v>-110.53</v>
       </c>
       <c r="K66" t="n">
-        <v>70.27</v>
+        <v>23.97</v>
       </c>
       <c r="L66" t="n">
-        <v>141.43</v>
+        <v>113.1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:22:05</t>
+          <t>07:27:37</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.47</v>
+        <v>4.08</v>
       </c>
       <c r="F67" t="n">
-        <v>10.3</v>
+        <v>9.1</v>
       </c>
       <c r="G67" t="n">
-        <v>76</v>
+        <v>49.1</v>
       </c>
       <c r="H67" t="n">
-        <v>33.6</v>
+        <v>0.7</v>
       </c>
       <c r="I67" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>-89.52</v>
+        <v>-57.38</v>
       </c>
       <c r="K67" t="n">
-        <v>-57.96</v>
+        <v>112.51</v>
       </c>
       <c r="L67" t="n">
-        <v>106.64</v>
+        <v>126.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:26:56</t>
+          <t>07:32:06</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.49</v>
+        <v>3.44</v>
       </c>
       <c r="F68" t="n">
-        <v>11.04</v>
+        <v>7.92</v>
       </c>
       <c r="G68" t="n">
-        <v>54.2</v>
+        <v>58.2</v>
       </c>
       <c r="H68" t="n">
-        <v>43.2</v>
+        <v>21.3</v>
       </c>
       <c r="I68" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-31.13</v>
+        <v>-128.66</v>
       </c>
       <c r="K68" t="n">
-        <v>160.58</v>
+        <v>-88.73</v>
       </c>
       <c r="L68" t="n">
-        <v>163.57</v>
+        <v>156.3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:28:56</t>
+          <t>07:33:30</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="F69" t="n">
-        <v>8.779999999999999</v>
+        <v>7.96</v>
       </c>
       <c r="G69" t="n">
-        <v>54.6</v>
+        <v>74</v>
       </c>
       <c r="H69" t="n">
-        <v>30.6</v>
+        <v>40.6</v>
       </c>
       <c r="I69" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-17.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>140.81</v>
+        <v>-147.85</v>
       </c>
       <c r="L69" t="n">
-        <v>141.87</v>
+        <v>168.78</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:31:01</t>
+          <t>07:34:59</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.29</v>
+        <v>3.97</v>
       </c>
       <c r="F70" t="n">
-        <v>7.12</v>
+        <v>11.04</v>
       </c>
       <c r="G70" t="n">
-        <v>54.3</v>
+        <v>42.7</v>
       </c>
       <c r="H70" t="n">
-        <v>27.5</v>
+        <v>40.2</v>
       </c>
       <c r="I70" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>7.76</v>
+        <v>39.49</v>
       </c>
       <c r="K70" t="n">
-        <v>-138.44</v>
+        <v>216.2</v>
       </c>
       <c r="L70" t="n">
-        <v>138.66</v>
+        <v>219.77</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:36:41</t>
+          <t>07:40:23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="F71" t="n">
-        <v>9.369999999999999</v>
+        <v>8.49</v>
       </c>
       <c r="G71" t="n">
-        <v>58.7</v>
+        <v>56.8</v>
       </c>
       <c r="H71" t="n">
-        <v>29.2</v>
+        <v>34.9</v>
       </c>
       <c r="I71" t="n">
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>255.42</v>
+        <v>216.9</v>
       </c>
       <c r="K71" t="n">
-        <v>-21.98</v>
+        <v>19.96</v>
       </c>
       <c r="L71" t="n">
-        <v>256.37</v>
+        <v>217.82</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:38:28</t>
+          <t>07:42:13</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="F72" t="n">
-        <v>8.15</v>
+        <v>7.91</v>
       </c>
       <c r="G72" t="n">
-        <v>69.2</v>
+        <v>41.3</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I72" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-252.39</v>
+        <v>-22.4</v>
       </c>
       <c r="K72" t="n">
-        <v>33.98</v>
+        <v>-208.32</v>
       </c>
       <c r="L72" t="n">
-        <v>254.67</v>
+        <v>209.52</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:39:44</t>
+          <t>07:43:09</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.95</v>
+        <v>4.17</v>
       </c>
       <c r="F73" t="n">
-        <v>9.300000000000001</v>
+        <v>11.04</v>
       </c>
       <c r="G73" t="n">
-        <v>55.3</v>
+        <v>49.4</v>
       </c>
       <c r="H73" t="n">
-        <v>27.9</v>
+        <v>20.1</v>
       </c>
       <c r="I73" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>64.33</v>
+        <v>156.05</v>
       </c>
       <c r="K73" t="n">
-        <v>-192.23</v>
+        <v>-335.17</v>
       </c>
       <c r="L73" t="n">
-        <v>202.7</v>
+        <v>369.72</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:51:48</t>
+          <t>07:50:40</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.47</v>
+        <v>3.8</v>
       </c>
       <c r="F74" t="n">
-        <v>11.01</v>
+        <v>9.84</v>
       </c>
       <c r="G74" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H74" t="n">
-        <v>38</v>
+        <v>53.5</v>
       </c>
       <c r="I74" t="n">
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.5</v>
+        <v>-40.2</v>
       </c>
       <c r="K74" t="n">
-        <v>68.5</v>
+        <v>57.81</v>
       </c>
       <c r="L74" t="n">
-        <v>68.65000000000001</v>
+        <v>70.41</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:53:19</t>
+          <t>07:52:30</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.57</v>
+        <v>3.46</v>
       </c>
       <c r="F75" t="n">
-        <v>10.9</v>
+        <v>8.26</v>
       </c>
       <c r="G75" t="n">
-        <v>61.1</v>
+        <v>47.1</v>
       </c>
       <c r="H75" t="n">
-        <v>48.1</v>
+        <v>46.2</v>
       </c>
       <c r="I75" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>55.91</v>
+        <v>-54.33</v>
       </c>
       <c r="K75" t="n">
-        <v>14.33</v>
+        <v>25.19</v>
       </c>
       <c r="L75" t="n">
-        <v>57.72</v>
+        <v>59.89</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:55:18</t>
+          <t>07:54:57</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="F76" t="n">
-        <v>8</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G76" t="n">
-        <v>49.3</v>
+        <v>76</v>
       </c>
       <c r="H76" t="n">
-        <v>50.9</v>
+        <v>33.6</v>
       </c>
       <c r="I76" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>32.86</v>
+        <v>-43.05</v>
       </c>
       <c r="K76" t="n">
-        <v>-57.39</v>
+        <v>-23.46</v>
       </c>
       <c r="L76" t="n">
-        <v>66.13</v>
+        <v>49.03</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:00:07</t>
+          <t>08:00:28</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.12</v>
+        <v>3.57</v>
       </c>
       <c r="F77" t="n">
-        <v>10.93</v>
+        <v>11.04</v>
       </c>
       <c r="G77" t="n">
-        <v>54.7</v>
+        <v>62.3</v>
       </c>
       <c r="H77" t="n">
-        <v>48.8</v>
+        <v>35.2</v>
       </c>
       <c r="I77" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>12.32</v>
+        <v>-42.63</v>
       </c>
       <c r="K77" t="n">
-        <v>-91.95</v>
+        <v>71.17</v>
       </c>
       <c r="L77" t="n">
-        <v>92.77</v>
+        <v>82.95999999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:01:10</t>
+          <t>08:01:30</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="F78" t="n">
-        <v>10.24</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G78" t="n">
-        <v>64.09999999999999</v>
+        <v>55.4</v>
       </c>
       <c r="H78" t="n">
-        <v>26.9</v>
+        <v>33.2</v>
       </c>
       <c r="I78" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>-107.95</v>
+        <v>11.77</v>
       </c>
       <c r="K78" t="n">
-        <v>2.28</v>
+        <v>77.75</v>
       </c>
       <c r="L78" t="n">
-        <v>107.97</v>
+        <v>78.64</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:03:33</t>
+          <t>08:04:04</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.83</v>
+        <v>3.78</v>
       </c>
       <c r="F79" t="n">
-        <v>9.890000000000001</v>
+        <v>11.04</v>
       </c>
       <c r="G79" t="n">
-        <v>65.5</v>
+        <v>54.3</v>
       </c>
       <c r="H79" t="n">
-        <v>29.2</v>
+        <v>27.5</v>
       </c>
       <c r="I79" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>40.49</v>
+        <v>-8.44</v>
       </c>
       <c r="K79" t="n">
-        <v>85.02</v>
+        <v>-71.11</v>
       </c>
       <c r="L79" t="n">
-        <v>94.17</v>
+        <v>71.61</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:07:37</t>
+          <t>08:09:56</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="F80" t="n">
-        <v>10.77</v>
+        <v>9.77</v>
       </c>
       <c r="G80" t="n">
-        <v>59.8</v>
+        <v>51.8</v>
       </c>
       <c r="H80" t="n">
-        <v>41</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>5.9</v>
+        <v>-98.25</v>
       </c>
       <c r="K80" t="n">
-        <v>-109.89</v>
+        <v>-35.86</v>
       </c>
       <c r="L80" t="n">
-        <v>110.05</v>
+        <v>104.59</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:09:03</t>
+          <t>08:11:31</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.11</v>
+        <v>3.51</v>
       </c>
       <c r="F81" t="n">
-        <v>8.65</v>
+        <v>8.49</v>
       </c>
       <c r="G81" t="n">
-        <v>51.7</v>
+        <v>35.8</v>
       </c>
       <c r="H81" t="n">
-        <v>26.9</v>
+        <v>26.4</v>
       </c>
       <c r="I81" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>17.49</v>
+        <v>-11.08</v>
       </c>
       <c r="K81" t="n">
-        <v>-29.21</v>
+        <v>167.64</v>
       </c>
       <c r="L81" t="n">
-        <v>34.05</v>
+        <v>168</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:10:56</t>
+          <t>08:12:21</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.45</v>
+        <v>3.49</v>
       </c>
       <c r="F82" t="n">
-        <v>8.550000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>65.09999999999999</v>
+        <v>53.8</v>
       </c>
       <c r="H82" t="n">
-        <v>20.7</v>
+        <v>4.8</v>
       </c>
       <c r="I82" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-45.44</v>
+        <v>44.82</v>
       </c>
       <c r="K82" t="n">
-        <v>110.79</v>
+        <v>-96.37</v>
       </c>
       <c r="L82" t="n">
-        <v>119.75</v>
+        <v>106.28</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:15:37</t>
+          <t>08:17:37</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.89</v>
+        <v>3.59</v>
       </c>
       <c r="F83" t="n">
-        <v>9.58</v>
+        <v>10.75</v>
       </c>
       <c r="G83" t="n">
-        <v>49.1</v>
+        <v>52.5</v>
       </c>
       <c r="H83" t="n">
-        <v>30.3</v>
+        <v>36.5</v>
       </c>
       <c r="I83" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>-202.75</v>
+        <v>96.42</v>
       </c>
       <c r="K83" t="n">
-        <v>83.56</v>
+        <v>-130.43</v>
       </c>
       <c r="L83" t="n">
-        <v>219.29</v>
+        <v>162.2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:17:52</t>
+          <t>08:19:35</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.37</v>
+        <v>3.57</v>
       </c>
       <c r="F84" t="n">
-        <v>10.79</v>
+        <v>11.04</v>
       </c>
       <c r="G84" t="n">
-        <v>44.1</v>
+        <v>48.6</v>
       </c>
       <c r="H84" t="n">
-        <v>35.8</v>
+        <v>42.8</v>
       </c>
       <c r="I84" t="n">
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-121.68</v>
+        <v>-213.42</v>
       </c>
       <c r="K84" t="n">
-        <v>-166.32</v>
+        <v>12.35</v>
       </c>
       <c r="L84" t="n">
-        <v>206.08</v>
+        <v>213.78</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:19:52</t>
+          <t>08:21:53</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="F85" t="n">
         <v>11.04</v>
       </c>
       <c r="G85" t="n">
-        <v>40.5</v>
+        <v>54.5</v>
       </c>
       <c r="H85" t="n">
-        <v>21.7</v>
+        <v>38.1</v>
       </c>
       <c r="I85" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>-30.38</v>
+        <v>-170.22</v>
       </c>
       <c r="K85" t="n">
-        <v>-139.65</v>
+        <v>-40.8</v>
       </c>
       <c r="L85" t="n">
-        <v>142.92</v>
+        <v>175.04</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:24:23</t>
+          <t>08:27:19</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.87</v>
+        <v>3.74</v>
       </c>
       <c r="F86" t="n">
-        <v>8.34</v>
+        <v>10.95</v>
       </c>
       <c r="G86" t="n">
-        <v>48.3</v>
+        <v>61.5</v>
       </c>
       <c r="H86" t="n">
-        <v>21.5</v>
+        <v>77.5</v>
       </c>
       <c r="I86" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J86" t="n">
-        <v>-73.06</v>
+        <v>-253.07</v>
       </c>
       <c r="K86" t="n">
-        <v>-312.66</v>
+        <v>117.84</v>
       </c>
       <c r="L86" t="n">
-        <v>321.08</v>
+        <v>279.16</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:26:23</t>
+          <t>08:28:52</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="F87" t="n">
-        <v>9.390000000000001</v>
+        <v>11.04</v>
       </c>
       <c r="G87" t="n">
-        <v>72.59999999999999</v>
+        <v>51.1</v>
       </c>
       <c r="H87" t="n">
-        <v>25.3</v>
+        <v>50.2</v>
       </c>
       <c r="I87" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>31.6</v>
+        <v>103.96</v>
       </c>
       <c r="K87" t="n">
-        <v>192.62</v>
+        <v>-253.49</v>
       </c>
       <c r="L87" t="n">
-        <v>195.2</v>
+        <v>273.98</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:27:24</t>
+          <t>08:30:47</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.39</v>
+        <v>3.34</v>
       </c>
       <c r="F88" t="n">
-        <v>11.04</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>49.7</v>
+        <v>52.4</v>
       </c>
       <c r="H88" t="n">
-        <v>28.5</v>
+        <v>58.4</v>
       </c>
       <c r="I88" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>-215.19</v>
+        <v>192.51</v>
       </c>
       <c r="K88" t="n">
-        <v>-39</v>
+        <v>75.52</v>
       </c>
       <c r="L88" t="n">
-        <v>218.69</v>
+        <v>206.79</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-22.xlsx
+++ b/output/2024-05-22.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-13.18</v>
+        <v>-13.52</v>
       </c>
       <c r="K14" t="n">
-        <v>48.28</v>
+        <v>49.52</v>
       </c>
       <c r="L14" t="n">
-        <v>50.04</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.31</v>
+        <v>-9.1</v>
       </c>
       <c r="K15" t="n">
-        <v>71.63</v>
+        <v>70.06</v>
       </c>
       <c r="L15" t="n">
-        <v>72.23999999999999</v>
+        <v>70.64</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-19.72</v>
+        <v>-19.02</v>
       </c>
       <c r="K16" t="n">
-        <v>-59.83</v>
+        <v>-57.71</v>
       </c>
       <c r="L16" t="n">
-        <v>63</v>
+        <v>60.77</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>50.68</v>
+        <v>55.04</v>
       </c>
       <c r="K17" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="L17" t="n">
-        <v>50.71</v>
+        <v>55.07</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>60.52</v>
+        <v>61.41</v>
       </c>
       <c r="K18" t="n">
-        <v>42.41</v>
+        <v>43.04</v>
       </c>
       <c r="L18" t="n">
-        <v>73.90000000000001</v>
+        <v>74.98999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-44.54</v>
+        <v>-43.53</v>
       </c>
       <c r="K19" t="n">
-        <v>55.58</v>
+        <v>54.32</v>
       </c>
       <c r="L19" t="n">
-        <v>71.22</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>-28.96</v>
+        <v>-30.72</v>
       </c>
       <c r="K20" t="n">
-        <v>82.73</v>
+        <v>87.75</v>
       </c>
       <c r="L20" t="n">
-        <v>87.65000000000001</v>
+        <v>92.97</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-68.45999999999999</v>
+        <v>-67.86</v>
       </c>
       <c r="K21" t="n">
-        <v>117.3</v>
+        <v>116.27</v>
       </c>
       <c r="L21" t="n">
-        <v>135.82</v>
+        <v>134.63</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-43.55</v>
+        <v>-44.74</v>
       </c>
       <c r="K22" t="n">
-        <v>96.77</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>106.12</v>
+        <v>109.01</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-117.74</v>
+        <v>-135.36</v>
       </c>
       <c r="K23" t="n">
-        <v>12.43</v>
+        <v>14.3</v>
       </c>
       <c r="L23" t="n">
-        <v>118.4</v>
+        <v>136.11</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-62.58</v>
+        <v>-73.70999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>-89.02</v>
+        <v>-104.85</v>
       </c>
       <c r="L24" t="n">
-        <v>108.82</v>
+        <v>128.17</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>98.44</v>
+        <v>105.56</v>
       </c>
       <c r="K25" t="n">
-        <v>-129.29</v>
+        <v>-138.63</v>
       </c>
       <c r="L25" t="n">
-        <v>162.5</v>
+        <v>174.25</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-159.47</v>
+        <v>-160.69</v>
       </c>
       <c r="K26" t="n">
-        <v>-256.27</v>
+        <v>-258.22</v>
       </c>
       <c r="L26" t="n">
-        <v>301.83</v>
+        <v>304.13</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>50.81</v>
+        <v>62.97</v>
       </c>
       <c r="K27" t="n">
-        <v>119.45</v>
+        <v>148.01</v>
       </c>
       <c r="L27" t="n">
-        <v>129.81</v>
+        <v>160.85</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-7.3</v>
+        <v>-8.75</v>
       </c>
       <c r="K28" t="n">
-        <v>-150.9</v>
+        <v>-180.8</v>
       </c>
       <c r="L28" t="n">
-        <v>151.08</v>
+        <v>181.02</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-58.42</v>
+        <v>-58.43</v>
       </c>
       <c r="K29" t="n">
         <v>-8.98</v>
       </c>
       <c r="L29" t="n">
-        <v>59.1</v>
+        <v>59.12</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-62.08</v>
+        <v>-58.04</v>
       </c>
       <c r="K30" t="n">
-        <v>-24.64</v>
+        <v>-23.03</v>
       </c>
       <c r="L30" t="n">
-        <v>66.79000000000001</v>
+        <v>62.44</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-47.65</v>
+        <v>-46.35</v>
       </c>
       <c r="K31" t="n">
-        <v>32.01</v>
+        <v>31.14</v>
       </c>
       <c r="L31" t="n">
-        <v>57.4</v>
+        <v>55.84</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-46.93</v>
+        <v>-50.95</v>
       </c>
       <c r="K32" t="n">
-        <v>-20.43</v>
+        <v>-22.18</v>
       </c>
       <c r="L32" t="n">
-        <v>51.18</v>
+        <v>55.57</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>-46.4</v>
+        <v>-46.55</v>
       </c>
       <c r="K33" t="n">
-        <v>-29.26</v>
+        <v>-29.36</v>
       </c>
       <c r="L33" t="n">
-        <v>54.86</v>
+        <v>55.03</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>70.19</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.76</v>
+        <v>-4.87</v>
       </c>
       <c r="L34" t="n">
-        <v>70.34999999999999</v>
+        <v>71.95999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-12.01</v>
+        <v>-12.34</v>
       </c>
       <c r="K35" t="n">
-        <v>105.5</v>
+        <v>108.4</v>
       </c>
       <c r="L35" t="n">
-        <v>106.18</v>
+        <v>109.1</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>108.05</v>
+        <v>110.23</v>
       </c>
       <c r="K36" t="n">
-        <v>-63.77</v>
+        <v>-65.06</v>
       </c>
       <c r="L36" t="n">
-        <v>125.46</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>30.57</v>
+        <v>30.35</v>
       </c>
       <c r="K37" t="n">
-        <v>-145.8</v>
+        <v>-144.76</v>
       </c>
       <c r="L37" t="n">
-        <v>148.97</v>
+        <v>147.91</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>24.08</v>
+        <v>25.22</v>
       </c>
       <c r="K38" t="n">
-        <v>-175.92</v>
+        <v>-184.24</v>
       </c>
       <c r="L38" t="n">
-        <v>177.56</v>
+        <v>185.96</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>32.51</v>
+        <v>36.84</v>
       </c>
       <c r="K39" t="n">
-        <v>-124.5</v>
+        <v>-141.06</v>
       </c>
       <c r="L39" t="n">
-        <v>128.68</v>
+        <v>145.79</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>94.52</v>
+        <v>114.5</v>
       </c>
       <c r="K40" t="n">
-        <v>1.23</v>
+        <v>1.49</v>
       </c>
       <c r="L40" t="n">
-        <v>94.52</v>
+        <v>114.51</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-176.07</v>
+        <v>-208.05</v>
       </c>
       <c r="K41" t="n">
-        <v>7.19</v>
+        <v>8.5</v>
       </c>
       <c r="L41" t="n">
-        <v>176.22</v>
+        <v>208.23</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>257.66</v>
+        <v>274.43</v>
       </c>
       <c r="K42" t="n">
-        <v>-13.89</v>
+        <v>-14.79</v>
       </c>
       <c r="L42" t="n">
-        <v>258.03</v>
+        <v>274.83</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>171.51</v>
+        <v>189.53</v>
       </c>
       <c r="K43" t="n">
-        <v>-143.22</v>
+        <v>-158.27</v>
       </c>
       <c r="L43" t="n">
-        <v>223.44</v>
+        <v>246.92</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>25.84</v>
+        <v>25.78</v>
       </c>
       <c r="K44" t="n">
-        <v>43.97</v>
+        <v>43.87</v>
       </c>
       <c r="L44" t="n">
-        <v>51</v>
+        <v>50.88</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>30.12</v>
+        <v>32.21</v>
       </c>
       <c r="K45" t="n">
-        <v>37.34</v>
+        <v>39.93</v>
       </c>
       <c r="L45" t="n">
-        <v>47.97</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-49.7</v>
+        <v>-50.02</v>
       </c>
       <c r="K46" t="n">
-        <v>23.46</v>
+        <v>23.61</v>
       </c>
       <c r="L46" t="n">
-        <v>54.96</v>
+        <v>55.31</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-9.19</v>
+        <v>-9.52</v>
       </c>
       <c r="K47" t="n">
-        <v>71.48999999999999</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>72.08</v>
+        <v>74.65000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-50.45</v>
+        <v>-49.58</v>
       </c>
       <c r="K48" t="n">
-        <v>-56.42</v>
+        <v>-55.45</v>
       </c>
       <c r="L48" t="n">
-        <v>75.69</v>
+        <v>74.38</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>47.59</v>
+        <v>47.57</v>
       </c>
       <c r="K49" t="n">
-        <v>51.97</v>
+        <v>51.95</v>
       </c>
       <c r="L49" t="n">
-        <v>70.47</v>
+        <v>70.44</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>119.68</v>
+        <v>116.81</v>
       </c>
       <c r="K50" t="n">
-        <v>-90.05</v>
+        <v>-87.89</v>
       </c>
       <c r="L50" t="n">
-        <v>149.77</v>
+        <v>146.19</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>28</v>
       </c>
       <c r="J51" t="n">
-        <v>-64.95</v>
+        <v>-67.12</v>
       </c>
       <c r="K51" t="n">
-        <v>-64.88</v>
+        <v>-67.05</v>
       </c>
       <c r="L51" t="n">
-        <v>91.8</v>
+        <v>94.87</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="K52" t="n">
-        <v>91.18000000000001</v>
+        <v>97.19</v>
       </c>
       <c r="L52" t="n">
-        <v>91.18000000000001</v>
+        <v>97.19</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-82.15000000000001</v>
+        <v>-91.04000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>94.98999999999999</v>
+        <v>105.27</v>
       </c>
       <c r="L53" t="n">
-        <v>125.58</v>
+        <v>139.18</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-50.34</v>
+        <v>-54.2</v>
       </c>
       <c r="K54" t="n">
-        <v>-132.53</v>
+        <v>-142.67</v>
       </c>
       <c r="L54" t="n">
-        <v>141.77</v>
+        <v>152.62</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-58.67</v>
+        <v>-62.35</v>
       </c>
       <c r="K55" t="n">
-        <v>-113.22</v>
+        <v>-120.31</v>
       </c>
       <c r="L55" t="n">
-        <v>127.51</v>
+        <v>135.51</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-87.69</v>
+        <v>-107</v>
       </c>
       <c r="K56" t="n">
-        <v>-144.14</v>
+        <v>-175.88</v>
       </c>
       <c r="L56" t="n">
-        <v>168.72</v>
+        <v>205.87</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-7.94</v>
+        <v>-8.83</v>
       </c>
       <c r="K57" t="n">
-        <v>-199.37</v>
+        <v>-221.73</v>
       </c>
       <c r="L57" t="n">
-        <v>199.52</v>
+        <v>221.91</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>15.17</v>
+        <v>17.16</v>
       </c>
       <c r="K58" t="n">
-        <v>176.06</v>
+        <v>199.24</v>
       </c>
       <c r="L58" t="n">
-        <v>176.71</v>
+        <v>199.98</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>69.19</v>
+        <v>66.36</v>
       </c>
       <c r="K59" t="n">
-        <v>-20.67</v>
+        <v>-19.83</v>
       </c>
       <c r="L59" t="n">
-        <v>72.22</v>
+        <v>69.25</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>23.64</v>
+        <v>24.56</v>
       </c>
       <c r="K60" t="n">
-        <v>39.14</v>
+        <v>40.67</v>
       </c>
       <c r="L60" t="n">
-        <v>45.73</v>
+        <v>47.51</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>50.92</v>
+        <v>54.78</v>
       </c>
       <c r="K61" t="n">
-        <v>4.66</v>
+        <v>5.01</v>
       </c>
       <c r="L61" t="n">
-        <v>51.13</v>
+        <v>55.01</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-17.23</v>
+        <v>-16.91</v>
       </c>
       <c r="K62" t="n">
-        <v>-79.61</v>
+        <v>-78.14</v>
       </c>
       <c r="L62" t="n">
-        <v>81.45</v>
+        <v>79.95</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>-48.05</v>
+        <v>-46.69</v>
       </c>
       <c r="K63" t="n">
-        <v>65.73999999999999</v>
+        <v>63.87</v>
       </c>
       <c r="L63" t="n">
-        <v>81.43000000000001</v>
+        <v>79.11</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>46.06</v>
+        <v>49.92</v>
       </c>
       <c r="K64" t="n">
-        <v>-22.77</v>
+        <v>-24.68</v>
       </c>
       <c r="L64" t="n">
-        <v>51.38</v>
+        <v>55.68</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-96.45999999999999</v>
+        <v>-105.83</v>
       </c>
       <c r="K65" t="n">
-        <v>26.14</v>
+        <v>28.68</v>
       </c>
       <c r="L65" t="n">
-        <v>99.94</v>
+        <v>109.65</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-4.26</v>
+        <v>-5.01</v>
       </c>
       <c r="K66" t="n">
-        <v>-69.79000000000001</v>
+        <v>-82.08</v>
       </c>
       <c r="L66" t="n">
-        <v>69.92</v>
+        <v>82.23</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>113.07</v>
+        <v>110.96</v>
       </c>
       <c r="K67" t="n">
-        <v>-67.76000000000001</v>
+        <v>-66.48999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>131.82</v>
+        <v>129.35</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>29.17</v>
+        <v>30.92</v>
       </c>
       <c r="K68" t="n">
-        <v>-168.09</v>
+        <v>-178.15</v>
       </c>
       <c r="L68" t="n">
-        <v>170.6</v>
+        <v>180.81</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-110.55</v>
+        <v>-119.41</v>
       </c>
       <c r="K69" t="n">
-        <v>-77.40000000000001</v>
+        <v>-83.59999999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>134.95</v>
+        <v>145.76</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-138.06</v>
+        <v>-150.21</v>
       </c>
       <c r="K70" t="n">
-        <v>82.67</v>
+        <v>89.95</v>
       </c>
       <c r="L70" t="n">
-        <v>160.92</v>
+        <v>175.09</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>125.69</v>
+        <v>148.38</v>
       </c>
       <c r="K71" t="n">
-        <v>71.01000000000001</v>
+        <v>83.83</v>
       </c>
       <c r="L71" t="n">
-        <v>144.36</v>
+        <v>170.42</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>49.23</v>
+        <v>54.23</v>
       </c>
       <c r="K72" t="n">
-        <v>220.02</v>
+        <v>242.41</v>
       </c>
       <c r="L72" t="n">
-        <v>225.46</v>
+        <v>248.4</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-111.05</v>
+        <v>-123.26</v>
       </c>
       <c r="K73" t="n">
-        <v>157.51</v>
+        <v>174.84</v>
       </c>
       <c r="L73" t="n">
-        <v>192.72</v>
+        <v>213.92</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>10.38</v>
+        <v>11.09</v>
       </c>
       <c r="K74" t="n">
-        <v>-45.92</v>
+        <v>-49.07</v>
       </c>
       <c r="L74" t="n">
-        <v>47.08</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>23.49</v>
+        <v>24.72</v>
       </c>
       <c r="K75" t="n">
-        <v>-41.25</v>
+        <v>-43.4</v>
       </c>
       <c r="L75" t="n">
-        <v>47.47</v>
+        <v>49.94</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>-64.34</v>
+        <v>-64.31999999999999</v>
       </c>
       <c r="K76" t="n">
         <v>9.869999999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>65.09</v>
+        <v>65.06999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-46.16</v>
+        <v>-46.15</v>
       </c>
       <c r="K77" t="n">
-        <v>61.05</v>
+        <v>61.03</v>
       </c>
       <c r="L77" t="n">
-        <v>76.53</v>
+        <v>76.52</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-20.36</v>
+        <v>-20.55</v>
       </c>
       <c r="K78" t="n">
-        <v>68.23</v>
+        <v>68.89</v>
       </c>
       <c r="L78" t="n">
-        <v>71.20999999999999</v>
+        <v>71.89</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="K79" t="n">
-        <v>86.70999999999999</v>
+        <v>85.34999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>86.72</v>
+        <v>85.36</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>69.19</v>
+        <v>73.94</v>
       </c>
       <c r="K80" t="n">
-        <v>92.06</v>
+        <v>98.38</v>
       </c>
       <c r="L80" t="n">
-        <v>115.16</v>
+        <v>123.07</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-41.45</v>
+        <v>-45.52</v>
       </c>
       <c r="K81" t="n">
-        <v>58.51</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>71.7</v>
+        <v>78.75</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-45.59</v>
+        <v>-46.67</v>
       </c>
       <c r="K82" t="n">
-        <v>87.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>98.93000000000001</v>
+        <v>101.29</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-121.54</v>
+        <v>-131.11</v>
       </c>
       <c r="K83" t="n">
-        <v>-89.31</v>
+        <v>-96.34</v>
       </c>
       <c r="L83" t="n">
-        <v>150.82</v>
+        <v>162.7</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>74.47</v>
+        <v>81.61</v>
       </c>
       <c r="K84" t="n">
-        <v>121.63</v>
+        <v>133.3</v>
       </c>
       <c r="L84" t="n">
-        <v>142.62</v>
+        <v>156.29</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>102.85</v>
+        <v>117.05</v>
       </c>
       <c r="K85" t="n">
-        <v>64.94</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>121.64</v>
+        <v>138.42</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-202.08</v>
+        <v>-224.91</v>
       </c>
       <c r="K86" t="n">
-        <v>16.13</v>
+        <v>17.96</v>
       </c>
       <c r="L86" t="n">
-        <v>202.72</v>
+        <v>225.62</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>19.9</v>
+        <v>23.05</v>
       </c>
       <c r="K87" t="n">
-        <v>-174.47</v>
+        <v>-202.05</v>
       </c>
       <c r="L87" t="n">
-        <v>175.61</v>
+        <v>203.36</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>83.2</v>
+        <v>93.36</v>
       </c>
       <c r="K88" t="n">
-        <v>-156.75</v>
+        <v>-175.89</v>
       </c>
       <c r="L88" t="n">
-        <v>177.46</v>
+        <v>199.14</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-22.xlsx
+++ b/output/2024-05-22.xlsx
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.1</v>
+        <v>-9.25</v>
       </c>
       <c r="K15" t="n">
-        <v>70.06</v>
+        <v>71.19</v>
       </c>
       <c r="L15" t="n">
-        <v>70.64</v>
+        <v>71.79000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-58.43</v>
+        <v>-62.32</v>
       </c>
       <c r="K29" t="n">
-        <v>-8.98</v>
+        <v>-9.58</v>
       </c>
       <c r="L29" t="n">
-        <v>59.12</v>
+        <v>63.05</v>
       </c>
     </row>
     <row r="30">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-50.95</v>
+        <v>-53.3</v>
       </c>
       <c r="K32" t="n">
-        <v>-22.18</v>
+        <v>-23.2</v>
       </c>
       <c r="L32" t="n">
-        <v>55.57</v>
+        <v>58.13</v>
       </c>
     </row>
     <row r="33">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>71.79000000000001</v>
+        <v>75.95</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.87</v>
+        <v>-5.15</v>
       </c>
       <c r="L34" t="n">
-        <v>71.95999999999999</v>
+        <v>76.12</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>25.78</v>
+        <v>26.04</v>
       </c>
       <c r="K44" t="n">
-        <v>43.87</v>
+        <v>44.3</v>
       </c>
       <c r="L44" t="n">
-        <v>50.88</v>
+        <v>51.39</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>32.21</v>
+        <v>33.29</v>
       </c>
       <c r="K45" t="n">
-        <v>39.93</v>
+        <v>41.27</v>
       </c>
       <c r="L45" t="n">
-        <v>51.3</v>
+        <v>53.02</v>
       </c>
     </row>
     <row r="46">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-9.52</v>
+        <v>-11.28</v>
       </c>
       <c r="K47" t="n">
-        <v>74.04000000000001</v>
+        <v>87.72</v>
       </c>
       <c r="L47" t="n">
-        <v>74.65000000000001</v>
+        <v>88.44</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-49.58</v>
+        <v>-50.33</v>
       </c>
       <c r="K48" t="n">
-        <v>-55.45</v>
+        <v>-56.28</v>
       </c>
       <c r="L48" t="n">
-        <v>74.38</v>
+        <v>75.51000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>47.57</v>
+        <v>51.9</v>
       </c>
       <c r="K49" t="n">
-        <v>51.95</v>
+        <v>56.67</v>
       </c>
       <c r="L49" t="n">
-        <v>70.44</v>
+        <v>76.84</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>66.36</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>-19.83</v>
+        <v>-20.18</v>
       </c>
       <c r="L59" t="n">
-        <v>69.25</v>
+        <v>70.48999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>54.78</v>
+        <v>61.25</v>
       </c>
       <c r="K61" t="n">
-        <v>5.01</v>
+        <v>5.61</v>
       </c>
       <c r="L61" t="n">
-        <v>55.01</v>
+        <v>61.51</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-16.91</v>
+        <v>-17.45</v>
       </c>
       <c r="K62" t="n">
-        <v>-78.14</v>
+        <v>-80.63</v>
       </c>
       <c r="L62" t="n">
-        <v>79.95</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>-46.69</v>
+        <v>-48.77</v>
       </c>
       <c r="K63" t="n">
-        <v>63.87</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>79.11</v>
+        <v>82.64</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>49.92</v>
+        <v>50.55</v>
       </c>
       <c r="K64" t="n">
-        <v>-24.68</v>
+        <v>-24.99</v>
       </c>
       <c r="L64" t="n">
-        <v>55.68</v>
+        <v>56.39</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>11.09</v>
+        <v>12.89</v>
       </c>
       <c r="K74" t="n">
-        <v>-49.07</v>
+        <v>-57.02</v>
       </c>
       <c r="L74" t="n">
-        <v>50.3</v>
+        <v>58.46</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>24.72</v>
+        <v>29.2</v>
       </c>
       <c r="K75" t="n">
-        <v>-43.4</v>
+        <v>-51.27</v>
       </c>
       <c r="L75" t="n">
-        <v>49.94</v>
+        <v>59</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>-64.31999999999999</v>
+        <v>-72.20999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>9.869999999999999</v>
+        <v>11.08</v>
       </c>
       <c r="L76" t="n">
-        <v>65.06999999999999</v>
+        <v>73.06</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-46.15</v>
+        <v>-54.51</v>
       </c>
       <c r="K77" t="n">
-        <v>61.03</v>
+        <v>72.09</v>
       </c>
       <c r="L77" t="n">
-        <v>76.52</v>
+        <v>90.37</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-20.55</v>
+        <v>-20.89</v>
       </c>
       <c r="K78" t="n">
-        <v>68.89</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>71.89</v>
+        <v>73.06</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="K79" t="n">
-        <v>85.34999999999999</v>
+        <v>110.24</v>
       </c>
       <c r="L79" t="n">
-        <v>85.36</v>
+        <v>110.26</v>
       </c>
     </row>
     <row r="80">
